--- a/Result/checksun_type/ITO導電玻璃.xlsx
+++ b/Result/checksun_type/ITO導電玻璃.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1498.0</t>
+          <t>390.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17.50</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-124.37</t>
+          <t>-120.78</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>83395.5998552822</t>
+          <t>83295.19942196531</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>16891.0</t>
+          <t>18210.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>10195.3</t>
+          <t>10729.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>10437.66</t>
+          <t>8369.26</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>390.5343885617743</t>
+          <t>779.7799219306776</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>3886.84</v>
+        <v>2920.63</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,42 +1177,42 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-7.376381350194507</t>
+          <t>-13.42998910113004</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-8.26694245871643</t>
+          <t>-25.43417574544826</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-3.481449886138677</t>
+          <t>-6.333574654154932</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>108.41</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1623.0</t>
+          <t>1498.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>65.67</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>61.41</t>
+          <t>86.42</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-127.21</t>
+          <t>-124.37</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>83395.5998552822</t>
+          <t>83295.19942196531</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>38343.0</t>
+          <t>36258.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>10310.4</t>
+          <t>16891.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>7058.7</t>
+          <t>10195.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>13160.96</t>
+          <t>10437.66</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-245.1581173895633</t>
+          <t>390.5343885617743</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>2237.72</v>
+        <v>3886.84</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,42 +1608,42 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-7.376381350194507</t>
+          <t>-13.42998910113004</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-8.26694245871643</t>
+          <t>-25.43417574544826</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-3.481449886138677</t>
+          <t>-6.333574654154932</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>108.41</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>1623.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>61.41</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>26.72</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-129.03</t>
+          <t>-127.21</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>83395.5998552822</t>
+          <t>83295.19942196531</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4524.0</t>
+          <t>38343.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>10310.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3638.9</t>
+          <t>7058.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>12810.66</t>
+          <t>13160.96</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-588</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-696.5912702806586</t>
+          <t>-245.1581173895633</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-421.47</v>
+        <v>2237.72</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,42 +2039,42 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-7.376381350194507</t>
+          <t>-13.42998910113004</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-8.26694245871643</t>
+          <t>-25.43417574544826</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-3.481449886138677</t>
+          <t>-6.333574654154932</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>108.41</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-26.87</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-13.49</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,72 +2302,72 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-128.78</t>
+          <t>-129.03</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>83395.5998552822</t>
+          <t>83295.19942196531</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2647.0</t>
+          <t>4524.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>2718.6</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3717.5</t>
+          <t>3638.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>13031.08</t>
+          <t>12810.66</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-998</t>
+          <t>-588</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-746.6130345102762</t>
+          <t>-696.5912702806586</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-581.8099999999999</v>
+        <v>-421.47</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-16.93</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,27 +2470,27 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-7.376381350194507</t>
+          <t>-13.42998910113004</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-8.26694245871643</t>
+          <t>-25.43417574544826</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-3.481449886138677</t>
+          <t>-6.333574654154932</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>108.41</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-15.70</t>
+          <t>-26.87</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-15.87</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,67 +2733,67 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>23.73</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-11.42</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-127.96</t>
+          <t>-128.78</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>83395.5998552822</t>
+          <t>83295.19942196531</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2683.0</t>
+          <t>2647.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>3248.8</t>
+          <t>2718.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>3717.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>13496.96</t>
+          <t>13031.08</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-605</t>
+          <t>-998</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-776.5779763001415</t>
+          <t>-746.6130345102762</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-588.97</v>
+        <v>-581.8099999999999</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-17.51</t>
+          <t>-16.93</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,27 +2901,27 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-7.376381350194507</t>
+          <t>-13.42998910113004</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-8.26694245871643</t>
+          <t>-25.43417574544826</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-3.481449886138677</t>
+          <t>-6.333574654154932</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>108.41</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2991,17 +2991,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>10.92</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-13.67</t>
+          <t>-15.70</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-14.29</t>
+          <t>-15.87</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,17 +3164,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,57 +3184,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-14.16</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-126.97</t>
+          <t>-127.96</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>83395.5998552822</t>
+          <t>83295.19942196531</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>2683.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>3499.6</t>
+          <t>3248.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4053.7</t>
+          <t>3854.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>13799.2</t>
+          <t>13496.96</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-554</t>
+          <t>-605</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-810.6887149656693</t>
+          <t>-776.5779763001415</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-582.02</v>
+        <v>-588.97</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-15.95</t>
+          <t>-17.51</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,27 +3332,27 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-7.376381350194507</t>
+          <t>-13.42998910113004</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-8.26694245871643</t>
+          <t>-25.43417574544826</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-3.481449886138677</t>
+          <t>-6.333574654154932</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>108.41</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-13.67</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-13.89</t>
+          <t>-14.29</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,67 +3595,67 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.77</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-16.06</t>
+          <t>-13.09</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-126.09</t>
+          <t>-126.97</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>83395.5998552822</t>
+          <t>83295.19942196531</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2041.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3807.0</t>
+          <t>3499.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3998.4</t>
+          <t>4053.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>14454.38</t>
+          <t>13799.2</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-191</t>
+          <t>-554</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-852.264046081364</t>
+          <t>-810.6887149656693</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-623.3200000000001</v>
+        <v>-582.02</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-15.56</t>
+          <t>-15.95</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,27 +3763,27 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-7.376381350194507</t>
+          <t>-13.42998910113004</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-8.26694245871643</t>
+          <t>-25.43417574544826</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-3.481449886138677</t>
+          <t>-6.333574654154932</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>108.41</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-14.88</t>
+          <t>-13.89</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>21.77</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-20.05</t>
+          <t>-16.06</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-125.04</t>
+          <t>-126.09</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>83395.5998552822</t>
+          <t>83295.19942196531</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2867.0</t>
+          <t>2041.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>4227.8</t>
+          <t>3807.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4048.6</t>
+          <t>3998.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>16723.7</t>
+          <t>14454.38</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>-191</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-893.8907697781259</t>
+          <t>-852.264046081364</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-519.26</v>
+        <v>-623.3200000000001</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-16.54</t>
+          <t>-15.56</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,22 +4194,22 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-7.376381350194507</t>
+          <t>-13.42998910113004</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-8.26694245871643</t>
+          <t>-25.43417574544826</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-3.481449886138677</t>
+          <t>-6.333574654154932</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>108.41</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-14.09</t>
+          <t>-14.88</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>22.94</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-18.04</t>
+          <t>-20.05</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-123.78</t>
+          <t>-125.04</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>83395.5998552822</t>
+          <t>83295.19942196531</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>5298.0</t>
+          <t>2867.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>4716.4</t>
+          <t>4227.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4361.7</t>
+          <t>4048.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>17648.9</t>
+          <t>16723.7</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>179</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-962.0055353740148</t>
+          <t>-893.8907697781259</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-440.56</v>
+        <v>-519.26</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-16.54</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,27 +4625,27 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-7.376381350194507</t>
+          <t>-13.42998910113004</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-8.26694245871643</t>
+          <t>-25.43417574544826</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-3.481449886138677</t>
+          <t>-6.333574654154932</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>108.41</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.15</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>178.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>9.03</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-12.50</t>
+          <t>-14.09</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,17 +4888,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.14</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>22.94</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>24.16</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-15.15</t>
+          <t>-18.04</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-122.71</t>
+          <t>-123.78</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>83395.5998552822</t>
+          <t>83295.19942196531</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3937.0</t>
+          <t>5298.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>4459.2</t>
+          <t>4716.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4382.4</t>
+          <t>4361.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>18368.1</t>
+          <t>17648.9</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>354</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1056.81363386356</t>
+          <t>-962.0055353740148</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-572.86</v>
+        <v>-440.56</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-14.20</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,27 +5056,27 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-7.376381350194507</t>
+          <t>-13.42998910113004</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-8.26694245871643</t>
+          <t>-25.43417574544826</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-3.481449886138677</t>
+          <t>-6.333574654154932</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>108.41</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>221.0</t>
+          <t>178.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-12.70</t>
+          <t>-12.50</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>390</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>23.18</t>
+          <t>23.07</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>24.22</t>
+          <t>24.16</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-15.98</t>
+          <t>-15.15</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-121.85</t>
+          <t>-122.71</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>83395.5998552822</t>
+          <t>83295.19942196531</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4892.0</t>
+          <t>3937.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>4607.8</t>
+          <t>4459.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4347.6</t>
+          <t>4382.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>19203.82</t>
+          <t>18368.1</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1144.804397055427</t>
+          <t>-1056.81363386356</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-595.59</v>
+        <v>-572.86</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-14.40</t>
+          <t>-14.20</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,27 +5487,27 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-7.376381350194507</t>
+          <t>-13.42998910113004</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-8.26694245871643</t>
+          <t>-25.43417574544826</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-3.481449886138677</t>
+          <t>-6.333574654154932</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>108.41</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>86.33</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22.05</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/ITO導電玻璃.xlsx
+++ b/Result/checksun_type/ITO導電玻璃.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>390.0</t>
+          <t>426.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>75.73</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>426</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>91.82</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-120.78</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>83295.19942196531</t>
+          <t>83196.71428571429</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>18210.2</t>
+          <t>19686.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>10729.5</t>
+          <t>11202.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>8369.26</t>
+          <t>8102.12</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>779.7799219306776</t>
+          <t>1002.520030170422</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>2920.63</v>
+        <v>2227.59</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1267,17 +1267,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>23.15</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>23.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1498.0</t>
+          <t>390.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>426</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-124.37</t>
+          <t>-120.78</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>83295.19942196531</t>
+          <t>83196.71428571429</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>16891.0</t>
+          <t>18210.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>10195.3</t>
+          <t>10729.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>10437.66</t>
+          <t>8369.26</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>390.5343885617743</t>
+          <t>779.7799219306776</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>3886.84</v>
+        <v>2920.63</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1623.0</t>
+          <t>1498.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>65.67</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>426</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>61.41</t>
+          <t>86.42</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-127.21</t>
+          <t>-124.37</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>83295.19942196531</t>
+          <t>83196.71428571429</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>38343.0</t>
+          <t>36258.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>10310.4</t>
+          <t>16891.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>7058.7</t>
+          <t>10195.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>13160.96</t>
+          <t>10437.66</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-245.1581173895633</t>
+          <t>390.5343885617743</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>2237.72</v>
+        <v>3886.84</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>1623.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>426</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>61.41</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>26.72</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-129.03</t>
+          <t>-127.21</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>83295.19942196531</t>
+          <t>83196.71428571429</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4524.0</t>
+          <t>38343.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>10310.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3638.9</t>
+          <t>7058.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>12810.66</t>
+          <t>13160.96</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-588</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-696.5912702806586</t>
+          <t>-245.1581173895633</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-421.47</v>
+        <v>2237.72</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-26.87</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-13.49</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,72 +2733,72 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>426</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-128.78</t>
+          <t>-129.03</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>83295.19942196531</t>
+          <t>83196.71428571429</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2647.0</t>
+          <t>4524.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>2718.6</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3717.5</t>
+          <t>3638.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>13031.08</t>
+          <t>12810.66</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-998</t>
+          <t>-588</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-746.6130345102762</t>
+          <t>-696.5912702806586</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-581.8099999999999</v>
+        <v>-421.47</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-16.93</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>10.92</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-15.70</t>
+          <t>-26.87</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-15.87</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,67 +3164,67 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>426</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>23.73</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-11.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-127.96</t>
+          <t>-128.78</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>83295.19942196531</t>
+          <t>83196.71428571429</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2683.0</t>
+          <t>2647.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>3248.8</t>
+          <t>2718.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>3717.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>13496.96</t>
+          <t>13031.08</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-605</t>
+          <t>-998</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-776.5779763001415</t>
+          <t>-746.6130345102762</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-588.97</v>
+        <v>-581.8099999999999</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-17.51</t>
+          <t>-16.93</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-13.67</t>
+          <t>-15.70</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-14.29</t>
+          <t>-15.87</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,17 +3595,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>426</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3615,57 +3615,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-14.16</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-126.97</t>
+          <t>-127.96</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>83295.19942196531</t>
+          <t>83196.71428571429</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>2683.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3499.6</t>
+          <t>3248.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4053.7</t>
+          <t>3854.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>13799.2</t>
+          <t>13496.96</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-554</t>
+          <t>-605</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-810.6887149656693</t>
+          <t>-776.5779763001415</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-582.02</v>
+        <v>-588.97</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-15.95</t>
+          <t>-17.51</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-13.67</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-13.89</t>
+          <t>-14.29</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,67 +4026,67 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>426</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.77</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-16.06</t>
+          <t>-13.09</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-126.09</t>
+          <t>-126.97</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>83295.19942196531</t>
+          <t>83196.71428571429</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2041.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>3807.0</t>
+          <t>3499.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3998.4</t>
+          <t>4053.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>14454.38</t>
+          <t>13799.2</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-191</t>
+          <t>-554</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-852.264046081364</t>
+          <t>-810.6887149656693</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-623.3200000000001</v>
+        <v>-582.02</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-15.56</t>
+          <t>-15.95</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-14.88</t>
+          <t>-13.89</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>426</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>21.77</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-20.05</t>
+          <t>-16.06</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-125.04</t>
+          <t>-126.09</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>83295.19942196531</t>
+          <t>83196.71428571429</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2867.0</t>
+          <t>2041.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>4227.8</t>
+          <t>3807.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4048.6</t>
+          <t>3998.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>16723.7</t>
+          <t>14454.38</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>-191</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-893.8907697781259</t>
+          <t>-852.264046081364</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-519.26</v>
+        <v>-623.3200000000001</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-16.54</t>
+          <t>-15.56</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9.03</t>
+          <t>8.92</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-14.09</t>
+          <t>-14.88</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>426</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>22.94</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-18.04</t>
+          <t>-20.05</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-123.78</t>
+          <t>-125.04</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>83295.19942196531</t>
+          <t>83196.71428571429</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>5298.0</t>
+          <t>2867.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>4716.4</t>
+          <t>4227.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4361.7</t>
+          <t>4048.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>17648.9</t>
+          <t>16723.7</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>179</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-962.0055353740148</t>
+          <t>-893.8907697781259</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-440.56</v>
+        <v>-519.26</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-16.54</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.15</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>178.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>8.07</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-12.50</t>
+          <t>-14.09</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,17 +5319,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>426</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.14</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>23.07</t>
+          <t>22.94</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>24.16</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-15.15</t>
+          <t>-18.04</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-122.71</t>
+          <t>-123.78</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>83295.19942196531</t>
+          <t>83196.71428571429</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3937.0</t>
+          <t>5298.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>4459.2</t>
+          <t>4716.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4382.4</t>
+          <t>4361.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>18368.1</t>
+          <t>17648.9</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>354</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1056.81363386356</t>
+          <t>-962.0055353740148</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-572.86</v>
+        <v>-440.56</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-14.20</t>
+          <t>-15.76</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>86.33</t>
+          <t>84.03</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/ITO導電玻璃.xlsx
+++ b/Result/checksun_type/ITO導電玻璃.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>426.0</t>
+          <t>293.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>75.73</t>
+          <t>73.69</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>91.82</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>22.43</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>87.14</t>
+          <t>92.50</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-113.86</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>83196.71428571429</t>
+          <t>83091.50144092219</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>19686.8</t>
+          <t>20139.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>11202.7</t>
+          <t>11594.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>8102.12</t>
+          <t>7648.36</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1002.520030170422</t>
+          <t>1070.358956124564</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>2227.59</v>
+        <v>1443.47</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>107.05</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>390.0</t>
+          <t>426.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>75.73</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>91.82</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-120.78</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>83196.71428571429</t>
+          <t>83091.50144092219</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>18210.2</t>
+          <t>19686.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>10729.5</t>
+          <t>11202.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>8369.26</t>
+          <t>8102.12</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>779.7799219306776</t>
+          <t>1002.520030170422</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>2920.63</v>
+        <v>2227.59</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>107.05</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1698,17 +1698,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>23.15</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>23.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1498.0</t>
+          <t>390.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-124.37</t>
+          <t>-120.78</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>83196.71428571429</t>
+          <t>83091.50144092219</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>16891.0</t>
+          <t>18210.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>10195.3</t>
+          <t>10729.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>10437.66</t>
+          <t>8369.26</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>390.5343885617743</t>
+          <t>779.7799219306776</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>3886.84</v>
+        <v>2920.63</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>107.05</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1623.0</t>
+          <t>1498.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>65.67</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>61.41</t>
+          <t>86.42</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-127.21</t>
+          <t>-124.37</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>83196.71428571429</t>
+          <t>83091.50144092219</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>38343.0</t>
+          <t>36258.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>10310.4</t>
+          <t>16891.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>7058.7</t>
+          <t>10195.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>13160.96</t>
+          <t>10437.66</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-245.1581173895633</t>
+          <t>390.5343885617743</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>2237.72</v>
+        <v>3886.84</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>107.05</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>1623.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>61.41</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>26.72</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-129.03</t>
+          <t>-127.21</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>83196.71428571429</t>
+          <t>83091.50144092219</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4524.0</t>
+          <t>38343.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>10310.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3638.9</t>
+          <t>7058.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>12810.66</t>
+          <t>13160.96</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-588</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-696.5912702806586</t>
+          <t>-245.1581173895633</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-421.47</v>
+        <v>2237.72</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>107.05</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-26.87</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-13.49</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,72 +3164,72 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-128.78</t>
+          <t>-129.03</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>83196.71428571429</t>
+          <t>83091.50144092219</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2647.0</t>
+          <t>4524.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>2718.6</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3717.5</t>
+          <t>3638.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>13031.08</t>
+          <t>12810.66</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-998</t>
+          <t>-588</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-746.6130345102762</t>
+          <t>-696.5912702806586</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-581.8099999999999</v>
+        <v>-421.47</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-16.93</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>107.05</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-15.70</t>
+          <t>-26.87</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-15.87</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,67 +3595,67 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>23.73</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-11.42</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-127.96</t>
+          <t>-128.78</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>83196.71428571429</t>
+          <t>83091.50144092219</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2683.0</t>
+          <t>2647.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3248.8</t>
+          <t>2718.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>3717.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>13496.96</t>
+          <t>13031.08</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-605</t>
+          <t>-998</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-776.5779763001415</t>
+          <t>-746.6130345102762</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-588.97</v>
+        <v>-581.8099999999999</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-17.51</t>
+          <t>-16.93</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>107.05</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3853,17 +3853,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>7.83</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-13.67</t>
+          <t>-15.70</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-14.29</t>
+          <t>-15.87</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,17 +4026,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4046,57 +4046,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-14.16</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-126.97</t>
+          <t>-127.96</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>83196.71428571429</t>
+          <t>83091.50144092219</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>2683.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>3499.6</t>
+          <t>3248.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4053.7</t>
+          <t>3854.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>13799.2</t>
+          <t>13496.96</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-554</t>
+          <t>-605</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-810.6887149656693</t>
+          <t>-776.5779763001415</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-582.02</v>
+        <v>-588.97</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-15.95</t>
+          <t>-17.51</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>107.05</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-13.67</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-13.89</t>
+          <t>-14.29</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,67 +4457,67 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.77</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-16.06</t>
+          <t>-13.09</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-126.09</t>
+          <t>-126.97</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>83196.71428571429</t>
+          <t>83091.50144092219</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2041.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>3807.0</t>
+          <t>3499.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>3998.4</t>
+          <t>4053.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>14454.38</t>
+          <t>13799.2</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-191</t>
+          <t>-554</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-852.264046081364</t>
+          <t>-810.6887149656693</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-623.3200000000001</v>
+        <v>-582.02</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-15.56</t>
+          <t>-15.95</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>107.05</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.92</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-14.88</t>
+          <t>-13.89</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>21.77</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-20.05</t>
+          <t>-16.06</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-125.04</t>
+          <t>-126.09</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>83196.71428571429</t>
+          <t>83091.50144092219</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2867.0</t>
+          <t>2041.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>4227.8</t>
+          <t>3807.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4048.6</t>
+          <t>3998.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>16723.7</t>
+          <t>14454.38</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>-191</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-893.8907697781259</t>
+          <t>-852.264046081364</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-519.26</v>
+        <v>-623.3200000000001</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-16.54</t>
+          <t>-15.56</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>107.05</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-14.09</t>
+          <t>-14.88</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>22.14</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>22.94</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-18.04</t>
+          <t>-20.05</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-123.78</t>
+          <t>-125.04</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>83196.71428571429</t>
+          <t>83091.50144092219</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>5298.0</t>
+          <t>2867.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>4716.4</t>
+          <t>4227.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4361.7</t>
+          <t>4048.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>17648.9</t>
+          <t>16723.7</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>179</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-962.0055353740148</t>
+          <t>-893.8907697781259</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-440.56</v>
+        <v>-519.26</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-15.76</t>
+          <t>-16.54</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>107.05</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>84.03</t>
+          <t>84.12</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.15</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/ITO導電玻璃.xlsx
+++ b/Result/checksun_type/ITO導電玻璃.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>293.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,84 +893,84 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>73.69</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>0</t>
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,275 +1009,275 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>81.76</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
+          <t>23.49</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>22.46</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>23.57</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>119.34</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-110.67</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>82989.77697841727</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>14123.0</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>12216.7</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>7629.54</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>1054.796642723689</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>969.2</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>-8.37</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>-13.42998910113004</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-25.43417574544826</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-6.333574654154932</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>107.05</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>19.70%</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>85.54</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>1612</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>安可-光電業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>光電業平上櫃</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>23.45</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>24.05</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>22.43</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>23.42</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>92.50</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-113.86</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>83091.50144092219</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>20139.2</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>11594.6</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>7648.36</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>8544</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>1070.358956124564</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>1443.47</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-10.51</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>-13.42998910113004</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-25.43417574544826</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-6.333574654154932</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>104.55</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>19.70%</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>-0.85%</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>84.12</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>1575</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>安可-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>光電業平上櫃</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>23.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>426.0</t>
+          <t>293.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>75.73</t>
+          <t>73.69</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>91.82</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>22.43</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>87.14</t>
+          <t>92.50</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-113.86</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>83091.50144092219</t>
+          <t>82989.77697841727</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>19686.8</t>
+          <t>20139.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>11202.7</t>
+          <t>11594.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>8102.12</t>
+          <t>7648.36</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1002.520030170422</t>
+          <t>1070.358956124564</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>2227.59</v>
+        <v>1443.47</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>390.0</t>
+          <t>426.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>75.73</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>91.82</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-120.78</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>83091.50144092219</t>
+          <t>82989.77697841727</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>18210.2</t>
+          <t>19686.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>10729.5</t>
+          <t>11202.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>8369.26</t>
+          <t>8102.12</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>779.7799219306776</t>
+          <t>1002.520030170422</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>2920.63</v>
+        <v>2227.59</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>23.15</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>23.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1498.0</t>
+          <t>390.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-124.37</t>
+          <t>-120.78</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>83091.50144092219</t>
+          <t>82989.77697841727</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>16891.0</t>
+          <t>18210.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>10195.3</t>
+          <t>10729.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>10437.66</t>
+          <t>8369.26</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>390.5343885617743</t>
+          <t>779.7799219306776</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>3886.84</v>
+        <v>2920.63</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1623.0</t>
+          <t>1498.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>65.67</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>61.41</t>
+          <t>86.42</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-127.21</t>
+          <t>-124.37</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>83091.50144092219</t>
+          <t>82989.77697841727</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>38343.0</t>
+          <t>36258.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>10310.4</t>
+          <t>16891.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>7058.7</t>
+          <t>10195.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>13160.96</t>
+          <t>10437.66</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-245.1581173895633</t>
+          <t>390.5343885617743</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>2237.72</v>
+        <v>3886.84</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>1623.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>61.41</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>26.72</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-129.03</t>
+          <t>-127.21</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>83091.50144092219</t>
+          <t>82989.77697841727</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>4524.0</t>
+          <t>38343.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>10310.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3638.9</t>
+          <t>7058.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>12810.66</t>
+          <t>13160.96</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-588</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-696.5912702806586</t>
+          <t>-245.1581173895633</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-421.47</v>
+        <v>2237.72</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-26.87</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-13.49</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,72 +3595,72 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-128.78</t>
+          <t>-129.03</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>83091.50144092219</t>
+          <t>82989.77697841727</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2647.0</t>
+          <t>4524.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>2718.6</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3717.5</t>
+          <t>3638.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>13031.08</t>
+          <t>12810.66</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-998</t>
+          <t>-588</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-746.6130345102762</t>
+          <t>-696.5912702806586</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-581.8099999999999</v>
+        <v>-421.47</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-16.93</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-15.70</t>
+          <t>-26.87</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-15.87</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,67 +4026,67 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>23.73</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-11.42</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-127.96</t>
+          <t>-128.78</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>83091.50144092219</t>
+          <t>82989.77697841727</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2683.0</t>
+          <t>2647.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>3248.8</t>
+          <t>2718.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>3717.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>13496.96</t>
+          <t>13031.08</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-605</t>
+          <t>-998</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-776.5779763001415</t>
+          <t>-746.6130345102762</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-588.97</v>
+        <v>-581.8099999999999</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-17.51</t>
+          <t>-16.93</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>9.98</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-13.67</t>
+          <t>-15.70</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-14.29</t>
+          <t>-15.87</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,17 +4457,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-14.16</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-126.97</t>
+          <t>-127.96</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>83091.50144092219</t>
+          <t>82989.77697841727</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>2683.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>3499.6</t>
+          <t>3248.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4053.7</t>
+          <t>3854.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>13799.2</t>
+          <t>13496.96</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-554</t>
+          <t>-605</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-810.6887149656693</t>
+          <t>-776.5779763001415</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-582.02</v>
+        <v>-588.97</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-15.95</t>
+          <t>-17.51</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-13.67</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-13.89</t>
+          <t>-14.29</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,67 +4888,67 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.77</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-16.06</t>
+          <t>-13.09</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-126.09</t>
+          <t>-126.97</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>83091.50144092219</t>
+          <t>82989.77697841727</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2041.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>3807.0</t>
+          <t>3499.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3998.4</t>
+          <t>4053.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>14454.38</t>
+          <t>13799.2</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-191</t>
+          <t>-554</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-852.264046081364</t>
+          <t>-810.6887149656693</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-623.3200000000001</v>
+        <v>-582.02</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-15.56</t>
+          <t>-15.95</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>-4.79</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-14.88</t>
+          <t>-13.89</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.52</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>21.77</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-20.05</t>
+          <t>-16.06</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-125.04</t>
+          <t>-126.09</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>83091.50144092219</t>
+          <t>82989.77697841727</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2867.0</t>
+          <t>2041.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>4227.8</t>
+          <t>3807.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4048.6</t>
+          <t>3998.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>16723.7</t>
+          <t>14454.38</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>-191</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-893.8907697781259</t>
+          <t>-852.264046081364</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-519.26</v>
+        <v>-623.3200000000001</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-16.54</t>
+          <t>-15.56</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>107.05</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>84.12</t>
+          <t>85.54</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/ITO導電玻璃.xlsx
+++ b/Result/checksun_type/ITO導電玻璃.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI12"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>-34.19</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-10.32</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,72 +1019,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>310</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>81.76</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>119.34</t>
+          <t>108.28</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,198 +1104,203 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>82989.77697841727</t>
+          <t>82885.7650862069</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>14123.0</t>
+          <t>8284.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>12216.7</t>
+          <t>12587.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>7629.54</t>
+          <t>7563.22</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>-4303</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1054.796642723689</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>969.2</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>973.0141484809627</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>523.2104301459694</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>7065</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>25.7</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/08/22</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-8.37</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>-12.06</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>-13.42998910113004</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-25.43417574544826</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>-6.333574654154932</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>107.05</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>102.73</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>19.70%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>-0.85%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>1547</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>安可-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>32.99</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 平面顯示器 - ITO導電基板** 觸控面板 - ITO導電玻璃** LED照明產業 - 藍寶石晶圓/晶片</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>293.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,84 +1334,84 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-4.2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.58</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>73.69</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1409,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,283 +1455,288 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>310</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>81.76</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
+          <t>23.49</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>22.46</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>23.57</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>119.34</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-110.67</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>82885.7650862069</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>14123.0</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>12216.7</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>7629.54</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>1054.796642723689</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>969.2039190188734</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>8262</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>-8.37</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-13.42998910113004</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-25.43417574544826</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>-6.333574654154932</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>102.73</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>19.70%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>83.58</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>1547</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>安可-光電業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>光電業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>23.45</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>24.05</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>23.55</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>22.43</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>23.42</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>92.50</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-113.86</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>82989.77697841727</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>20139.2</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>11594.6</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>7648.36</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>8544</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>1070.358956124564</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>1443.47</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-10.51</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>-13.42998910113004</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-25.43417574544826</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>-6.333574654154932</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>107.05</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>19.70%</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>-0.85%</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>1612</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>安可-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>光電業平上櫃</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>32.99</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 平面顯示器 - ITO導電基板** 觸控面板 - ITO導電玻璃** LED照明產業 - 藍寶石晶圓/晶片</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>426.0</t>
+          <t>293.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>75.73</t>
+          <t>73.69</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,72 +1891,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>310</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>91.82</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>22.43</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>87.14</t>
+          <t>92.50</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-113.86</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,198 +1976,203 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>82989.77697841727</t>
+          <t>82885.7650862069</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>19686.8</t>
+          <t>20139.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>11202.7</t>
+          <t>11594.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>8102.12</t>
+          <t>7648.36</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1002.520030170422</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>2227.59</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>1070.358956124564</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>1443.473048872349</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>6786</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>25.7</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/08/22</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>-8.37</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>-10.51</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-13.42998910113004</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-25.43417574544826</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>-6.333574654154932</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>107.05</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>102.73</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>19.70%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>-0.85%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>1547</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>安可-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>23.8</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>32.99</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 平面顯示器 - ITO導電基板** 觸控面板 - ITO導電玻璃** LED照明產業 - 藍寶石晶圓/晶片</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>390.0</t>
+          <t>426.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-4.2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>75.73</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,72 +2327,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>310</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>91.82</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-120.78</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,198 +2412,203 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>82989.77697841727</t>
+          <t>82885.7650862069</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>18210.2</t>
+          <t>19686.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>10729.5</t>
+          <t>11202.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>8369.26</t>
+          <t>8102.12</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>779.7799219306776</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>2920.63</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>1002.520030170422</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>2227.590625489014</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>10030</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>25.7</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/08/22</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-7.39</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>-8.37</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-13.42998910113004</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-25.43417574544826</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>-6.333574654154932</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>107.05</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>102.73</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>19.70%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>-0.85%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>1547</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>安可-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>23.8</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>24.35</t>
-        </is>
-      </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>23.15</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>23.55</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>23.8</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>32.99</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 平面顯示器 - ITO導電基板** 觸控面板 - ITO導電玻璃** LED照明產業 - 藍寶石晶圓/晶片</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1498.0</t>
+          <t>390.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,72 +2763,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>310</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-124.37</t>
+          <t>-120.78</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,198 +2848,203 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>82989.77697841727</t>
+          <t>82885.7650862069</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>16891.0</t>
+          <t>18210.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>10195.3</t>
+          <t>10729.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>10437.66</t>
+          <t>8369.26</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>390.5343885617743</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>3886.84</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>779.7799219306776</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>2920.630355459645</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>9279</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>25.7</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/08/22</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-8.37</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>-7.39</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-13.42998910113004</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-25.43417574544826</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>-6.333574654154932</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>107.05</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>102.73</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>19.70%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>-0.85%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>1547</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>安可-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>23.85</t>
-        </is>
-      </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>24.35</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>23.55</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>32.99</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 平面顯示器 - ITO導電基板** 觸控面板 - ITO導電玻璃** LED照明產業 - 藍寶石晶圓/晶片</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1623.0</t>
+          <t>1498.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-4.2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>65.67</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,72 +3199,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>310</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>61.41</t>
+          <t>86.42</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-127.21</t>
+          <t>-124.37</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,198 +3284,203 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>82989.77697841727</t>
+          <t>82885.7650862069</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>38343.0</t>
+          <t>36258.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>10310.4</t>
+          <t>16891.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>7058.7</t>
+          <t>10195.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>13160.96</t>
+          <t>10437.66</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-245.1581173895633</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>2237.72</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>390.5343885617743</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>3886.843171294131</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>36258</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>25.7</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/08/22</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>-7.20</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>-8.37</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-13.42998910113004</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-25.43417574544826</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>-6.333574654154932</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>107.05</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>102.73</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>19.70%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>-0.85%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>1547</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>安可-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>32.99</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 平面顯示器 - ITO導電基板** 觸控面板 - ITO導電玻璃** LED照明產業 - 藍寶石晶圓/晶片</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>1623.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>-5.53</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,72 +3635,72 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>310</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>61.41</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>26.72</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-129.03</t>
+          <t>-127.21</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,198 +3720,203 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>82989.77697841727</t>
+          <t>82885.7650862069</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4524.0</t>
+          <t>38343.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>10310.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3638.9</t>
+          <t>7058.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>12810.66</t>
+          <t>13160.96</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-588</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-696.5912702806586</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-421.47</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-245.1581173895633</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>2237.724223511461</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>38343</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>25.7</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/08/22</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>-15.18</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>-7.20</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-13.42998910113004</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-25.43417574544826</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>-6.333574654154932</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>107.05</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>102.73</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>19.70%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>-0.85%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>1547</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>安可-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>23.85</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>32.99</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 平面顯示器 - ITO導電基板** 觸控面板 - ITO導電玻璃** LED照明產業 - 藍寶石晶圓/晶片</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-26.87</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-13.49</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,67 +4071,67 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>310</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-128.78</t>
+          <t>-129.03</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,180 +4156,180 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>82989.77697841727</t>
+          <t>82885.7650862069</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2647.0</t>
+          <t>4524.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>2718.6</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3717.5</t>
+          <t>3638.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>13031.08</t>
+          <t>12810.66</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-998</t>
+          <t>-588</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-746.6130345102762</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-581.8099999999999</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-696.5912702806586</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-421.4715670177616</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>4524</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>25.7</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/08/22</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-16.93</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>-15.18</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-13.42998910113004</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-25.43417574544826</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>-6.333574654154932</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>107.05</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>102.73</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>19.70%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>-0.85%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>1547</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>安可-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4299,15 +4339,20 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>21.8</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>32.99</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 平面顯示器 - ITO導電基板** 觸控面板 - ITO導電玻璃** LED照明產業 - 藍寶石晶圓/晶片</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-15.70</t>
+          <t>-26.87</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-15.87</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,62 +4507,62 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>310</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>23.73</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-11.42</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4527,7 +4572,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-127.96</t>
+          <t>-128.78</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,198 +4592,203 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>82989.77697841727</t>
+          <t>82885.7650862069</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2683.0</t>
+          <t>2647.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>3248.8</t>
+          <t>2718.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>3717.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>13496.96</t>
+          <t>13031.08</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-605</t>
+          <t>-998</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-776.5779763001415</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-588.97</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-746.6130345102762</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-581.8058546660172</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>2647</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>25.7</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/08/22</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-17.51</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>-16.93</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-13.42998910113004</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-25.43417574544826</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>-6.333574654154932</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>107.05</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
+          <t>102.73</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
           <t>19.70%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>-0.85%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>1547</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>安可-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>32.99</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 平面顯示器 - ITO導電基板** 觸控面板 - ITO導電玻璃** LED照明產業 - 藍寶石晶圓/晶片</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-13.67</t>
+          <t>-15.70</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-14.29</t>
+          <t>-15.87</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,12 +4943,12 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>310</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4908,57 +4958,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-14.16</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-126.97</t>
+          <t>-127.96</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,175 +5028,175 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>82989.77697841727</t>
+          <t>82885.7650862069</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>2683.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>3499.6</t>
+          <t>3248.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4053.7</t>
+          <t>3854.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>13799.2</t>
+          <t>13496.96</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-554</t>
+          <t>-605</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-810.6887149656693</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-582.02</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-776.5779763001415</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-588.9689136397383</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>2683</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>25.7</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/08/22</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-15.95</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>-17.51</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-13.42998910113004</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-25.43417574544826</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>-6.333574654154932</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>107.05</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>102.73</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>19.70%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>-0.85%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>1547</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>安可-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>21.6</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5156,20 +5206,25 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>21.2</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>32.99</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 平面顯示器 - ITO導電基板** 觸控面板 - ITO導電玻璃** LED照明產業 - 藍寶石晶圓/晶片</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>-13.67</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-13.89</t>
+          <t>-14.29</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,62 +5379,62 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>310</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>18.52</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.77</t>
+          <t>21.69</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>23.89</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-16.06</t>
+          <t>-13.09</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5389,7 +5444,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-126.09</t>
+          <t>-126.97</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,198 +5464,203 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>82989.77697841727</t>
+          <t>82885.7650862069</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2041.0</t>
+          <t>3355.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>3807.0</t>
+          <t>3499.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3998.4</t>
+          <t>4053.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>14454.38</t>
+          <t>13799.2</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-191</t>
+          <t>-554</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-852.264046081364</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-623.3200000000001</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-810.6887149656693</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-582.0243938293488</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>3355</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
           <t>25.7</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/08/22</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-15.56</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>-15.95</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-13.42998910113004</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-25.43417574544826</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>-6.333574654154932</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>107.05</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
+          <t>102.73</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
           <t>19.70%</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>-0.85%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>85.54</t>
-        </is>
-      </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>1547</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>安可-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>21.5</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>21.6</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>32.99</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 平面顯示器 - ITO導電基板** 觸控面板 - ITO導電玻璃** LED照明產業 - 藍寶石晶圓/晶片</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/ITO導電玻璃.xlsx
+++ b/Result/checksun_type/ITO導電玻璃.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-34.19</t>
+          <t>-41.51</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.32</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,72 +1019,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>64.93</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>108.28</t>
+          <t>115.43</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-106.52</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>82885.7650862069</t>
+          <t>82778.67073170732</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>8284.4</t>
+          <t>7527.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>12587.7</t>
+          <t>12868.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>7563.22</t>
+          <t>7378.32</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-4303</t>
+          <t>-5341</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>973.0141484809627</t>
+          <t>835.6442375117817</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>523.2104301459694</t>
+          <t>80.10972718128687</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>7065</v>
+        <v>5494</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-12.06</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>104.32</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.2</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>-34.19</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-10.32</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1455,72 +1455,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>81.76</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>119.34</t>
+          <t>108.28</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>82885.7650862069</t>
+          <t>82778.67073170732</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>14123.0</t>
+          <t>8284.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12216.7</t>
+          <t>12587.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>7629.54</t>
+          <t>7563.22</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>-4303</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1054.796642723689</t>
+          <t>973.0141484809627</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>969.2039190188734</t>
+          <t>523.2104301459694</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>8262</v>
+        <v>7065</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-12.06</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>104.32</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>293.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,84 +1770,84 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-2.61</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-2.69</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-1.77</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.58</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>73.69</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1891,275 +1891,275 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>81.76</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
+          <t>23.49</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>22.46</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>23.57</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>119.34</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-110.67</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>82778.67073170732</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>14123.0</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>12216.7</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>7629.54</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>1054.796642723689</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>969.2039190188734</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>8262</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>-8.37</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>-13.42998910113004</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-25.43417574544826</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>-6.333574654154932</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>104.32</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>19.70%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>84.96</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>1571</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>安可-光電業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>光電業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>23.45</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>24.05</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>22.43</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>23.42</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>92.50</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-113.86</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>82885.7650862069</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>20139.2</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>11594.6</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>7648.36</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>8544</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>1070.358956124564</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>1443.473048872349</t>
-        </is>
-      </c>
-      <c r="BD4" t="n">
-        <v>6786</v>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>-10.51</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>-13.42998910113004</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-25.43417574544826</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>-6.333574654154932</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>102.73</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>19.70%</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>-0.85%</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>83.58</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>1547</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>安可-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>光電業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>23.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>426.0</t>
+          <t>293.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.2</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>75.73</t>
+          <t>73.69</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2327,72 +2327,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>91.82</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>22.43</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>87.14</t>
+          <t>92.50</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-113.86</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>82885.7650862069</t>
+          <t>82778.67073170732</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>19686.8</t>
+          <t>20139.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>11202.7</t>
+          <t>11594.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>8102.12</t>
+          <t>7648.36</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1002.520030170422</t>
+          <t>1070.358956124564</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>2227.590625489014</t>
+          <t>1443.473048872349</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>10030</v>
+        <v>6786</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>104.32</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>390.0</t>
+          <t>426.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>75.73</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2763,72 +2763,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>91.82</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-120.78</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>82885.7650862069</t>
+          <t>82778.67073170732</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>18210.2</t>
+          <t>19686.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>10729.5</t>
+          <t>11202.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>8369.26</t>
+          <t>8102.12</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>779.7799219306776</t>
+          <t>1002.520030170422</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>2920.630355459645</t>
+          <t>2227.590625489014</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>9279</v>
+        <v>10030</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>104.32</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3021,17 +3021,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
+          <t>23.15</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>23.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1498.0</t>
+          <t>390.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.2</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3199,72 +3199,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-124.37</t>
+          <t>-120.78</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>82885.7650862069</t>
+          <t>82778.67073170732</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>16891.0</t>
+          <t>18210.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>10195.3</t>
+          <t>10729.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>10437.66</t>
+          <t>8369.26</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>390.5343885617743</t>
+          <t>779.7799219306776</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>3886.843171294131</t>
+          <t>2920.630355459645</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>36258</v>
+        <v>9279</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>104.32</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1623.0</t>
+          <t>1498.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.53</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>65.67</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3635,72 +3635,72 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>61.41</t>
+          <t>86.42</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-127.21</t>
+          <t>-124.37</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>82885.7650862069</t>
+          <t>82778.67073170732</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>38343.0</t>
+          <t>36258.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>10310.4</t>
+          <t>16891.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7058.7</t>
+          <t>10195.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>13160.96</t>
+          <t>10437.66</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-245.1581173895633</t>
+          <t>390.5343885617743</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>2237.724223511461</t>
+          <t>3886.843171294131</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>38343</v>
+        <v>36258</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>104.32</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>1623.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4071,72 +4071,72 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>61.41</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>26.72</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-129.03</t>
+          <t>-127.21</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>82885.7650862069</t>
+          <t>82778.67073170732</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4524.0</t>
+          <t>38343.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>10310.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3638.9</t>
+          <t>7058.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>12810.66</t>
+          <t>13160.96</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-588</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-696.5912702806586</t>
+          <t>-245.1581173895633</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-421.4715670177616</t>
+          <t>2237.724223511461</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>4524</v>
+        <v>38343</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>104.32</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-26.87</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-13.49</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4507,67 +4507,67 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-128.78</t>
+          <t>-129.03</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>82885.7650862069</t>
+          <t>82778.67073170732</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2647.0</t>
+          <t>4524.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>2718.6</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>3717.5</t>
+          <t>3638.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>13031.08</t>
+          <t>12810.66</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-998</t>
+          <t>-588</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-746.6130345102762</t>
+          <t>-696.5912702806586</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-581.8058546660172</t>
+          <t>-421.4715670177616</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>2647</v>
+        <v>4524</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-16.93</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>104.32</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-15.70</t>
+          <t>-26.87</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-15.87</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4943,62 +4943,62 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>23.73</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-11.42</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-127.96</t>
+          <t>-128.78</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>82885.7650862069</t>
+          <t>82778.67073170732</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2683.0</t>
+          <t>2647.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>3248.8</t>
+          <t>2718.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>3717.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>13496.96</t>
+          <t>13031.08</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-605</t>
+          <t>-998</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-776.5779763001415</t>
+          <t>-746.6130345102762</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-588.9689136397383</t>
+          <t>-581.8058546660172</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>2683</v>
+        <v>2647</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-17.51</t>
+          <t>-16.93</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>104.32</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5201,17 +5201,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-13.67</t>
+          <t>-15.70</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-14.29</t>
+          <t>-15.87</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>240</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5394,57 +5394,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.68</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.69</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-14.16</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-126.97</t>
+          <t>-127.96</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>82885.7650862069</t>
+          <t>82778.67073170732</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3355.0</t>
+          <t>2683.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>3499.6</t>
+          <t>3248.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4053.7</t>
+          <t>3854.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>13799.2</t>
+          <t>13496.96</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-554</t>
+          <t>-605</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-810.6887149656693</t>
+          <t>-776.5779763001415</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-582.0243938293488</t>
+          <t>-588.9689136397383</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>3355</v>
+        <v>2683</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-15.95</t>
+          <t>-17.51</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>102.73</t>
+          <t>104.32</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>84.96</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO導電玻璃.xlsx
+++ b/Result/checksun_type/ITO導電玻璃.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-41.51</t>
+          <t>-51.37</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,72 +1019,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>23.61</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>115.43</t>
+          <t>160.83</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.52</t>
+          <t>-104.65</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>82778.67073170732</t>
+          <t>82668.7005730659</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>7527.4</t>
+          <t>6324.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>12868.8</t>
+          <t>13005.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>7378.32</t>
+          <t>7283.74</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-5341</t>
+          <t>-6681</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>835.6442375117817</t>
+          <t>654.2930458832735</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>80.10972718128687</t>
+          <t>-343.1385080735217</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>5494</v>
+        <v>4013</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-10.70</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-34.19</t>
+          <t>-41.51</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.32</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1455,72 +1455,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>64.93</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>108.28</t>
+          <t>115.43</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-106.52</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>82778.67073170732</t>
+          <t>82668.7005730659</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>8284.4</t>
+          <t>7527.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12587.7</t>
+          <t>12868.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>7563.22</t>
+          <t>7378.32</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-4303</t>
+          <t>-5341</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>973.0141484809627</t>
+          <t>835.6442375117817</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>523.2104301459694</t>
+          <t>80.10972718128687</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>7065</v>
+        <v>5494</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-12.06</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>-34.19</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-10.32</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1891,72 +1891,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>81.76</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>119.34</t>
+          <t>108.28</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>82778.67073170732</t>
+          <t>82668.7005730659</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>14123.0</t>
+          <t>8284.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>12216.7</t>
+          <t>12587.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>7629.54</t>
+          <t>7563.22</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>-4303</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1054.796642723689</t>
+          <t>973.0141484809627</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>969.2039190188734</t>
+          <t>523.2104301459694</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>8262</v>
+        <v>7065</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-12.06</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>293.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,84 +2206,84 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-1.84</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-2.69</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>73.69</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2327,275 +2327,275 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>81.76</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
+          <t>23.49</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>22.46</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>23.57</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>119.34</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-110.67</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>82668.7005730659</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>14123.0</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>12216.7</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>7629.54</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>1054.796642723689</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>969.2039190188734</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>8262</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>-8.37</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>-13.42998910113004</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-25.43417574544826</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>-6.333574654154932</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>106.14</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>19.70%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>86.4</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>1599</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>安可-光電業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>光電業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>23.45</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>24.05</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>22.43</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>23.42</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>92.50</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-113.86</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>82778.67073170732</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>20139.2</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>11594.6</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>7648.36</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>8544</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>1070.358956124564</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>1443.473048872349</t>
-        </is>
-      </c>
-      <c r="BD5" t="n">
-        <v>6786</v>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>-10.51</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>-13.42998910113004</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>-25.43417574544826</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>-6.333574654154932</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>104.32</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>19.70%</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>-0.85%</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>84.96</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>1571</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>安可-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>光電業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>23.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>426.0</t>
+          <t>293.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>75.73</t>
+          <t>73.69</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2763,72 +2763,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>91.82</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>22.43</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>87.14</t>
+          <t>92.50</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-113.86</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>82778.67073170732</t>
+          <t>82668.7005730659</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>19686.8</t>
+          <t>20139.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>11202.7</t>
+          <t>11594.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>8102.12</t>
+          <t>7648.36</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>1002.520030170422</t>
+          <t>1070.358956124564</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>2227.590625489014</t>
+          <t>1443.473048872349</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>10030</v>
+        <v>6786</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>390.0</t>
+          <t>426.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>75.73</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3199,72 +3199,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>91.82</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-120.78</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>82778.67073170732</t>
+          <t>82668.7005730659</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>18210.2</t>
+          <t>19686.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>10729.5</t>
+          <t>11202.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>8369.26</t>
+          <t>8102.12</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>779.7799219306776</t>
+          <t>1002.520030170422</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>2920.630355459645</t>
+          <t>2227.590625489014</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>9279</v>
+        <v>10030</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3457,17 +3457,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
+          <t>23.15</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>23.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1498.0</t>
+          <t>390.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3635,72 +3635,72 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-124.37</t>
+          <t>-120.78</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>82778.67073170732</t>
+          <t>82668.7005730659</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>16891.0</t>
+          <t>18210.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>10195.3</t>
+          <t>10729.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>10437.66</t>
+          <t>8369.26</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>390.5343885617743</t>
+          <t>779.7799219306776</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>3886.843171294131</t>
+          <t>2920.630355459645</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>36258</v>
+        <v>9279</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1623.0</t>
+          <t>1498.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>65.67</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4071,72 +4071,72 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>61.41</t>
+          <t>86.42</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-127.21</t>
+          <t>-124.37</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>82778.67073170732</t>
+          <t>82668.7005730659</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>38343.0</t>
+          <t>36258.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>10310.4</t>
+          <t>16891.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>7058.7</t>
+          <t>10195.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>13160.96</t>
+          <t>10437.66</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-245.1581173895633</t>
+          <t>390.5343885617743</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>2237.724223511461</t>
+          <t>3886.843171294131</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>38343</v>
+        <v>36258</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>1623.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4507,72 +4507,72 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>61.41</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>26.72</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-129.03</t>
+          <t>-127.21</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>82778.67073170732</t>
+          <t>82668.7005730659</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4524.0</t>
+          <t>38343.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>10310.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>3638.9</t>
+          <t>7058.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>12810.66</t>
+          <t>13160.96</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-588</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-696.5912702806586</t>
+          <t>-245.1581173895633</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-421.4715670177616</t>
+          <t>2237.724223511461</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>4524</v>
+        <v>38343</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,22 +4695,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-26.87</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-13.49</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4943,67 +4943,67 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-128.78</t>
+          <t>-129.03</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>82778.67073170732</t>
+          <t>82668.7005730659</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2647.0</t>
+          <t>4524.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>2718.6</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3717.5</t>
+          <t>3638.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>13031.08</t>
+          <t>12810.66</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-998</t>
+          <t>-588</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-746.6130345102762</t>
+          <t>-696.5912702806586</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-581.8058546660172</t>
+          <t>-421.4715670177616</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>2647</v>
+        <v>4524</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-16.93</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-15.70</t>
+          <t>-26.87</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-15.87</t>
+          <t>-15.28</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5379,62 +5379,62 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.68</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>23.73</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-11.42</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-127.96</t>
+          <t>-128.78</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>82778.67073170732</t>
+          <t>82668.7005730659</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2683.0</t>
+          <t>2647.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>3248.8</t>
+          <t>2718.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3854.0</t>
+          <t>3717.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>13496.96</t>
+          <t>13031.08</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-605</t>
+          <t>-998</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-776.5779763001415</t>
+          <t>-746.6130345102762</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-588.9689136397383</t>
+          <t>-581.8058546660172</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>2683</v>
+        <v>2647</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-17.51</t>
+          <t>-16.93</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>84.96</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5637,17 +5637,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO導電玻璃.xlsx
+++ b/Result/checksun_type/ITO導電玻璃.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-51.37</t>
+          <t>-35.31</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,52 +1014,52 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>958</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1069,22 +1069,22 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.61</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>160.83</t>
+          <t>430.70</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-104.65</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>82668.7005730659</t>
+          <t>82600.4592274678</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>6324.0</t>
+          <t>9629.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>13005.4</t>
+          <t>14884.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>7283.74</t>
+          <t>7449.74</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-6681</t>
+          <t>-5255</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>654.2930458832735</t>
+          <t>679.2619911243006</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-343.1385080735217</t>
+          <t>816.5911899499497</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>4013</v>
+        <v>23312</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>109.77</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-41.51</t>
+          <t>-51.37</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>958</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>23.61</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>115.43</t>
+          <t>160.83</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.52</t>
+          <t>-104.65</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>82668.7005730659</t>
+          <t>82600.4592274678</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>7527.4</t>
+          <t>6324.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12868.8</t>
+          <t>13005.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>7378.32</t>
+          <t>7283.74</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-5341</t>
+          <t>-6681</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>835.6442375117817</t>
+          <t>654.2930458832735</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>80.10972718128687</t>
+          <t>-343.1385080735217</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>5494</v>
+        <v>4013</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-10.70</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>109.77</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-34.19</t>
+          <t>-41.51</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.32</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>958</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>64.93</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>108.28</t>
+          <t>115.43</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-106.52</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>82668.7005730659</t>
+          <t>82600.4592274678</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>8284.4</t>
+          <t>7527.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>12587.7</t>
+          <t>12868.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>7563.22</t>
+          <t>7378.32</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-4303</t>
+          <t>-5341</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>973.0141484809627</t>
+          <t>835.6442375117817</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>523.2104301459694</t>
+          <t>80.10972718128687</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>7065</v>
+        <v>5494</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-12.06</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>109.77</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>-34.19</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-10.32</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>958</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>81.76</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>119.34</t>
+          <t>108.28</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>82668.7005730659</t>
+          <t>82600.4592274678</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>14123.0</t>
+          <t>8284.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>12216.7</t>
+          <t>12587.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>7629.54</t>
+          <t>7563.22</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>-4303</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1054.796642723689</t>
+          <t>973.0141484809627</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>969.2039190188734</t>
+          <t>523.2104301459694</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>8262</v>
+        <v>7065</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-12.06</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>109.77</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>293.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,84 +2642,84 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-1.84</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>73.69</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,280 +2758,280 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>958</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>81.76</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
+          <t>23.49</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>22.46</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>23.57</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>119.34</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-110.67</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>82600.4592274678</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>14123.0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>12216.7</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>7629.54</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>1054.796642723689</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>969.2039190188734</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>8262</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>-8.37</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>-13.42998910113004</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-25.43417574544826</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>-6.333574654154932</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>109.77</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>19.70%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>89.09</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>1653</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>安可-光電業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>光電業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>23.45</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>24.05</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>22.43</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>23.42</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>92.50</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-113.86</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>82668.7005730659</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>20139.2</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>11594.6</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>7648.36</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>8544</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>1070.358956124564</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>1443.473048872349</t>
-        </is>
-      </c>
-      <c r="BD6" t="n">
-        <v>6786</v>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>-10.51</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>-13.42998910113004</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>-25.43417574544826</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>-6.333574654154932</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>106.14</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>19.70%</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>-0.85%</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>86.4</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>1599</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>安可-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>光電業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>23.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>426.0</t>
+          <t>293.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>75.73</t>
+          <t>73.69</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>958</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>91.82</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>22.43</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>87.14</t>
+          <t>92.50</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-113.86</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>82668.7005730659</t>
+          <t>82600.4592274678</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19686.8</t>
+          <t>20139.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>11202.7</t>
+          <t>11594.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>8102.12</t>
+          <t>7648.36</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1002.520030170422</t>
+          <t>1070.358956124564</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>2227.590625489014</t>
+          <t>1443.473048872349</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>10030</v>
+        <v>6786</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>109.77</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>390.0</t>
+          <t>426.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>75.73</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>958</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>91.82</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-120.78</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>82668.7005730659</t>
+          <t>82600.4592274678</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>18210.2</t>
+          <t>19686.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>10729.5</t>
+          <t>11202.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>8369.26</t>
+          <t>8102.12</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>779.7799219306776</t>
+          <t>1002.520030170422</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>2920.630355459645</t>
+          <t>2227.590625489014</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>9279</v>
+        <v>10030</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>109.77</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3893,17 +3893,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
+          <t>23.15</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>23.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1498.0</t>
+          <t>390.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>958</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>22.38</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-124.37</t>
+          <t>-120.78</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>82668.7005730659</t>
+          <t>82600.4592274678</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>16891.0</t>
+          <t>18210.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>10195.3</t>
+          <t>10729.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>10437.66</t>
+          <t>8369.26</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>390.5343885617743</t>
+          <t>779.7799219306776</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>3886.843171294131</t>
+          <t>2920.630355459645</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>36258</v>
+        <v>9279</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>109.77</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1623.0</t>
+          <t>1498.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>65.67</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>958</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>61.41</t>
+          <t>86.42</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-127.21</t>
+          <t>-124.37</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>82668.7005730659</t>
+          <t>82600.4592274678</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>38343.0</t>
+          <t>36258.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>10310.4</t>
+          <t>16891.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7058.7</t>
+          <t>10195.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>13160.96</t>
+          <t>10437.66</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-245.1581173895633</t>
+          <t>390.5343885617743</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>2237.724223511461</t>
+          <t>3886.843171294131</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>38343</v>
+        <v>36258</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>109.77</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>1623.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>958</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>61.41</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.62</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>23.48</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>26.72</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-129.03</t>
+          <t>-127.21</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>82668.7005730659</t>
+          <t>82600.4592274678</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4524.0</t>
+          <t>38343.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>10310.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3638.9</t>
+          <t>7058.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>12810.66</t>
+          <t>13160.96</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-588</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-696.5912702806586</t>
+          <t>-245.1581173895633</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-421.4715670177616</t>
+          <t>2237.724223511461</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>4524</v>
+        <v>38343</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-15.18</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>109.77</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>208.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-26.87</t>
+          <t>-16.18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-13.49</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,72 +5374,72 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>958</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>8.55</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.53</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.23</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-11.42</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-128.78</t>
+          <t>-129.03</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>82668.7005730659</t>
+          <t>82600.4592274678</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2647.0</t>
+          <t>4524.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2718.6</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3717.5</t>
+          <t>3638.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>13031.08</t>
+          <t>12810.66</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-998</t>
+          <t>-588</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-746.6130345102762</t>
+          <t>-696.5912702806586</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-581.8058546660172</t>
+          <t>-421.4715670177616</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>2647</v>
+        <v>4524</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-16.93</t>
+          <t>-15.18</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>109.77</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO導電玻璃.xlsx
+++ b/Result/checksun_type/ITO導電玻璃.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>23.32</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>22.57</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>23.26</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>22.57</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>23.26</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>23312.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>9629.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>9629.200000000001</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>14884.2</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>7449.74</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>7449.74</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>816.5911899499497</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>23312</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>23312.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>23.09</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>22.5</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>23.26</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>23.26</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>4013.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>6324.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>6324</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>13005.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>7283.74</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>7283.74</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-343.1385080735217</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>4013</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>4013.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>23.13</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>22.46</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>23.28</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>23.28</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>5494.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>7527.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>7527.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>12868.8</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>7378.32</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>7378.32</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>80.10972718128687</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>5494</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>5494.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>23.3</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>22.45</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>23.33</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>23.33</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>7065.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>8284.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>8284.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>12587.7</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>7563.22</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>7563.22</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>523.2104301459694</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>7065</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>7065.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>23.49</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>22.46</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>23.38</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>23.38</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>8262.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>14123.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>14123</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>12216.7</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>7629.54</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>7629.54</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>969.2039190188734</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>8262</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>23.55</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>22.43</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>23.42</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>23.42</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>6786.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>20139.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>20139.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>11594.6</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>7648.36</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>7648.36</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>1443.473048872349</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>6786</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>6786.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>23.31</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>22.42</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>23.46</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>22.42</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>23.46</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>10030.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>19686.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>19686.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>11202.7</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>8102.12</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>8102.12</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>2227.590625489014</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>10030</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>10030.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>22.87</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>22.38</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>23.5</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>9279.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>18210.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>18210.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>10729.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>8369.26</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>8369.26</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>2920.630355459645</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>9279</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>9279.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>22.35</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>22.34</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>23.54</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>22.34</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>23.54</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>36258.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>16891.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>16891</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>10195.3</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>10437.66</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>10437.66</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>3886.843171294131</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>36258</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>36258.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>21.96</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>22.29</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>23.62</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>23.62</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>38343.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>10310.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>10310.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>7058.7</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>13160.96</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>13160.96</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>2237.724223511461</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>38343</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>38343.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>21.53</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>22.23</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>23.66</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>23.66</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>4524.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>3050.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>3050</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>3638.9</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>12810.66</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>12810.66</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-421.4715670177616</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>4524</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>4524.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>

--- a/Result/checksun_type/ITO導電玻璃.xlsx
+++ b/Result/checksun_type/ITO導電玻璃.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>361.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-35.31</t>
+          <t>-18.48</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>361</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>72.03</t>
+          <t>82.37</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>22.57</v>
+        <v>22.66</v>
       </c>
       <c r="AN2" t="n">
         <v>23.26</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>430.70</t>
+          <t>4280.47</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-99.77</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>82600.4592274678</t>
+          <t>82501.10142857143</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>9629.200000000001</v>
+        <v>9716.799999999999</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>14884.2</t>
+          <t>11919.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>7449.74</v>
+        <v>7436.54</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-5255</t>
+          <t>-2203</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>679.2619911243006</t>
+          <t>653.54279230789</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>816.5911899499497</t>
+          <t>512.0871988176314</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>109.77</t>
+          <t>108.86</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-51.37</t>
+          <t>-35.31</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>361</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>22.5</v>
+        <v>22.57</v>
       </c>
       <c r="AN3" t="n">
         <v>23.26</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.61</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>160.83</t>
+          <t>430.70</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.65</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>82600.4592274678</t>
+          <t>82501.10142857143</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>6324</v>
+        <v>9629.200000000001</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>13005.4</t>
+          <t>14884.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>7283.74</v>
+        <v>7449.74</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-6681</t>
+          <t>-5255</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>654.2930458832735</t>
+          <t>679.2619911243006</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-343.1385080735217</t>
+          <t>816.5911899499497</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>109.77</t>
+          <t>108.86</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-41.51</t>
+          <t>-51.37</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>361</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>22.46</v>
+        <v>22.5</v>
       </c>
       <c r="AN4" t="n">
-        <v>23.28</v>
+        <v>23.26</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>23.61</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>115.43</t>
+          <t>160.83</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.52</t>
+          <t>-104.65</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>82600.4592274678</t>
+          <t>82501.10142857143</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>7527.4</v>
+        <v>6324</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>12868.8</t>
+          <t>13005.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>7378.32</v>
+        <v>7283.74</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-5341</t>
+          <t>-6681</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>835.6442375117817</t>
+          <t>654.2930458832735</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>80.10972718128687</t>
+          <t>-343.1385080735217</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-10.70</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>109.77</t>
+          <t>108.86</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-34.19</t>
+          <t>-41.51</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.32</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>361</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>64.93</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>22.45</v>
+        <v>22.46</v>
       </c>
       <c r="AN5" t="n">
-        <v>23.33</v>
+        <v>23.28</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>108.28</t>
+          <t>115.43</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-106.52</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>82600.4592274678</t>
+          <t>82501.10142857143</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>8284.4</v>
+        <v>7527.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>12587.7</t>
+          <t>12868.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>7563.22</v>
+        <v>7378.32</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-4303</t>
+          <t>-5341</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>973.0141484809627</t>
+          <t>835.6442375117817</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>523.2104301459694</t>
+          <t>80.10972718128687</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-12.06</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>109.77</t>
+          <t>108.86</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>-34.19</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-10.32</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>361</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>81.76</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>22.46</v>
+        <v>22.45</v>
       </c>
       <c r="AN6" t="n">
-        <v>23.38</v>
+        <v>23.33</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>119.34</t>
+          <t>108.28</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>82600.4592274678</t>
+          <t>82501.10142857143</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>14123</v>
+        <v>8284.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>12216.7</t>
+          <t>12587.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>7629.54</v>
+        <v>7563.22</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>-4303</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>1054.796642723689</t>
+          <t>973.0141484809627</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>969.2039190188734</t>
+          <t>523.2104301459694</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-12.06</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>109.77</t>
+          <t>108.86</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>293.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,84 +3048,84 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>4.76</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>73.69</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,274 +3164,274 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>361</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>81.76</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
+          <t>23.49</t>
+        </is>
+      </c>
+      <c r="AM7" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>23.57</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>119.34</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-110.67</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>82501.10142857143</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>14123</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>12216.7</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>7629.54</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>1054.796642723689</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>969.2039190188734</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>-8.37</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>-13.42998910113004</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>-25.43417574544826</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>-6.333574654154932</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>108.86</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>19.70%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>89.61</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>1640</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>安可-光電業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>光電業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>23.45</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>24.05</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="AM7" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>23.42</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>92.50</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-113.86</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>82600.4592274678</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="n">
-        <v>20139.2</v>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>11594.6</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>7648.36</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>8544</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>1070.358956124564</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>1443.473048872349</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>-10.51</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>-13.42998910113004</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>-25.43417574544826</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>-6.333574654154932</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>109.77</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>19.70%</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>-0.85%</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>89.09</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>1653</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>安可-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>光電業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>23.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>426.0</t>
+          <t>293.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>75.73</t>
+          <t>73.69</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>361</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>91.82</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>22.42</v>
+        <v>22.43</v>
       </c>
       <c r="AN8" t="n">
-        <v>23.46</v>
+        <v>23.42</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>87.14</t>
+          <t>92.50</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-113.86</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>82600.4592274678</t>
+          <t>82501.10142857143</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>19686.8</v>
+        <v>20139.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>11202.7</t>
+          <t>11594.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>8102.12</v>
+        <v>7648.36</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1002.520030170422</t>
+          <t>1070.358956124564</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>2227.590625489014</t>
+          <t>1443.473048872349</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>109.77</t>
+          <t>108.86</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>390.0</t>
+          <t>426.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>75.73</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>361</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>91.82</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>22.38</v>
+        <v>22.42</v>
       </c>
       <c r="AN9" t="n">
-        <v>23.5</v>
+        <v>23.46</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-120.78</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>82600.4592274678</t>
+          <t>82501.10142857143</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>18210.2</v>
+        <v>19686.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>10729.5</t>
+          <t>11202.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>8369.26</v>
+        <v>8102.12</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>779.7799219306776</t>
+          <t>1002.520030170422</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>2920.630355459645</t>
+          <t>2227.590625489014</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>109.77</t>
+          <t>108.86</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4281,17 +4281,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
+          <t>23.15</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>23.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1498.0</t>
+          <t>390.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>361</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>22.34</v>
+        <v>22.38</v>
       </c>
       <c r="AN10" t="n">
-        <v>23.54</v>
+        <v>23.5</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-124.37</t>
+          <t>-120.78</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>82600.4592274678</t>
+          <t>82501.10142857143</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>16891</v>
+        <v>18210.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>10195.3</t>
+          <t>10729.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>10437.66</v>
+        <v>8369.26</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>390.5343885617743</t>
+          <t>779.7799219306776</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>3886.843171294131</t>
+          <t>2920.630355459645</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>109.77</t>
+          <t>108.86</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1623.0</t>
+          <t>1498.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>65.67</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>361</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>61.41</t>
+          <t>86.42</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>22.29</v>
+        <v>22.34</v>
       </c>
       <c r="AN11" t="n">
-        <v>23.62</v>
+        <v>23.54</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-127.21</t>
+          <t>-124.37</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>82600.4592274678</t>
+          <t>82501.10142857143</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>38343.0</t>
+          <t>36258.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>10310.4</v>
+        <v>16891</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>7058.7</t>
+          <t>10195.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>13160.96</v>
+        <v>10437.66</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-245.1581173895633</t>
+          <t>390.5343885617743</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>2237.724223511461</t>
+          <t>3886.843171294131</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>38343.0</t>
+          <t>36258.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>109.77</t>
+          <t>108.86</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>1623.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-16.18</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-13.49</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,211 +5314,211 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>361</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>61.41</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
+          <t>8.61</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>-1.49</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>-5.64</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>21.96</t>
+        </is>
+      </c>
+      <c r="AM12" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>23.48</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>26.72</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>-0.40</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-127.21</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>82501.10142857143</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>38343.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="n">
+        <v>10310.4</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>7058.7</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>13160.96</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>3251</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-245.1581173895633</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>2237.724223511461</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>38343.0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>-7.20</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-13.42998910113004</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>-25.43417574544826</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-6.333574654154932</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-3.14</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>-6.03</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>21.53</t>
-        </is>
-      </c>
-      <c r="AM12" t="n">
-        <v>22.23</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>23.66</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>23.47</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-3.44</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.60</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.58</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-129.03</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>82600.4592274678</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>4524.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="n">
-        <v>3050</v>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>3638.9</t>
-        </is>
-      </c>
-      <c r="AZ12" t="n">
-        <v>12810.66</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>-588</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-696.5912702806586</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>-421.4715670177616</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>4524.0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>-15.18</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>-13.42998910113004</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>-25.43417574544826</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>-6.333574654154932</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
       <c r="BU12" t="inlineStr">
         <is>
           <t>3.47</t>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>109.77</t>
+          <t>108.86</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.61</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO導電玻璃.xlsx
+++ b/Result/checksun_type/ITO導電玻璃.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>361.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,79 +898,79 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-1.15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>6.64</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>23.95</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-18.48</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>77.42</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>82.37</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>22.66</v>
+        <v>22.74</v>
       </c>
       <c r="AN2" t="n">
         <v>23.26</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>4280.47</t>
+          <t>362.90</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-99.77</t>
+          <t>-97.51</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>82501.10142857143</t>
+          <t>82395.80670470756</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>9716.799999999999</v>
+        <v>9462.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>11919.9</t>
+          <t>8873.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>7436.54</v>
+        <v>7472.64</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2203</t>
+          <t>589</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>653.54279230789</t>
+          <t>563.475781961225</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>512.0871988176314</t>
+          <t>68.1072250545676</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>108.86</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>24.05</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>24.45</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>361.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-35.31</t>
+          <t>-18.48</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>72.03</t>
+          <t>82.37</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>22.57</v>
+        <v>22.66</v>
       </c>
       <c r="AN3" t="n">
         <v>23.26</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>430.70</t>
+          <t>4280.47</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-99.77</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>82501.10142857143</t>
+          <t>82395.80670470756</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>9629.200000000001</v>
+        <v>9716.799999999999</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>14884.2</t>
+          <t>11919.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>7449.74</v>
+        <v>7436.54</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-5255</t>
+          <t>-2203</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>679.2619911243006</t>
+          <t>653.54279230789</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>816.5911899499497</t>
+          <t>512.0871988176314</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>108.86</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-51.37</t>
+          <t>-35.31</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>22.5</v>
+        <v>22.57</v>
       </c>
       <c r="AN4" t="n">
         <v>23.26</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.61</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>160.83</t>
+          <t>430.70</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.65</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>82501.10142857143</t>
+          <t>82395.80670470756</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>6324</v>
+        <v>9629.200000000001</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>13005.4</t>
+          <t>14884.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>7283.74</v>
+        <v>7449.74</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-6681</t>
+          <t>-5255</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>654.2930458832735</t>
+          <t>679.2619911243006</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-343.1385080735217</t>
+          <t>816.5911899499497</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>108.86</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-41.51</t>
+          <t>-51.37</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>22.46</v>
+        <v>22.5</v>
       </c>
       <c r="AN5" t="n">
-        <v>23.28</v>
+        <v>23.26</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>23.61</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>115.43</t>
+          <t>160.83</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.52</t>
+          <t>-104.65</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>82501.10142857143</t>
+          <t>82395.80670470756</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>7527.4</v>
+        <v>6324</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>12868.8</t>
+          <t>13005.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>7378.32</v>
+        <v>7283.74</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-5341</t>
+          <t>-6681</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>835.6442375117817</t>
+          <t>654.2930458832735</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>80.10972718128687</t>
+          <t>-343.1385080735217</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-10.70</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>108.86</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-34.19</t>
+          <t>-41.51</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.32</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>64.93</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>22.45</v>
+        <v>22.46</v>
       </c>
       <c r="AN6" t="n">
-        <v>23.33</v>
+        <v>23.28</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>108.28</t>
+          <t>115.43</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-106.52</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>82501.10142857143</t>
+          <t>82395.80670470756</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>8284.4</v>
+        <v>7527.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>12587.7</t>
+          <t>12868.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>7563.22</v>
+        <v>7378.32</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-4303</t>
+          <t>-5341</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>973.0141484809627</t>
+          <t>835.6442375117817</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>523.2104301459694</t>
+          <t>80.10972718128687</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-12.06</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>108.86</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>-34.19</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-10.32</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>81.76</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>22.46</v>
+        <v>22.45</v>
       </c>
       <c r="AN7" t="n">
-        <v>23.38</v>
+        <v>23.33</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>119.34</t>
+          <t>108.28</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>82501.10142857143</t>
+          <t>82395.80670470756</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>14123</v>
+        <v>8284.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>12216.7</t>
+          <t>12587.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>7629.54</v>
+        <v>7563.22</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>-4303</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1054.796642723689</t>
+          <t>973.0141484809627</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>969.2039190188734</t>
+          <t>523.2104301459694</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-12.06</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>108.86</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>293.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,84 +3478,84 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-1.15</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>3.97</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>73.69</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,274 +3594,274 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>81.76</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>23.49</t>
+        </is>
+      </c>
+      <c r="AM8" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>23.57</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>119.34</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-110.67</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>82395.80670470756</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>14123</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>12216.7</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>7629.54</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>1054.796642723689</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>969.2039190188734</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>-8.37</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-13.42998910113004</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-25.43417574544826</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>-6.333574654154932</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>108.18</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>19.70%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>89.32</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>1630</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>安可-光電業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>光電業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>23.45</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>24.05</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="AM8" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>23.42</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>92.50</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-113.86</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>82501.10142857143</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="n">
-        <v>20139.2</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>11594.6</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>7648.36</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>8544</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>1070.358956124564</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>1443.473048872349</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>-10.51</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>-13.42998910113004</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>-25.43417574544826</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>-6.333574654154932</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>108.86</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>19.70%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>-0.85%</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>89.61</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>1640</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>安可-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>光電業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>23.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>426.0</t>
+          <t>293.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>75.73</t>
+          <t>73.69</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>91.82</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>22.42</v>
+        <v>22.43</v>
       </c>
       <c r="AN9" t="n">
-        <v>23.46</v>
+        <v>23.42</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>87.14</t>
+          <t>92.50</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-113.86</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>82501.10142857143</t>
+          <t>82395.80670470756</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>19686.8</v>
+        <v>20139.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>11202.7</t>
+          <t>11594.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>8102.12</v>
+        <v>7648.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1002.520030170422</t>
+          <t>1070.358956124564</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>2227.590625489014</t>
+          <t>1443.473048872349</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>108.86</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,42 +4323,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>-1.05</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>426.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>1.05</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>390.0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>23.8</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>75.73</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>91.82</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>22.38</v>
+        <v>22.42</v>
       </c>
       <c r="AN10" t="n">
-        <v>23.5</v>
+        <v>23.46</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-120.78</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>82501.10142857143</t>
+          <t>82395.80670470756</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>18210.2</v>
+        <v>19686.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>10729.5</t>
+          <t>11202.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>8369.26</v>
+        <v>8102.12</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>779.7799219306776</t>
+          <t>1002.520030170422</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>2920.630355459645</t>
+          <t>2227.590625489014</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>108.86</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
+          <t>23.15</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>23.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1498.0</t>
+          <t>390.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>22.34</v>
+        <v>22.38</v>
       </c>
       <c r="AN11" t="n">
-        <v>23.54</v>
+        <v>23.5</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-124.37</t>
+          <t>-120.78</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>82501.10142857143</t>
+          <t>82395.80670470756</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>16891</v>
+        <v>18210.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>10195.3</t>
+          <t>10729.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>10437.66</v>
+        <v>8369.26</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>390.5343885617743</t>
+          <t>779.7799219306776</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>3886.843171294131</t>
+          <t>2920.630355459645</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>108.86</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1623.0</t>
+          <t>1498.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>65.67</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>61.41</t>
+          <t>86.42</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.11</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>22.29</v>
+        <v>22.34</v>
       </c>
       <c r="AN12" t="n">
-        <v>23.62</v>
+        <v>23.54</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.48</t>
+          <t>23.49</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>26.72</t>
+          <t>46.64</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-127.21</t>
+          <t>-124.37</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>82501.10142857143</t>
+          <t>82395.80670470756</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>38343.0</t>
+          <t>36258.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>10310.4</v>
+        <v>16891</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7058.7</t>
+          <t>10195.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>13160.96</v>
+        <v>10437.66</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-245.1581173895633</t>
+          <t>390.5343885617743</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>2237.724223511461</t>
+          <t>3886.843171294131</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>38343.0</t>
+          <t>36258.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-7.20</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>108.86</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.61</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO導電玻璃.xlsx
+++ b/Result/checksun_type/ITO導電玻璃.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>77.42</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>88.17</t>
+          <t>68.82</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>22.74</v>
+        <v>22.8</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.26</v>
+        <v>23.25</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>362.90</t>
+          <t>154.33</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-97.51</t>
+          <t>-95.95</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>82395.80670470756</t>
+          <t>82288.22863247864</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>9462.4</v>
+        <v>9280.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>8873.4</t>
+          <t>8403.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>7472.64</v>
+        <v>7418.64</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>876</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>563.475781961225</t>
+          <t>425.2400559355071</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>68.1072250545676</t>
+          <t>-335.0564372059416</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>105.68</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>361.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,79 +1328,79 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-2.37</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6.64</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>23.95</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-0.63</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-18.48</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>77.42</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>82.37</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>22.66</v>
+        <v>22.74</v>
       </c>
       <c r="AN3" t="n">
         <v>23.26</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>4280.47</t>
+          <t>362.90</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-99.77</t>
+          <t>-97.51</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>82395.80670470756</t>
+          <t>82288.22863247864</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>9716.799999999999</v>
+        <v>9462.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>11919.9</t>
+          <t>8873.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>7436.54</v>
+        <v>7472.64</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2203</t>
+          <t>589</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>653.54279230789</t>
+          <t>563.475781961225</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>512.0871988176314</t>
+          <t>68.1072250545676</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>105.68</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>24.05</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>24.45</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>361.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>-3.01</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>-1.47</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-35.31</t>
+          <t>-18.48</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>72.03</t>
+          <t>82.37</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>22.57</v>
+        <v>22.66</v>
       </c>
       <c r="AN4" t="n">
         <v>23.26</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>430.70</t>
+          <t>4280.47</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-99.77</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>82395.80670470756</t>
+          <t>82288.22863247864</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>9629.200000000001</v>
+        <v>9716.799999999999</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>14884.2</t>
+          <t>11919.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>7449.74</v>
+        <v>7436.54</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-5255</t>
+          <t>-2203</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>679.2619911243006</t>
+          <t>653.54279230789</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>816.5911899499497</t>
+          <t>512.0871988176314</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>105.68</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-51.37</t>
+          <t>-35.31</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>22.5</v>
+        <v>22.57</v>
       </c>
       <c r="AN5" t="n">
         <v>23.26</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.61</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>160.83</t>
+          <t>430.70</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.65</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>82395.80670470756</t>
+          <t>82288.22863247864</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>6324</v>
+        <v>9629.200000000001</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>13005.4</t>
+          <t>14884.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>7283.74</v>
+        <v>7449.74</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-6681</t>
+          <t>-5255</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>654.2930458832735</t>
+          <t>679.2619911243006</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-343.1385080735217</t>
+          <t>816.5911899499497</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>105.68</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-41.51</t>
+          <t>-51.37</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>22.46</v>
+        <v>22.5</v>
       </c>
       <c r="AN6" t="n">
-        <v>23.28</v>
+        <v>23.26</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>23.61</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>115.43</t>
+          <t>160.83</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.52</t>
+          <t>-104.65</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>82395.80670470756</t>
+          <t>82288.22863247864</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>7527.4</v>
+        <v>6324</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>12868.8</t>
+          <t>13005.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>7378.32</v>
+        <v>7283.74</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-5341</t>
+          <t>-6681</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>835.6442375117817</t>
+          <t>654.2930458832735</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>80.10972718128687</t>
+          <t>-343.1385080735217</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-10.70</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>105.68</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-34.19</t>
+          <t>-41.51</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.32</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>64.93</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>22.45</v>
+        <v>22.46</v>
       </c>
       <c r="AN7" t="n">
-        <v>23.33</v>
+        <v>23.28</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>108.28</t>
+          <t>115.43</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-106.52</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>82395.80670470756</t>
+          <t>82288.22863247864</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>8284.4</v>
+        <v>7527.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>12587.7</t>
+          <t>12868.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>7563.22</v>
+        <v>7378.32</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-4303</t>
+          <t>-5341</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>973.0141484809627</t>
+          <t>835.6442375117817</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>523.2104301459694</t>
+          <t>80.10972718128687</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-12.06</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>105.68</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>-34.19</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-10.32</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>81.76</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>22.46</v>
+        <v>22.45</v>
       </c>
       <c r="AN8" t="n">
-        <v>23.38</v>
+        <v>23.33</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>119.34</t>
+          <t>108.28</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>82395.80670470756</t>
+          <t>82288.22863247864</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>14123</v>
+        <v>8284.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>12216.7</t>
+          <t>12587.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>7629.54</v>
+        <v>7563.22</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>-4303</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1054.796642723689</t>
+          <t>973.0141484809627</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>969.2039190188734</t>
+          <t>523.2104301459694</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-12.06</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>105.68</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>293.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,84 +3908,84 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-1.29</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>3.36</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>73.69</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,274 +4024,274 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>81.76</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>23.49</t>
+        </is>
+      </c>
+      <c r="AM9" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>23.57</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>119.34</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-110.67</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>82288.22863247864</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>14123</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>12216.7</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>7629.54</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>1054.796642723689</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>969.2039190188734</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>-8.37</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-13.42998910113004</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-25.43417574544826</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-6.333574654154932</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>105.68</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>19.70%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>1592</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>安可-光電業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>光電業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>23.45</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>24.05</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="AM9" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>23.42</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>92.50</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-113.86</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>82395.80670470756</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="n">
-        <v>20139.2</v>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>11594.6</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>7648.36</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>8544</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>1070.358956124564</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>1443.473048872349</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>-10.51</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-13.42998910113004</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>-25.43417574544826</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>-6.333574654154932</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>108.18</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>19.70%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>-0.85%</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>89.32</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>1630</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>安可-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>光電業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>23.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>426.0</t>
+          <t>293.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>75.73</t>
+          <t>73.69</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>91.82</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>22.42</v>
+        <v>22.43</v>
       </c>
       <c r="AN10" t="n">
-        <v>23.46</v>
+        <v>23.42</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>87.14</t>
+          <t>92.50</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-113.86</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>82395.80670470756</t>
+          <t>82288.22863247864</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>19686.8</v>
+        <v>20139.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>11202.7</t>
+          <t>11594.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>8102.12</v>
+        <v>7648.36</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1002.520030170422</t>
+          <t>1070.358956124564</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>2227.590625489014</t>
+          <t>1443.473048872349</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>105.68</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>390.0</t>
+          <t>426.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>75.73</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>91.82</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>22.38</v>
+        <v>22.42</v>
       </c>
       <c r="AN11" t="n">
-        <v>23.5</v>
+        <v>23.46</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-120.78</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>82395.80670470756</t>
+          <t>82288.22863247864</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>18210.2</v>
+        <v>19686.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>10729.5</t>
+          <t>11202.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>8369.26</v>
+        <v>8102.12</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>779.7799219306776</t>
+          <t>1002.520030170422</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>2920.630355459645</t>
+          <t>2227.590625489014</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>105.68</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
+          <t>23.15</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>23.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1498.0</t>
+          <t>390.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>65.67</t>
+          <t>69.72</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>98.11</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>95.6</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.11</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>22.34</v>
+        <v>22.38</v>
       </c>
       <c r="AN12" t="n">
-        <v>23.54</v>
+        <v>23.5</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.52</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>46.64</t>
+          <t>69.08</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-124.37</t>
+          <t>-120.78</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>82395.80670470756</t>
+          <t>82288.22863247864</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>16891</v>
+        <v>18210.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>10195.3</t>
+          <t>10729.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>10437.66</v>
+        <v>8369.26</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>390.5343885617743</t>
+          <t>779.7799219306776</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>3886.843171294131</t>
+          <t>2920.630355459645</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>36258.0</t>
+          <t>9279.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>105.68</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO導電玻璃.xlsx
+++ b/Result/checksun_type/ITO導電玻璃.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,54 +1014,54 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>248</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>38.71</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>68.82</t>
+          <t>52.69</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
+          <t>-1.99</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>-1.46</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>-1.90</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>3.92</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>-1.9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>-1.79</t>
-        </is>
-      </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>22.8</v>
+        <v>22.88</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.25</v>
+        <v>23.22</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>154.33</t>
+          <t>78.99</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-95.95</t>
+          <t>-94.95</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>82288.22863247864</t>
+          <t>82183.42105263157</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4584.0</t>
+          <t>5739.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>9280.4</v>
+        <v>9625.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>8403.9</t>
+          <t>7974.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>7418.64</v>
+        <v>7390.28</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>425.2400559355071</t>
+          <t>279.4693411980216</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-335.0564372059416</t>
+          <t>-522.2695898581487</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>4584.0</t>
+          <t>5739.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>105.68</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>23.2</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>23.25</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,102 +1338,102 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.48</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>10.43</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-7.74</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>10.87</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>-2.37</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-1.47</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>6.64</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-5.56</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>10.87</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>-0.84</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>248</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>77.42</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>88.17</t>
+          <t>68.82</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>22.74</v>
+        <v>22.8</v>
       </c>
       <c r="AN3" t="n">
-        <v>23.26</v>
+        <v>23.25</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>362.90</t>
+          <t>154.33</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-97.51</t>
+          <t>-95.95</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>82288.22863247864</t>
+          <t>82183.42105263157</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>9462.4</v>
+        <v>9280.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>8873.4</t>
+          <t>8403.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>7472.64</v>
+        <v>7418.64</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>876</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>563.475781961225</t>
+          <t>425.2400559355071</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>68.1072250545676</t>
+          <t>-335.0564372059416</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>105.68</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>361.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,79 +1758,79 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-2.59</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-1.48</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>6.64</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>23.95</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-3.01</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.47</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-18.48</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>248</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>77.42</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>82.37</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>22.66</v>
+        <v>22.74</v>
       </c>
       <c r="AN4" t="n">
         <v>23.26</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>4280.47</t>
+          <t>362.90</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-99.77</t>
+          <t>-97.51</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>82288.22863247864</t>
+          <t>82183.42105263157</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>9716.799999999999</v>
+        <v>9462.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>11919.9</t>
+          <t>8873.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>7436.54</v>
+        <v>7472.64</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2203</t>
+          <t>589</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>653.54279230789</t>
+          <t>563.475781961225</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>512.0871988176314</t>
+          <t>68.1072250545676</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>105.68</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>24.05</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>24.45</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>361.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-35.31</t>
+          <t>-18.48</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>248</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>72.03</t>
+          <t>82.37</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>22.57</v>
+        <v>22.66</v>
       </c>
       <c r="AN5" t="n">
         <v>23.26</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>430.70</t>
+          <t>4280.47</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-99.77</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>82288.22863247864</t>
+          <t>82183.42105263157</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>9629.200000000001</v>
+        <v>9716.799999999999</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>14884.2</t>
+          <t>11919.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>7449.74</v>
+        <v>7436.54</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-5255</t>
+          <t>-2203</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>679.2619911243006</t>
+          <t>653.54279230789</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>816.5911899499497</t>
+          <t>512.0871988176314</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>105.68</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-51.37</t>
+          <t>-35.31</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>248</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>22.5</v>
+        <v>22.57</v>
       </c>
       <c r="AN6" t="n">
         <v>23.26</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.61</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>160.83</t>
+          <t>430.70</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.65</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>82288.22863247864</t>
+          <t>82183.42105263157</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>6324</v>
+        <v>9629.200000000001</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>13005.4</t>
+          <t>14884.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>7283.74</v>
+        <v>7449.74</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-6681</t>
+          <t>-5255</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>654.2930458832735</t>
+          <t>679.2619911243006</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-343.1385080735217</t>
+          <t>816.5911899499497</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>105.68</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-41.51</t>
+          <t>-51.37</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>248</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>22.46</v>
+        <v>22.5</v>
       </c>
       <c r="AN7" t="n">
-        <v>23.28</v>
+        <v>23.26</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>23.61</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>115.43</t>
+          <t>160.83</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-106.52</t>
+          <t>-104.65</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>82288.22863247864</t>
+          <t>82183.42105263157</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>7527.4</v>
+        <v>6324</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>12868.8</t>
+          <t>13005.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>7378.32</v>
+        <v>7283.74</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-5341</t>
+          <t>-6681</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>835.6442375117817</t>
+          <t>654.2930458832735</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>80.10972718128687</t>
+          <t>-343.1385080735217</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-10.70</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>105.68</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-34.19</t>
+          <t>-41.51</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.32</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>248</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>64.93</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>22.45</v>
+        <v>22.46</v>
       </c>
       <c r="AN8" t="n">
-        <v>23.33</v>
+        <v>23.28</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>108.28</t>
+          <t>115.43</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-106.52</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>82288.22863247864</t>
+          <t>82183.42105263157</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>8284.4</v>
+        <v>7527.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>12587.7</t>
+          <t>12868.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>7563.22</v>
+        <v>7378.32</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-4303</t>
+          <t>-5341</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>973.0141484809627</t>
+          <t>835.6442375117817</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>523.2104301459694</t>
+          <t>80.10972718128687</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-12.06</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>105.68</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>-34.19</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-10.32</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>248</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>81.76</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>22.46</v>
+        <v>22.45</v>
       </c>
       <c r="AN9" t="n">
-        <v>23.38</v>
+        <v>23.33</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>119.34</t>
+          <t>108.28</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>82288.22863247864</t>
+          <t>82183.42105263157</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>14123</v>
+        <v>8284.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>12216.7</t>
+          <t>12587.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>7629.54</v>
+        <v>7563.22</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>-4303</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1054.796642723689</t>
+          <t>973.0141484809627</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>969.2039190188734</t>
+          <t>523.2104301459694</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-12.06</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>105.68</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>293.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,84 +4338,84 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-1.48</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-1.47</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>73.69</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,274 +4454,274 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>248</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>81.76</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>23.49</t>
+        </is>
+      </c>
+      <c r="AM10" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>23.57</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>119.34</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-110.67</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>82183.42105263157</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="n">
+        <v>14123</v>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>12216.7</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>7629.54</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>1054.796642723689</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>969.2039190188734</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>-8.37</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-13.42998910113004</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-25.43417574544826</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-6.333574654154932</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>105.45</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>19.70%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>88.59</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>1588</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>安可-光電業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>光電業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>23.45</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>24.05</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="AM10" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>23.42</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>92.50</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-113.86</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>82288.22863247864</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="n">
-        <v>20139.2</v>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>11594.6</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>7648.36</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>8544</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>1070.358956124564</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>1443.473048872349</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>-10.51</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>-13.42998910113004</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>-25.43417574544826</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>-6.333574654154932</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>105.68</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>19.70%</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>-0.85%</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>1592</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>安可-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>光電業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>23.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>426.0</t>
+          <t>293.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>75.73</t>
+          <t>73.69</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>248</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>91.82</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>22.42</v>
+        <v>22.43</v>
       </c>
       <c r="AN11" t="n">
-        <v>23.46</v>
+        <v>23.42</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>87.14</t>
+          <t>92.50</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-113.86</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>82288.22863247864</t>
+          <t>82183.42105263157</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>19686.8</v>
+        <v>20139.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>11202.7</t>
+          <t>11594.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>8102.12</v>
+        <v>7648.36</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>1002.520030170422</t>
+          <t>1070.358956124564</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>2227.590625489014</t>
+          <t>1443.473048872349</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>105.68</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>390.0</t>
+          <t>426.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>69.72</t>
+          <t>75.73</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>248</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>98.11</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>95.6</t>
+          <t>91.82</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-4.41</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>23.31</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>22.38</v>
+        <v>22.42</v>
       </c>
       <c r="AN12" t="n">
-        <v>23.5</v>
+        <v>23.46</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.52</t>
+          <t>23.54</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>69.08</t>
+          <t>87.14</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-120.78</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>82288.22863247864</t>
+          <t>82183.42105263157</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>18210.2</v>
+        <v>19686.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>10729.5</t>
+          <t>11202.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>8369.26</v>
+        <v>8102.12</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>779.7799219306776</t>
+          <t>1002.520030170422</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>2920.630355459645</t>
+          <t>2227.590625489014</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>9279.0</t>
+          <t>10030.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-8.37</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>105.68</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5571,17 +5571,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
+          <t>23.15</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>23.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO導電玻璃.xlsx
+++ b/Result/checksun_type/ITO導電玻璃.xlsx
@@ -883,7 +883,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>-22.22</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1024,63 +1024,63 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>52.69</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>22.88</v>
+        <v>22.98</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.22</v>
+        <v>23.19</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>78.99</t>
+          <t>48.56</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-94.95</t>
+          <t>-94.25</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>82183.42105263157</t>
+          <t>82079.0859375</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5739.0</t>
+          <t>5821.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>9625.6</v>
+        <v>6127.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>7974.8</t>
+          <t>7878.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>7390.28</v>
+        <v>7309.38</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>-1750</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>279.4693411980216</t>
+          <t>138.9183568647506</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-522.2695898581487</t>
+          <t>-634.1120569682398</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>5739.0</t>
+          <t>5821.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,7 +1444,7 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1454,44 +1454,44 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>38.71</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>68.82</t>
+          <t>52.69</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
+          <t>-1.99</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>-1.46</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>-1.90</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>3.92</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>-1.9</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>-1.79</t>
-        </is>
-      </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>22.8</v>
+        <v>22.88</v>
       </c>
       <c r="AN3" t="n">
-        <v>23.25</v>
+        <v>23.22</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>154.33</t>
+          <t>78.99</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-95.95</t>
+          <t>-94.95</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>82183.42105263157</t>
+          <t>82079.0859375</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4584.0</t>
+          <t>5739.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>9280.4</v>
+        <v>9625.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>8403.9</t>
+          <t>7974.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>7418.64</v>
+        <v>7390.28</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>425.2400559355071</t>
+          <t>279.4693411980216</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-335.0564372059416</t>
+          <t>-522.2695898581487</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4584.0</t>
+          <t>5739.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>23.2</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>23.25</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,7 +1874,7 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1884,63 +1884,63 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>77.42</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>88.17</t>
+          <t>68.82</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>22.74</v>
+        <v>22.8</v>
       </c>
       <c r="AN4" t="n">
-        <v>23.26</v>
+        <v>23.25</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>362.90</t>
+          <t>154.33</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-97.51</t>
+          <t>-95.95</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>82183.42105263157</t>
+          <t>82079.0859375</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>9462.4</v>
+        <v>9280.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>8873.4</t>
+          <t>8403.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>7472.64</v>
+        <v>7418.64</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>876</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>563.475781961225</t>
+          <t>425.2400559355071</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>68.1072250545676</t>
+          <t>-335.0564372059416</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>361.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,79 +2188,79 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-1.93</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>6.64</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>23.95</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-3.23</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-1.48</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-18.48</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,7 +2304,7 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -2314,63 +2314,63 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>77.42</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>82.37</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>22.66</v>
+        <v>22.74</v>
       </c>
       <c r="AN5" t="n">
         <v>23.26</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>4280.47</t>
+          <t>362.90</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-99.77</t>
+          <t>-97.51</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>82183.42105263157</t>
+          <t>82079.0859375</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>9716.799999999999</v>
+        <v>9462.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>11919.9</t>
+          <t>8873.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>7436.54</v>
+        <v>7472.64</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2203</t>
+          <t>589</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>653.54279230789</t>
+          <t>563.475781961225</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>512.0871988176314</t>
+          <t>68.1072250545676</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>24.05</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>24.45</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>361.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-35.31</t>
+          <t>-18.48</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,7 +2734,7 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2744,63 +2744,63 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>72.03</t>
+          <t>82.37</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>22.57</v>
+        <v>22.66</v>
       </c>
       <c r="AN6" t="n">
         <v>23.26</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>430.70</t>
+          <t>4280.47</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-99.77</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>82183.42105263157</t>
+          <t>82079.0859375</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>9629.200000000001</v>
+        <v>9716.799999999999</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>14884.2</t>
+          <t>11919.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>7449.74</v>
+        <v>7436.54</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-5255</t>
+          <t>-2203</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>679.2619911243006</t>
+          <t>653.54279230789</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>816.5911899499497</t>
+          <t>512.0871988176314</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-51.37</t>
+          <t>-35.31</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,7 +3164,7 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -3174,63 +3174,63 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>22.5</v>
+        <v>22.57</v>
       </c>
       <c r="AN7" t="n">
         <v>23.26</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.61</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>160.83</t>
+          <t>430.70</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.65</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>82183.42105263157</t>
+          <t>82079.0859375</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>6324</v>
+        <v>9629.200000000001</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>13005.4</t>
+          <t>14884.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>7283.74</v>
+        <v>7449.74</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-6681</t>
+          <t>-5255</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>654.2930458832735</t>
+          <t>679.2619911243006</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-343.1385080735217</t>
+          <t>816.5911899499497</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-41.51</t>
+          <t>-51.37</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,7 +3594,7 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -3604,63 +3604,63 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>22.46</v>
+        <v>22.5</v>
       </c>
       <c r="AN8" t="n">
-        <v>23.28</v>
+        <v>23.26</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>23.61</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>115.43</t>
+          <t>160.83</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-106.52</t>
+          <t>-104.65</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>82183.42105263157</t>
+          <t>82079.0859375</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>7527.4</v>
+        <v>6324</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>12868.8</t>
+          <t>13005.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>7378.32</v>
+        <v>7283.74</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-5341</t>
+          <t>-6681</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>835.6442375117817</t>
+          <t>654.2930458832735</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>80.10972718128687</t>
+          <t>-343.1385080735217</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-10.70</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-34.19</t>
+          <t>-41.51</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-10.32</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,7 +4024,7 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -4034,63 +4034,63 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>64.93</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>22.45</v>
+        <v>22.46</v>
       </c>
       <c r="AN9" t="n">
-        <v>23.33</v>
+        <v>23.28</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>108.28</t>
+          <t>115.43</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-106.52</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>82183.42105263157</t>
+          <t>82079.0859375</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>8284.4</v>
+        <v>7527.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>12587.7</t>
+          <t>12868.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>7563.22</v>
+        <v>7378.32</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-4303</t>
+          <t>-5341</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>973.0141484809627</t>
+          <t>835.6442375117817</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>523.2104301459694</t>
+          <t>80.10972718128687</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-12.06</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>-34.19</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-10.32</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,7 +4454,7 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -4464,63 +4464,63 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>81.76</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>22.46</v>
+        <v>22.45</v>
       </c>
       <c r="AN10" t="n">
-        <v>23.38</v>
+        <v>23.33</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>119.34</t>
+          <t>108.28</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>82183.42105263157</t>
+          <t>82079.0859375</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>14123</v>
+        <v>8284.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>12216.7</t>
+          <t>12587.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>7629.54</v>
+        <v>7563.22</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>-4303</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1054.796642723689</t>
+          <t>973.0141484809627</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>969.2039190188734</t>
+          <t>523.2104301459694</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-12.06</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>293.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,84 +4768,84 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-1.48</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>73.69</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,7 +4884,7 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -4894,264 +4894,264 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>81.76</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>23.49</t>
+        </is>
+      </c>
+      <c r="AM11" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>23.57</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>119.34</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-110.67</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>82079.0859375</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="n">
+        <v>14123</v>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>12216.7</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>7629.54</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>1054.796642723689</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>969.2039190188734</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>-8.37</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-13.42998910113004</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>-25.43417574544826</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-6.333574654154932</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>106.14</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>19.70%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>90.37</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>1599</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>安可-光電業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>光電業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>23.45</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>24.05</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="AM11" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>23.42</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>92.50</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-113.86</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>82183.42105263157</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="n">
-        <v>20139.2</v>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>11594.6</t>
-        </is>
-      </c>
-      <c r="AZ11" t="n">
-        <v>7648.36</v>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>8544</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>1070.358956124564</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>1443.473048872349</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>-10.51</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>-13.42998910113004</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>-25.43417574544826</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>-6.333574654154932</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>105.45</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>19.70%</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>-0.85%</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>88.59</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>1588</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>安可-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>光電業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>23.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>426.0</t>
+          <t>293.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>75.73</t>
+          <t>73.69</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,7 +5314,7 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -5324,63 +5324,63 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>67.92</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>91.82</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.41</t>
+          <t>-4.22</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>22.42</v>
+        <v>22.43</v>
       </c>
       <c r="AN12" t="n">
-        <v>23.46</v>
+        <v>23.42</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.54</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>87.14</t>
+          <t>92.50</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-113.86</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>82183.42105263157</t>
+          <t>82079.0859375</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>19686.8</v>
+        <v>20139.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>11202.7</t>
+          <t>11594.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>8102.12</v>
+        <v>7648.36</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>1002.520030170422</t>
+          <t>1070.358956124564</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>2227.590625489014</t>
+          <t>1443.473048872349</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>10030.0</t>
+          <t>6786.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-10.51</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>106.14</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO導電玻璃.xlsx
+++ b/Result/checksun_type/ITO導電玻璃.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-22.22</t>
+          <t>-30.12</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-6.75</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,63 +1014,63 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>177</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>44.31</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>22.98</v>
+        <v>23.07</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.19</v>
+        <v>23.17</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>23.69</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-94.25</t>
+          <t>-93.67</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>82079.0859375</t>
+          <t>81971.50638297873</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5821.0</t>
+          <t>4157.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>6127.4</v>
+        <v>5218.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>7878.3</t>
+          <t>7467.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>7309.38</v>
+        <v>7306.04</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1750</t>
+          <t>-2249</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>138.9183568647506</t>
+          <t>-8.815079963841526</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-634.1120569682398</t>
+          <t>-821.3489825210982</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>5821.0</t>
+          <t>4157.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-8.56</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>106.82</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.83</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1609</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>-22.22</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>177</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>52.69</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>22.88</v>
+        <v>22.98</v>
       </c>
       <c r="AN3" t="n">
-        <v>23.22</v>
+        <v>23.19</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>78.99</t>
+          <t>48.56</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-94.95</t>
+          <t>-94.25</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>82079.0859375</t>
+          <t>81971.50638297873</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5739.0</t>
+          <t>5821.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>9625.6</v>
+        <v>6127.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>7974.8</t>
+          <t>7878.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>7390.28</v>
+        <v>7309.38</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>-1750</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>279.4693411980216</t>
+          <t>138.9183568647506</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-522.2695898581487</t>
+          <t>-634.1120569682398</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>5739.0</t>
+          <t>5821.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>106.82</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.83</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1609</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1701,17 +1701,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,54 +1874,54 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>177</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>38.71</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>68.82</t>
+          <t>52.69</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
+          <t>-1.99</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>-1.46</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>-1.90</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>3.92</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>-1.9</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>-1.79</t>
-        </is>
-      </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>22.8</v>
+        <v>22.88</v>
       </c>
       <c r="AN4" t="n">
-        <v>23.25</v>
+        <v>23.22</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1930,17 +1930,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>154.33</t>
+          <t>78.99</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-95.95</t>
+          <t>-94.95</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>82079.0859375</t>
+          <t>81971.50638297873</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4584.0</t>
+          <t>5739.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>9280.4</v>
+        <v>9625.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>8403.9</t>
+          <t>7974.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>7418.64</v>
+        <v>7390.28</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>425.2400559355071</t>
+          <t>279.4693411980216</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-335.0564372059416</t>
+          <t>-522.2695898581487</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>4584.0</t>
+          <t>5739.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>106.82</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.83</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1609</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>23.2</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>23.25</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>177</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>77.42</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>88.17</t>
+          <t>68.82</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>22.74</v>
+        <v>22.8</v>
       </c>
       <c r="AN5" t="n">
-        <v>23.26</v>
+        <v>23.25</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>362.90</t>
+          <t>154.33</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-97.51</t>
+          <t>-95.95</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>82079.0859375</t>
+          <t>81971.50638297873</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>9462.4</v>
+        <v>9280.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>8873.4</t>
+          <t>8403.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>7472.64</v>
+        <v>7418.64</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>876</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>563.475781961225</t>
+          <t>425.2400559355071</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>68.1072250545676</t>
+          <t>-335.0564372059416</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>106.82</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.83</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1609</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>361.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,79 +2618,79 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-1.28</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-1.33</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>6.64</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>23.95</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-2.57</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-18.48</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>177</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>77.42</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>82.37</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>22.66</v>
+        <v>22.74</v>
       </c>
       <c r="AN6" t="n">
         <v>23.26</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>4280.47</t>
+          <t>362.90</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-99.77</t>
+          <t>-97.51</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>82079.0859375</t>
+          <t>81971.50638297873</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>9716.799999999999</v>
+        <v>9462.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>11919.9</t>
+          <t>8873.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>7436.54</v>
+        <v>7472.64</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2203</t>
+          <t>589</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>653.54279230789</t>
+          <t>563.475781961225</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>512.0871988176314</t>
+          <t>68.1072250545676</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>106.82</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.83</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1609</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>24.05</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>24.45</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>361.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-35.31</t>
+          <t>-18.48</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>177</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>72.03</t>
+          <t>82.37</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>22.57</v>
+        <v>22.66</v>
       </c>
       <c r="AN7" t="n">
         <v>23.26</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>430.70</t>
+          <t>4280.47</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-99.77</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>82079.0859375</t>
+          <t>81971.50638297873</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>9629.200000000001</v>
+        <v>9716.799999999999</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>14884.2</t>
+          <t>11919.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>7449.74</v>
+        <v>7436.54</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-5255</t>
+          <t>-2203</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>679.2619911243006</t>
+          <t>653.54279230789</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>816.5911899499497</t>
+          <t>512.0871988176314</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>106.82</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.83</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1609</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-51.37</t>
+          <t>-35.31</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>177</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>22.5</v>
+        <v>22.57</v>
       </c>
       <c r="AN8" t="n">
         <v>23.26</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.61</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>160.83</t>
+          <t>430.70</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.65</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>82079.0859375</t>
+          <t>81971.50638297873</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>6324</v>
+        <v>9629.200000000001</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>13005.4</t>
+          <t>14884.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>7283.74</v>
+        <v>7449.74</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-6681</t>
+          <t>-5255</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>654.2930458832735</t>
+          <t>679.2619911243006</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-343.1385080735217</t>
+          <t>816.5911899499497</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>-6.03</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>106.82</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.83</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1609</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-41.51</t>
+          <t>-51.37</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>177</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>22.46</v>
+        <v>22.5</v>
       </c>
       <c r="AN9" t="n">
-        <v>23.28</v>
+        <v>23.26</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>23.61</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>115.43</t>
+          <t>160.83</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-106.52</t>
+          <t>-104.65</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>82079.0859375</t>
+          <t>81971.50638297873</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>7527.4</v>
+        <v>6324</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>12868.8</t>
+          <t>13005.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>7378.32</v>
+        <v>7283.74</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-5341</t>
+          <t>-6681</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>835.6442375117817</t>
+          <t>654.2930458832735</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>80.10972718128687</t>
+          <t>-343.1385080735217</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-10.70</t>
+          <t>-9.14</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>106.82</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.83</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1609</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-34.19</t>
+          <t>-41.51</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-10.32</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>177</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>64.93</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>22.45</v>
+        <v>22.46</v>
       </c>
       <c r="AN10" t="n">
-        <v>23.33</v>
+        <v>23.28</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>108.28</t>
+          <t>115.43</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-106.52</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>82079.0859375</t>
+          <t>81971.50638297873</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>8284.4</v>
+        <v>7527.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>12587.7</t>
+          <t>12868.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>7563.22</v>
+        <v>7378.32</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-4303</t>
+          <t>-5341</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>973.0141484809627</t>
+          <t>835.6442375117817</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>523.2104301459694</t>
+          <t>80.10972718128687</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-12.06</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>106.82</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.83</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1609</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>-34.19</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-10.32</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>177</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>81.76</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>22.46</v>
+        <v>22.45</v>
       </c>
       <c r="AN11" t="n">
-        <v>23.38</v>
+        <v>23.33</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>119.34</t>
+          <t>108.28</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>82079.0859375</t>
+          <t>81971.50638297873</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>14123</v>
+        <v>8284.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>12216.7</t>
+          <t>12587.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>7629.54</v>
+        <v>7563.22</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>-4303</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>1054.796642723689</t>
+          <t>973.0141484809627</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>969.2039190188734</t>
+          <t>523.2104301459694</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-12.06</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>106.14</t>
+          <t>106.82</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>90.83</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1609</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>293.0</t>
+          <t>350.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,84 +5198,84 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-1.33</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>15.60</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>73.69</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,274 +5314,274 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>177</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>67.92</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>81.76</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.22</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
+          <t>23.49</t>
+        </is>
+      </c>
+      <c r="AM12" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>23.57</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>119.34</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-110.67</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>81971.50638297873</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="n">
+        <v>14123</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>12216.7</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>7629.54</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>1054.796642723689</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>969.2039190188734</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>8262.0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>-8.37</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>安可</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>光電業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-13.42998910113004</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>-25.43417574544826</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-6.333574654154932</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>106.82</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>19.70%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>90.83</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>1609</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>安可-光電業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>光電業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>23.45</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>24.05</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>23.55</t>
-        </is>
-      </c>
-      <c r="AM12" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>23.42</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>92.50</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-113.86</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>82079.0859375</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="n">
-        <v>20139.2</v>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>11594.6</t>
-        </is>
-      </c>
-      <c r="AZ12" t="n">
-        <v>7648.36</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>8544</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>1070.358956124564</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>1443.473048872349</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>6786.0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>-10.51</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>安可</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>光電業</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>-13.42998910113004</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>-25.43417574544826</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>-6.333574654154932</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>106.14</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>19.70%</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>-0.85%</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>90.37</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>1599</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>安可-光電業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>光電業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>22.95</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>23.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO導電玻璃.xlsx
+++ b/Result/checksun_type/ITO導電玻璃.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>219.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-30.12</t>
+          <t>-30.19</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.75</t>
+          <t>-8.53</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,74 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>44.31</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
+          <t>31.41</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.5600000000000001</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>23.27</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>23.07</v>
+        <v>23.14</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.17</v>
+        <v>23.13</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.69</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>36.65</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
+          <t>6.41</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.13</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-93.67</t>
+          <t>-93.57</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>81971.50638297873</t>
+          <t>81866.1671388102</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4157.0</t>
+          <t>5068.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>5218.8</v>
+        <v>5073.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>7467.8</t>
+          <t>7268.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>7306.04</v>
+        <v>7204.54</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2249</t>
+          <t>-2194</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-8.815079963841526</t>
+          <t>-140.3136993301846</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-821.3489825210982</t>
+          <t>-863.5561058450712</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>4157.0</t>
+          <t>5068.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1146,17 +1138,17 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>2025/08/22</t>
+          <t>2025/12/05</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.56</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>106.82</t>
+          <t>104.77</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-22.22</t>
+          <t>-30.12</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-6.75</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,74 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>43.01</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>-0.68</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
+          <t>44.31</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1.53</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>22.98</v>
+        <v>23.07</v>
       </c>
       <c r="AN3" t="n">
-        <v>23.19</v>
+        <v>23.17</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>23.69</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>48.56</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.13</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-94.25</t>
+          <t>-93.67</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>81971.50638297873</t>
+          <t>81866.1671388102</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5821.0</t>
+          <t>4157.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>6127.4</v>
+        <v>5218.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>7878.3</t>
+          <t>7467.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>7309.38</v>
+        <v>7306.04</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1750</t>
+          <t>-2249</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>138.9183568647506</t>
+          <t>-8.815079963841526</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-634.1120569682398</t>
+          <t>-821.3489825210982</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>5821.0</t>
+          <t>4157.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1576,17 +1560,17 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>2025/08/22</t>
+          <t>2025/12/05</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1646,7 +1630,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>106.82</t>
+          <t>104.77</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,7 +1727,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1758,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>-22.22</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,7 +1837,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1863,7 +1847,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,74 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>52.69</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-1.99</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>3.44</t>
-        </is>
+          <t>43.01</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2.32</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>22.88</v>
+        <v>22.98</v>
       </c>
       <c r="AN4" t="n">
-        <v>23.22</v>
+        <v>23.19</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>78.99</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
+          <t>48.56</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.12</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-94.95</t>
+          <t>-94.25</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>81971.50638297873</t>
+          <t>81866.1671388102</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5739.0</t>
+          <t>5821.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>9625.6</v>
+        <v>6127.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>7974.8</t>
+          <t>7878.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>7390.28</v>
+        <v>7309.38</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>-1750</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>279.4693411980216</t>
+          <t>138.9183568647506</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-522.2695898581487</t>
+          <t>-634.1120569682398</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>5739.0</t>
+          <t>5821.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2006,17 +1982,17 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2025/08/22</t>
+          <t>2025/12/05</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>106.82</t>
+          <t>104.77</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2131,17 +2107,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,54 +2280,50 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>38.71</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>68.82</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
+          <t>52.69</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>-1.99</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>-1.46</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>-1.90</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>3.92</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>-1.9</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>-1.79</t>
-        </is>
-      </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>22.8</v>
+        <v>22.88</v>
       </c>
       <c r="AN5" t="n">
-        <v>23.25</v>
+        <v>23.22</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2360,18 +2332,14 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>154.33</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
+          <t>78.99</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.1</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-95.95</t>
+          <t>-94.95</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>81971.50638297873</t>
+          <t>81866.1671388102</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4584.0</t>
+          <t>5739.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>9280.4</v>
+        <v>9625.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>8403.9</t>
+          <t>7974.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>7418.64</v>
+        <v>7390.28</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>425.2400559355071</t>
+          <t>279.4693411980216</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-335.0564372059416</t>
+          <t>-522.2695898581487</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>4584.0</t>
+          <t>5739.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2436,17 +2404,17 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>2025/08/22</t>
+          <t>2025/12/05</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,12 +2459,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2506,7 +2474,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>106.82</t>
+          <t>104.77</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>23.2</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>23.25</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,74 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>77.42</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>88.17</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>3.93</t>
-        </is>
+          <t>68.82</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>3.92</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>22.74</v>
+        <v>22.8</v>
       </c>
       <c r="AN6" t="n">
-        <v>23.26</v>
+        <v>23.25</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>362.90</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+          <t>154.33</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.08</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-97.51</t>
+          <t>-95.95</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>81971.50638297873</t>
+          <t>81866.1671388102</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>9462.4</v>
+        <v>9280.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>8873.4</t>
+          <t>8403.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>7472.64</v>
+        <v>7418.64</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>876</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>563.475781961225</t>
+          <t>425.2400559355071</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>68.1072250545676</t>
+          <t>-335.0564372059416</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2866,17 +2826,17 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>2025/08/22</t>
+          <t>2025/12/05</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>106.82</t>
+          <t>104.77</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>361.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,79 +3008,79 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-3.25</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-0.66</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6.64</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>23.95</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-1.91</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-1.33</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-18.48</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -3133,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,74 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>77.42</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>82.37</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>3.29</t>
-        </is>
+          <t>88.17</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>3.93</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>22.66</v>
+        <v>22.74</v>
       </c>
       <c r="AN7" t="n">
         <v>23.26</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>4280.47</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+          <t>362.90</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.05</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-99.77</t>
+          <t>-97.51</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>81971.50638297873</t>
+          <t>81866.1671388102</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>9716.799999999999</v>
+        <v>9462.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>11919.9</t>
+          <t>8873.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>7436.54</v>
+        <v>7472.64</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2203</t>
+          <t>589</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>653.54279230789</t>
+          <t>563.475781961225</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>512.0871988176314</t>
+          <t>68.1072250545676</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3296,17 +3248,17 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>2025/08/22</t>
+          <t>2025/12/05</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>106.82</t>
+          <t>104.77</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
           <t>24.05</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>24.45</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>361.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-35.31</t>
+          <t>-18.48</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,74 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>72.03</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>3.56</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>3.31</t>
-        </is>
+          <t>82.37</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>3.29</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>22.57</v>
+        <v>22.66</v>
       </c>
       <c r="AN8" t="n">
         <v>23.26</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>430.70</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
+          <t>4280.47</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-99.77</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>81971.50638297873</t>
+          <t>81866.1671388102</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>9629.200000000001</v>
+        <v>9716.799999999999</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>14884.2</t>
+          <t>11919.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>7449.74</v>
+        <v>7436.54</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-5255</t>
+          <t>-2203</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>679.2619911243006</t>
+          <t>653.54279230789</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>816.5911899499497</t>
+          <t>512.0871988176314</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3726,17 +3670,17 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>2025/08/22</t>
+          <t>2025/12/05</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-6.03</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,12 +3725,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3796,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>106.82</t>
+          <t>104.77</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-51.37</t>
+          <t>-35.31</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,74 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>55.37</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
+          <t>72.03</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>3.31</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>22.5</v>
+        <v>22.57</v>
       </c>
       <c r="AN9" t="n">
         <v>23.26</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.61</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>160.83</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
+          <t>430.70</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0.04</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.65</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>81971.50638297873</t>
+          <t>81866.1671388102</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>6324</v>
+        <v>9629.200000000001</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>13005.4</t>
+          <t>14884.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>7283.74</v>
+        <v>7449.74</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-6681</t>
+          <t>-5255</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>654.2930458832735</t>
+          <t>679.2619911243006</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-343.1385080735217</t>
+          <t>816.5911899499497</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4156,17 +4092,17 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>2025/08/22</t>
+          <t>2025/12/05</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-9.14</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>106.82</t>
+          <t>104.77</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4249,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-41.51</t>
+          <t>-51.37</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,74 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>64.93</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-0.78</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
+          <t>55.37</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>2.62</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>22.46</v>
+        <v>22.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>23.28</v>
+        <v>23.26</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>23.61</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>115.43</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
+          <t>160.83</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0.09</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-106.52</t>
+          <t>-104.65</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>81971.50638297873</t>
+          <t>81866.1671388102</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>7527.4</v>
+        <v>6324</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>12868.8</t>
+          <t>13005.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>7378.32</v>
+        <v>7283.74</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-5341</t>
+          <t>-6681</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>835.6442375117817</t>
+          <t>654.2930458832735</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>80.10972718128687</t>
+          <t>-343.1385080735217</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4586,17 +4514,17 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>2025/08/22</t>
+          <t>2025/12/05</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-10.70</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>106.82</t>
+          <t>104.77</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4671,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-34.19</t>
+          <t>-41.51</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-10.32</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,74 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>68.87</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-3.00</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
+          <t>64.93</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>3.01</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>22.45</v>
+        <v>22.46</v>
       </c>
       <c r="AN11" t="n">
-        <v>23.33</v>
+        <v>23.28</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>108.28</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
+          <t>115.43</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0.13</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-106.52</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>81971.50638297873</t>
+          <t>81866.1671388102</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>8284.4</v>
+        <v>7527.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>12587.7</t>
+          <t>12868.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>7563.22</v>
+        <v>7378.32</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-4303</t>
+          <t>-5341</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>973.0141484809627</t>
+          <t>835.6442375117817</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>523.2104301459694</t>
+          <t>80.10972718128687</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5016,17 +4936,17 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>2025/08/22</t>
+          <t>2025/12/05</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-12.06</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>106.82</t>
+          <t>104.77</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5093,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>350.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15.60</t>
+          <t>-34.19</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-10.32</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,74 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>219</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>81.76</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>4.61</t>
-        </is>
+          <t>68.87</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>3.8</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>23.49</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>22.46</v>
+        <v>22.45</v>
       </c>
       <c r="AN12" t="n">
-        <v>23.38</v>
+        <v>23.33</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>119.34</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
+          <t>108.28</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0.17</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-110.67</t>
+          <t>-108.40</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>81971.50638297873</t>
+          <t>81866.1671388102</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>14123</v>
+        <v>8284.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>12216.7</t>
+          <t>12587.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>7629.54</v>
+        <v>7563.22</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>-4303</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>1054.796642723689</t>
+          <t>973.0141484809627</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>969.2039190188734</t>
+          <t>523.2104301459694</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>8262.0</t>
+          <t>7065.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5446,17 +5358,17 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>2025/08/22</t>
+          <t>2025/12/05</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>106.82</t>
+          <t>104.77</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>90.83</t>
+          <t>90.14</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO導電玻璃.xlsx
+++ b/Result/checksun_type/ITO導電玻璃.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>219.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-30.19</t>
+          <t>-30.81</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.53</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,63 +1014,63 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>31.41</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.95</v>
+        <v>-0.26</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.27</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>23.14</v>
+        <v>23.24</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.13</v>
+        <v>23.11</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.71</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AR2" t="n">
         <v>0.13</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-93.57</t>
+          <t>-93.67</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>81866.1671388102</t>
+          <t>81758.34653465346</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5068.0</t>
+          <t>3758.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>5073.8</v>
+        <v>4908.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>7268.1</t>
+          <t>7094.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>7204.54</v>
+        <v>7155.24</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2194</t>
+          <t>-2185</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-140.3136993301846</t>
+          <t>-267.9211593602678</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-863.5561058450712</t>
+          <t>-969.7621895257253</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>5068.0</t>
+          <t>3758.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>104.77</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>219.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-30.12</t>
+          <t>-30.19</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.75</t>
+          <t>-8.53</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,63 +1436,63 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>44.31</t>
+          <t>31.41</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.34</v>
+        <v>-0.95</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>23.27</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>23.07</v>
+        <v>23.14</v>
       </c>
       <c r="AN3" t="n">
-        <v>23.17</v>
+        <v>23.13</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.69</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR3" t="n">
         <v>0.13</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-93.67</t>
+          <t>-93.57</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>81866.1671388102</t>
+          <t>81758.34653465346</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4157.0</t>
+          <t>5068.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>5218.8</v>
+        <v>5073.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>7467.8</t>
+          <t>7268.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>7306.04</v>
+        <v>7204.54</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2249</t>
+          <t>-2194</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-8.815079963841526</t>
+          <t>-140.3136993301846</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-821.3489825210982</t>
+          <t>-863.5561058450712</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4157.0</t>
+          <t>5068.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>104.77</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-22.22</t>
+          <t>-30.12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-6.75</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>44.31</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.68</v>
+        <v>0.34</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.32</v>
+        <v>1.53</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>22.98</v>
+        <v>23.07</v>
       </c>
       <c r="AN4" t="n">
-        <v>23.19</v>
+        <v>23.17</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>23.69</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="AQ4" t="n">
         <v>0.17</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-94.25</t>
+          <t>-93.67</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>81866.1671388102</t>
+          <t>81758.34653465346</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5821.0</t>
+          <t>4157.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>6127.4</v>
+        <v>5218.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>7878.3</t>
+          <t>7467.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>7309.38</v>
+        <v>7306.04</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1750</t>
+          <t>-2249</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>138.9183568647506</t>
+          <t>-8.815079963841526</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-634.1120569682398</t>
+          <t>-821.3489825210982</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>5821.0</t>
+          <t>4157.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>104.77</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>-22.22</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>52.69</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-1.99</v>
+        <v>-0.68</v>
       </c>
       <c r="AI5" t="n">
-        <v>3.44</v>
+        <v>2.32</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>22.88</v>
+        <v>22.98</v>
       </c>
       <c r="AN5" t="n">
-        <v>23.22</v>
+        <v>23.19</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>78.99</t>
+          <t>48.56</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-94.95</t>
+          <t>-94.25</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>81866.1671388102</t>
+          <t>81758.34653465346</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5739.0</t>
+          <t>5821.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>9625.6</v>
+        <v>6127.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>7974.8</t>
+          <t>7878.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>7390.28</v>
+        <v>7309.38</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>-1750</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>279.4693411980216</t>
+          <t>138.9183568647506</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-522.2695898581487</t>
+          <t>-634.1120569682398</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>5739.0</t>
+          <t>5821.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>104.77</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2529,17 +2529,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2561,7 +2561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,50 +2702,50 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>38.71</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>68.82</t>
+          <t>52.69</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-1.9</v>
+        <v>-1.99</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.92</v>
+        <v>3.44</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>22.8</v>
+        <v>22.88</v>
       </c>
       <c r="AN6" t="n">
-        <v>23.25</v>
+        <v>23.22</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>154.33</t>
+          <t>78.99</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-95.95</t>
+          <t>-94.95</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>81866.1671388102</t>
+          <t>81758.34653465346</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4584.0</t>
+          <t>5739.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>9280.4</v>
+        <v>9625.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>8403.9</t>
+          <t>7974.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>7418.64</v>
+        <v>7390.28</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>425.2400559355071</t>
+          <t>279.4693411980216</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-335.0564372059416</t>
+          <t>-522.2695898581487</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>4584.0</t>
+          <t>5739.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>104.77</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>23.2</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>23.25</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>77.42</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>88.17</t>
+          <t>68.82</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.68</v>
+        <v>-1.9</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>22.74</v>
+        <v>22.8</v>
       </c>
       <c r="AN7" t="n">
-        <v>23.26</v>
+        <v>23.25</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>362.90</t>
+          <t>154.33</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-97.51</t>
+          <t>-95.95</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>81866.1671388102</t>
+          <t>81758.34653465346</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>9462.4</v>
+        <v>9280.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>8873.4</t>
+          <t>8403.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>7472.64</v>
+        <v>7418.64</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>876</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>563.475781961225</t>
+          <t>425.2400559355071</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>68.1072250545676</t>
+          <t>-335.0564372059416</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>104.77</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>361.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,79 +3430,79 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-2.59</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>6.64</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>23.95</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-3.9</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-18.48</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>77.42</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>82.37</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>2.35</v>
+        <v>0.68</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.29</v>
+        <v>3.93</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>22.66</v>
+        <v>22.74</v>
       </c>
       <c r="AN8" t="n">
         <v>23.26</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>4280.47</t>
+          <t>362.90</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-99.77</t>
+          <t>-97.51</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>81866.1671388102</t>
+          <t>81758.34653465346</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>9716.799999999999</v>
+        <v>9462.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>11919.9</t>
+          <t>8873.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>7436.54</v>
+        <v>7472.64</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2203</t>
+          <t>589</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>653.54279230789</t>
+          <t>563.475781961225</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>512.0871988176314</t>
+          <t>68.1072250545676</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>104.77</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
           <t>24.05</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>24.45</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3827,7 +3827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>361.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-35.31</t>
+          <t>-18.48</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>72.03</t>
+          <t>82.37</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>3.56</v>
+        <v>2.35</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>22.57</v>
+        <v>22.66</v>
       </c>
       <c r="AN9" t="n">
         <v>23.26</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>430.70</t>
+          <t>4280.47</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-99.77</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>81866.1671388102</t>
+          <t>81758.34653465346</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>9629.200000000001</v>
+        <v>9716.799999999999</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14884.2</t>
+          <t>11919.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>7449.74</v>
+        <v>7436.54</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-5255</t>
+          <t>-2203</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>679.2619911243006</t>
+          <t>653.54279230789</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>816.5911899499497</t>
+          <t>512.0871988176314</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>104.77</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-51.37</t>
+          <t>-35.31</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.13</v>
+        <v>3.56</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.62</v>
+        <v>3.31</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>22.5</v>
+        <v>22.57</v>
       </c>
       <c r="AN10" t="n">
         <v>23.26</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.61</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>160.83</t>
+          <t>430.70</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.65</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>81866.1671388102</t>
+          <t>81758.34653465346</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>6324</v>
+        <v>9629.200000000001</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>13005.4</t>
+          <t>14884.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>7283.74</v>
+        <v>7449.74</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-6681</t>
+          <t>-5255</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>654.2930458832735</t>
+          <t>679.2619911243006</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-343.1385080735217</t>
+          <t>816.5911899499497</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,22 +4569,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>104.77</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4671,7 +4671,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-41.51</t>
+          <t>-51.37</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-0.78</v>
+        <v>1.13</v>
       </c>
       <c r="AI11" t="n">
-        <v>3.01</v>
+        <v>2.62</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>22.46</v>
+        <v>22.5</v>
       </c>
       <c r="AN11" t="n">
-        <v>23.28</v>
+        <v>23.26</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>23.61</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>115.43</t>
+          <t>160.83</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.13</v>
+        <v>-0.09</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-106.52</t>
+          <t>-104.65</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>81866.1671388102</t>
+          <t>81758.34653465346</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>7527.4</v>
+        <v>6324</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>12868.8</t>
+          <t>13005.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>7378.32</v>
+        <v>7283.74</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-5341</t>
+          <t>-6681</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>835.6442375117817</t>
+          <t>654.2930458832735</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>80.10972718128687</t>
+          <t>-343.1385080735217</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>104.77</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5093,7 +5093,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-34.19</t>
+          <t>-41.51</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-10.32</t>
+          <t>-8.93</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>64.93</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-3</v>
+        <v>-0.78</v>
       </c>
       <c r="AI12" t="n">
-        <v>3.8</v>
+        <v>3.01</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>22.45</v>
+        <v>22.46</v>
       </c>
       <c r="AN12" t="n">
-        <v>23.33</v>
+        <v>23.28</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>23.59</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>108.28</t>
+          <t>115.43</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.17</v>
+        <v>-0.13</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-108.40</t>
+          <t>-106.52</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>81866.1671388102</t>
+          <t>81758.34653465346</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>8284.4</v>
+        <v>7527.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>12587.7</t>
+          <t>12868.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>7563.22</v>
+        <v>7378.32</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-4303</t>
+          <t>-5341</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>973.0141484809627</t>
+          <t>835.6442375117817</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>523.2104301459694</t>
+          <t>80.10972718128687</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>7065.0</t>
+          <t>5494.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>104.77</t>
+          <t>105.45</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>90.14</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1578</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO導電玻璃.xlsx
+++ b/Result/checksun_type/ITO導電玻璃.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>229.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-30.81</t>
+          <t>-33.26</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,62 +1019,62 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.26</v>
+        <v>-0.95</v>
       </c>
       <c r="AI2" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>-2.66</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>23.22</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>23.71</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-26.25</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
         <v>0.09</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>-2.52</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>23.26</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>23.24</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>23.11</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>23.71</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-6.10</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
+      <c r="AR2" t="n">
         <v>0.12</v>
       </c>
-      <c r="AR2" t="n">
-        <v>0.13</v>
-      </c>
       <c r="AS2" t="inlineStr">
         <is>
           <t>2.01</t>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-93.67</t>
+          <t>-94.06</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>81758.34653465346</t>
+          <t>81654.09745762711</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3758.0</t>
+          <t>5300.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4908.6</v>
+        <v>4820.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>7094.5</t>
+          <t>7223.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>7155.24</v>
+        <v>7076.86</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2185</t>
+          <t>-2402</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-267.9211593602678</t>
+          <t>-365.8121184377713</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-969.7621895257253</t>
+          <t>-904.2123933640405</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>3758.0</t>
+          <t>5300.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>219.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-30.19</t>
+          <t>-30.81</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.53</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1441,58 +1441,58 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>31.41</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.95</v>
+        <v>-0.26</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.27</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>23.14</v>
+        <v>23.24</v>
       </c>
       <c r="AN3" t="n">
-        <v>23.13</v>
+        <v>23.11</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.71</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AR3" t="n">
         <v>0.13</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-93.57</t>
+          <t>-93.67</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>81758.34653465346</t>
+          <t>81654.09745762711</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5068.0</t>
+          <t>3758.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>5073.8</v>
+        <v>4908.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>7268.1</t>
+          <t>7094.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>7204.54</v>
+        <v>7155.24</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2194</t>
+          <t>-2185</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-140.3136993301846</t>
+          <t>-267.9211593602678</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-863.5561058450712</t>
+          <t>-969.7621895257253</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>5068.0</t>
+          <t>3758.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>219.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-30.12</t>
+          <t>-30.19</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.75</t>
+          <t>-8.53</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1863,58 +1863,58 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>44.31</t>
+          <t>31.41</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.34</v>
+        <v>-0.95</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>23.27</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>23.07</v>
+        <v>23.14</v>
       </c>
       <c r="AN4" t="n">
-        <v>23.17</v>
+        <v>23.13</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.69</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR4" t="n">
         <v>0.13</v>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-93.67</t>
+          <t>-93.57</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>81758.34653465346</t>
+          <t>81654.09745762711</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4157.0</t>
+          <t>5068.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>5218.8</v>
+        <v>5073.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>7467.8</t>
+          <t>7268.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>7306.04</v>
+        <v>7204.54</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2249</t>
+          <t>-2194</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-8.815079963841526</t>
+          <t>-140.3136993301846</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-821.3489825210982</t>
+          <t>-863.5561058450712</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>4157.0</t>
+          <t>5068.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-22.22</t>
+          <t>-30.12</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-6.75</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2285,61 +2285,61 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>44.31</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.68</v>
+        <v>0.34</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.32</v>
+        <v>1.53</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>22.98</v>
+        <v>23.07</v>
       </c>
       <c r="AN5" t="n">
-        <v>23.19</v>
+        <v>23.17</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>23.69</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="AQ5" t="n">
         <v>0.17</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-94.25</t>
+          <t>-93.67</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>81758.34653465346</t>
+          <t>81654.09745762711</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5821.0</t>
+          <t>4157.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>6127.4</v>
+        <v>5218.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>7878.3</t>
+          <t>7467.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>7309.38</v>
+        <v>7306.04</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1750</t>
+          <t>-2249</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>138.9183568647506</t>
+          <t>-8.815079963841526</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-634.1120569682398</t>
+          <t>-821.3489825210982</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>5821.0</t>
+          <t>4157.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>-22.22</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2707,61 +2707,61 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>52.69</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-1.99</v>
+        <v>-0.68</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.44</v>
+        <v>2.32</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>22.88</v>
+        <v>22.98</v>
       </c>
       <c r="AN6" t="n">
-        <v>23.22</v>
+        <v>23.19</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>78.99</t>
+          <t>48.56</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-94.95</t>
+          <t>-94.25</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>81758.34653465346</t>
+          <t>81654.09745762711</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5739.0</t>
+          <t>5821.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>9625.6</v>
+        <v>6127.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>7974.8</t>
+          <t>7878.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>7390.28</v>
+        <v>7309.38</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>-1750</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>279.4693411980216</t>
+          <t>138.9183568647506</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-522.2695898581487</t>
+          <t>-634.1120569682398</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>5739.0</t>
+          <t>5821.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3129,45 +3129,45 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>38.71</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>68.82</t>
+          <t>52.69</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-1.9</v>
+        <v>-1.99</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.92</v>
+        <v>3.44</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>22.8</v>
+        <v>22.88</v>
       </c>
       <c r="AN7" t="n">
-        <v>23.25</v>
+        <v>23.22</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3176,14 +3176,14 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>154.33</t>
+          <t>78.99</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-95.95</t>
+          <t>-94.95</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>81758.34653465346</t>
+          <t>81654.09745762711</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>4584.0</t>
+          <t>5739.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>9280.4</v>
+        <v>9625.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>8403.9</t>
+          <t>7974.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>7418.64</v>
+        <v>7390.28</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>425.2400559355071</t>
+          <t>279.4693411980216</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-335.0564372059416</t>
+          <t>-522.2695898581487</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>4584.0</t>
+          <t>5739.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>23.2</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>23.25</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3551,61 +3551,61 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>77.42</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>88.17</t>
+          <t>68.82</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.68</v>
+        <v>-1.9</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>22.74</v>
+        <v>22.8</v>
       </c>
       <c r="AN8" t="n">
-        <v>23.26</v>
+        <v>23.25</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>362.90</t>
+          <t>154.33</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-97.51</t>
+          <t>-95.95</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>81758.34653465346</t>
+          <t>81654.09745762711</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>9462.4</v>
+        <v>9280.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>8873.4</t>
+          <t>8403.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>7472.64</v>
+        <v>7418.64</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>876</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>563.475781961225</t>
+          <t>425.2400559355071</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>68.1072250545676</t>
+          <t>-335.0564372059416</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>361.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,79 +3852,79 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-3.48</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>6.64</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>23.95</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-3.23</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-18.48</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3973,61 +3973,61 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>77.42</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>82.37</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>2.35</v>
+        <v>0.68</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.29</v>
+        <v>3.93</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>22.66</v>
+        <v>22.74</v>
       </c>
       <c r="AN9" t="n">
         <v>23.26</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>4280.47</t>
+          <t>362.90</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-99.77</t>
+          <t>-97.51</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>81758.34653465346</t>
+          <t>81654.09745762711</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>9716.799999999999</v>
+        <v>9462.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>11919.9</t>
+          <t>8873.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>7436.54</v>
+        <v>7472.64</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2203</t>
+          <t>589</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>653.54279230789</t>
+          <t>563.475781961225</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>512.0871988176314</t>
+          <t>68.1072250545676</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>24.05</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>24.45</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>361.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-35.31</t>
+          <t>-18.48</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4395,61 +4395,61 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>72.03</t>
+          <t>82.37</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>3.56</v>
+        <v>2.35</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>22.57</v>
+        <v>22.66</v>
       </c>
       <c r="AN10" t="n">
         <v>23.26</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>430.70</t>
+          <t>4280.47</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-99.77</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>81758.34653465346</t>
+          <t>81654.09745762711</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>9629.200000000001</v>
+        <v>9716.799999999999</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>14884.2</t>
+          <t>11919.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>7449.74</v>
+        <v>7436.54</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-5255</t>
+          <t>-2203</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>679.2619911243006</t>
+          <t>653.54279230789</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>816.5911899499497</t>
+          <t>512.0871988176314</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-51.37</t>
+          <t>-35.31</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4817,61 +4817,61 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>1.13</v>
+        <v>3.56</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.62</v>
+        <v>3.31</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>22.5</v>
+        <v>22.57</v>
       </c>
       <c r="AN11" t="n">
         <v>23.26</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.61</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>160.83</t>
+          <t>430.70</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.65</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>81758.34653465346</t>
+          <t>81654.09745762711</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>6324</v>
+        <v>9629.200000000001</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>13005.4</t>
+          <t>14884.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>7283.74</v>
+        <v>7449.74</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-6681</t>
+          <t>-5255</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>654.2930458832735</t>
+          <t>679.2619911243006</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-343.1385080735217</t>
+          <t>816.5911899499497</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-41.51</t>
+          <t>-51.37</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-8.93</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5239,61 +5239,61 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-0.78</v>
+        <v>1.13</v>
       </c>
       <c r="AI12" t="n">
-        <v>3.01</v>
+        <v>2.62</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>22.46</v>
+        <v>22.5</v>
       </c>
       <c r="AN12" t="n">
-        <v>23.28</v>
+        <v>23.26</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>23.61</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>115.43</t>
+          <t>160.83</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.13</v>
+        <v>-0.09</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-106.52</t>
+          <t>-104.65</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>81758.34653465346</t>
+          <t>81654.09745762711</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>7527.4</v>
+        <v>6324</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>12868.8</t>
+          <t>13005.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>7378.32</v>
+        <v>7283.74</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-5341</t>
+          <t>-6681</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>835.6442375117817</t>
+          <t>654.2930458832735</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>80.10972718128687</t>
+          <t>-343.1385080735217</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>5494.0</t>
+          <t>4013.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>105.45</t>
+          <t>104.55</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO導電玻璃.xlsx
+++ b/Result/checksun_type/ITO導電玻璃.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>229.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,84 +898,84 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-18.40</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-33.26</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>0</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1033,31 +1033,31 @@
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.95</v>
+        <v>-0.99</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.44</v>
+        <v>-1.06</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.22</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>23.32</v>
+        <v>23.38</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.08</v>
+        <v>23.04</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1066,14 +1066,14 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-26.25</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-94.06</t>
+          <t>-94.70</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>81654.09745762711</t>
+          <t>81544.9167842031</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5300.0</t>
+          <t>2830.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4820.8</v>
+        <v>4222.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>7223.2</t>
+          <t>5175.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>7076.86</v>
+        <v>6856.42</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2402</t>
+          <t>-952</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-365.8121184377713</t>
+          <t>-466.6059811730004</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-904.2123933640405</t>
+          <t>-1020.972226216761</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>5300.0</t>
+          <t>2830.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>104.09</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,14 +1258,14 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>23.3</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
           <t>22.9</t>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>229.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,102 +1330,102 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>-0.44</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-33.26</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-8.73</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>10.87</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>-0.87</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-30.81</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-7.94</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>10.87</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.88</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,67 +1436,67 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.26</v>
+        <v>-0.95</v>
       </c>
       <c r="AI3" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>-2.66</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>23.22</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>23.71</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-26.25</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
         <v>0.09</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>-2.52</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>23.26</t>
-        </is>
-      </c>
-      <c r="AM3" t="n">
-        <v>23.24</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>23.11</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>23.71</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>-6.10</t>
-        </is>
-      </c>
-      <c r="AQ3" t="n">
+      <c r="AR3" t="n">
         <v>0.12</v>
       </c>
-      <c r="AR3" t="n">
-        <v>0.13</v>
-      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>2.01</t>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-93.67</t>
+          <t>-94.06</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>81654.09745762711</t>
+          <t>81544.9167842031</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3758.0</t>
+          <t>5300.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4908.6</v>
+        <v>4820.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>7094.5</t>
+          <t>7223.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>7155.24</v>
+        <v>7076.86</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2185</t>
+          <t>-2402</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-267.9211593602678</t>
+          <t>-365.8121184377713</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-969.7621895257253</t>
+          <t>-904.2123933640405</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>3758.0</t>
+          <t>5300.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>104.09</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>219.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-30.19</t>
+          <t>-30.81</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.53</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,63 +1858,63 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>31.41</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.95</v>
+        <v>-0.26</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.27</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>23.14</v>
+        <v>23.24</v>
       </c>
       <c r="AN4" t="n">
-        <v>23.13</v>
+        <v>23.11</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.71</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AR4" t="n">
         <v>0.13</v>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-93.57</t>
+          <t>-93.67</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>81654.09745762711</t>
+          <t>81544.9167842031</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5068.0</t>
+          <t>3758.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>5073.8</v>
+        <v>4908.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>7268.1</t>
+          <t>7094.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>7204.54</v>
+        <v>7155.24</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2194</t>
+          <t>-2185</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-140.3136993301846</t>
+          <t>-267.9211593602678</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-863.5561058450712</t>
+          <t>-969.7621895257253</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>5068.0</t>
+          <t>3758.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>104.09</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>219.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-30.12</t>
+          <t>-30.19</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.75</t>
+          <t>-8.53</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,63 +2280,63 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>44.31</t>
+          <t>31.41</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.34</v>
+        <v>-0.95</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>23.27</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>23.07</v>
+        <v>23.14</v>
       </c>
       <c r="AN5" t="n">
-        <v>23.17</v>
+        <v>23.13</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.69</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR5" t="n">
         <v>0.13</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-93.67</t>
+          <t>-93.57</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>81654.09745762711</t>
+          <t>81544.9167842031</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4157.0</t>
+          <t>5068.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>5218.8</v>
+        <v>5073.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>7467.8</t>
+          <t>7268.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>7306.04</v>
+        <v>7204.54</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2249</t>
+          <t>-2194</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-8.815079963841526</t>
+          <t>-140.3136993301846</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-821.3489825210982</t>
+          <t>-863.5561058450712</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>4157.0</t>
+          <t>5068.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>104.09</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-22.22</t>
+          <t>-30.12</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-6.75</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>44.31</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.68</v>
+        <v>0.34</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.32</v>
+        <v>1.53</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>22.98</v>
+        <v>23.07</v>
       </c>
       <c r="AN6" t="n">
-        <v>23.19</v>
+        <v>23.17</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>23.69</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="AQ6" t="n">
         <v>0.17</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-94.25</t>
+          <t>-93.67</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>81654.09745762711</t>
+          <t>81544.9167842031</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5821.0</t>
+          <t>4157.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>6127.4</v>
+        <v>5218.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>7878.3</t>
+          <t>7467.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>7309.38</v>
+        <v>7306.04</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1750</t>
+          <t>-2249</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>138.9183568647506</t>
+          <t>-8.815079963841526</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-634.1120569682398</t>
+          <t>-821.3489825210982</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>5821.0</t>
+          <t>4157.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>104.09</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>-22.22</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>52.69</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-1.99</v>
+        <v>-0.68</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.44</v>
+        <v>2.32</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>22.88</v>
+        <v>22.98</v>
       </c>
       <c r="AN7" t="n">
-        <v>23.22</v>
+        <v>23.19</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>78.99</t>
+          <t>48.56</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-94.95</t>
+          <t>-94.25</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>81654.09745762711</t>
+          <t>81544.9167842031</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5739.0</t>
+          <t>5821.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>9625.6</v>
+        <v>6127.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>7974.8</t>
+          <t>7878.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>7390.28</v>
+        <v>7309.38</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>-1750</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>279.4693411980216</t>
+          <t>138.9183568647506</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-522.2695898581487</t>
+          <t>-634.1120569682398</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>5739.0</t>
+          <t>5821.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>104.09</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3373,17 +3373,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,50 +3546,50 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>38.71</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>68.82</t>
+          <t>52.69</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-1.9</v>
+        <v>-1.99</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.92</v>
+        <v>3.44</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>22.8</v>
+        <v>22.88</v>
       </c>
       <c r="AN8" t="n">
-        <v>23.25</v>
+        <v>23.22</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3598,14 +3598,14 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>154.33</t>
+          <t>78.99</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-95.95</t>
+          <t>-94.95</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>81654.09745762711</t>
+          <t>81544.9167842031</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4584.0</t>
+          <t>5739.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>9280.4</v>
+        <v>9625.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>8403.9</t>
+          <t>7974.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>7418.64</v>
+        <v>7390.28</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>425.2400559355071</t>
+          <t>279.4693411980216</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-335.0564372059416</t>
+          <t>-522.2695898581487</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>4584.0</t>
+          <t>5739.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>104.09</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>23.2</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>23.25</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>77.42</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>88.17</t>
+          <t>68.82</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.68</v>
+        <v>-1.9</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>22.74</v>
+        <v>22.8</v>
       </c>
       <c r="AN9" t="n">
-        <v>23.26</v>
+        <v>23.25</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>362.90</t>
+          <t>154.33</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-97.51</t>
+          <t>-95.95</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>81654.09745762711</t>
+          <t>81544.9167842031</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>9462.4</v>
+        <v>9280.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>8873.4</t>
+          <t>8403.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>7472.64</v>
+        <v>7418.64</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>876</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>563.475781961225</t>
+          <t>425.2400559355071</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>68.1072250545676</t>
+          <t>-335.0564372059416</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>104.09</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>361.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,79 +4274,79 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-3.93</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>6.64</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>23.95</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-4.13</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-18.48</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>77.42</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>82.37</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>2.35</v>
+        <v>0.68</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.29</v>
+        <v>3.93</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>22.66</v>
+        <v>22.74</v>
       </c>
       <c r="AN10" t="n">
         <v>23.26</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>4280.47</t>
+          <t>362.90</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-99.77</t>
+          <t>-97.51</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>81654.09745762711</t>
+          <t>81544.9167842031</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>9716.799999999999</v>
+        <v>9462.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>11919.9</t>
+          <t>8873.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>7436.54</v>
+        <v>7472.64</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2203</t>
+          <t>589</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>653.54279230789</t>
+          <t>563.475781961225</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>512.0871988176314</t>
+          <t>68.1072250545676</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,22 +4569,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>104.09</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>24.05</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>24.45</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>361.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-35.31</t>
+          <t>-18.48</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>72.03</t>
+          <t>82.37</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>3.56</v>
+        <v>2.35</v>
       </c>
       <c r="AI11" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>22.57</v>
+        <v>22.66</v>
       </c>
       <c r="AN11" t="n">
         <v>23.26</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>430.70</t>
+          <t>4280.47</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-99.77</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>81654.09745762711</t>
+          <t>81544.9167842031</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>9629.200000000001</v>
+        <v>9716.799999999999</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>14884.2</t>
+          <t>11919.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>7449.74</v>
+        <v>7436.54</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-5255</t>
+          <t>-2203</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>679.2619911243006</t>
+          <t>653.54279230789</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>816.5911899499497</t>
+          <t>512.0871988176314</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>104.09</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-5.46</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-51.37</t>
+          <t>-35.31</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>1.13</v>
+        <v>3.56</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.62</v>
+        <v>3.31</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>23.32</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>22.5</v>
+        <v>22.57</v>
       </c>
       <c r="AN12" t="n">
         <v>23.26</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.61</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>160.83</t>
+          <t>430.70</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.65</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>81654.09745762711</t>
+          <t>81544.9167842031</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>6324</v>
+        <v>9629.200000000001</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>13005.4</t>
+          <t>14884.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>7283.74</v>
+        <v>7449.74</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-6681</t>
+          <t>-5255</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>654.2930458832735</t>
+          <t>679.2619911243006</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-343.1385080735217</t>
+          <t>816.5911899499497</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>4013.0</t>
+          <t>23312.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>104.09</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>24.15</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO導電玻璃.xlsx
+++ b/Result/checksun_type/ITO導電玻璃.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>260.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-18.40</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>260</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,51 +1029,51 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.99</v>
+        <v>-0.48</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1.06</v>
+        <v>-1.37</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.01</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>23.38</v>
+        <v>23.33</v>
       </c>
       <c r="AN2" t="n">
-        <v>23.04</v>
+        <v>23.02</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>23.71</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-69.66</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-94.70</t>
+          <t>-95.49</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>81544.9167842031</t>
+          <t>81442.64154929577</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2830.0</t>
+          <t>5953.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4222.6</v>
+        <v>4581.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>5175.0</t>
+          <t>4900.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>6856.42</v>
+        <v>6754.58</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-952</t>
+          <t>-318</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-466.6059811730004</t>
+          <t>-524.5058000014994</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1020.972226216761</t>
+          <t>-842.9548035582447</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2830.0</t>
+          <t>5953.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.84</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1258,17 +1258,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>229.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,84 +1320,84 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.12</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-18.40</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-0.44</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-33.26</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,12 +1436,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>260</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,31 +1455,31 @@
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.95</v>
+        <v>-0.99</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.44</v>
+        <v>-1.06</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.22</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>23.32</v>
+        <v>23.38</v>
       </c>
       <c r="AN3" t="n">
-        <v>23.08</v>
+        <v>23.04</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1488,14 +1488,14 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-26.25</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-94.06</t>
+          <t>-94.70</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>81544.9167842031</t>
+          <t>81442.64154929577</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5300.0</t>
+          <t>2830.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4820.8</v>
+        <v>4222.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>7223.2</t>
+          <t>5175.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>7076.86</v>
+        <v>6856.42</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2402</t>
+          <t>-952</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-365.8121184377713</t>
+          <t>-466.6059811730004</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-904.2123933640405</t>
+          <t>-1020.972226216761</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>5300.0</t>
+          <t>2830.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.84</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1680,14 +1680,14 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>23.3</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
           <t>22.9</t>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>229.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-30.81</t>
+          <t>-33.26</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,67 +1858,67 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>260</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.26</v>
+        <v>-0.95</v>
       </c>
       <c r="AI4" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>-2.66</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>23.22</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>23.71</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-26.25</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
         <v>0.09</v>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>-2.52</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>23.26</t>
-        </is>
-      </c>
-      <c r="AM4" t="n">
-        <v>23.24</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>23.11</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>23.71</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>-6.10</t>
-        </is>
-      </c>
-      <c r="AQ4" t="n">
+      <c r="AR4" t="n">
         <v>0.12</v>
       </c>
-      <c r="AR4" t="n">
-        <v>0.13</v>
-      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>2.01</t>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-93.67</t>
+          <t>-94.06</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>81544.9167842031</t>
+          <t>81442.64154929577</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3758.0</t>
+          <t>5300.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4908.6</v>
+        <v>4820.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>7094.5</t>
+          <t>7223.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>7155.24</v>
+        <v>7076.86</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2185</t>
+          <t>-2402</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-267.9211593602678</t>
+          <t>-365.8121184377713</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-969.7621895257253</t>
+          <t>-904.2123933640405</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>3758.0</t>
+          <t>5300.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.84</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>219.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-30.19</t>
+          <t>-30.81</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.53</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,63 +2280,63 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>260</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>31.41</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.95</v>
+        <v>-0.26</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>23.27</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>23.14</v>
+        <v>23.24</v>
       </c>
       <c r="AN5" t="n">
-        <v>23.13</v>
+        <v>23.11</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.71</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AR5" t="n">
         <v>0.13</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-93.57</t>
+          <t>-93.67</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>81544.9167842031</t>
+          <t>81442.64154929577</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5068.0</t>
+          <t>3758.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>5073.8</v>
+        <v>4908.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>7268.1</t>
+          <t>7094.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>7204.54</v>
+        <v>7155.24</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2194</t>
+          <t>-2185</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-140.3136993301846</t>
+          <t>-267.9211593602678</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-863.5561058450712</t>
+          <t>-969.7621895257253</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>5068.0</t>
+          <t>3758.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.84</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2561,7 +2561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>219.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-30.12</t>
+          <t>-30.19</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-6.75</t>
+          <t>-8.53</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,63 +2702,63 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>260</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>44.31</t>
+          <t>31.41</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.34</v>
+        <v>-0.95</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>23.27</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>23.07</v>
+        <v>23.14</v>
       </c>
       <c r="AN6" t="n">
-        <v>23.17</v>
+        <v>23.13</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>23.69</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR6" t="n">
         <v>0.13</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-93.67</t>
+          <t>-93.57</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>81544.9167842031</t>
+          <t>81442.64154929577</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4157.0</t>
+          <t>5068.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>5218.8</v>
+        <v>5073.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>7467.8</t>
+          <t>7268.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>7306.04</v>
+        <v>7204.54</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2249</t>
+          <t>-2194</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-8.815079963841526</t>
+          <t>-140.3136993301846</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-821.3489825210982</t>
+          <t>-863.5561058450712</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>4157.0</t>
+          <t>5068.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.84</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-22.22</t>
+          <t>-30.12</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-6.75</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>260</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>44.31</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-0.68</v>
+        <v>0.34</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.32</v>
+        <v>1.53</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>22.98</v>
+        <v>23.07</v>
       </c>
       <c r="AN7" t="n">
-        <v>23.19</v>
+        <v>23.17</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>23.69</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="AQ7" t="n">
         <v>0.17</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-94.25</t>
+          <t>-93.67</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>81544.9167842031</t>
+          <t>81442.64154929577</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5821.0</t>
+          <t>4157.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>6127.4</v>
+        <v>5218.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>7878.3</t>
+          <t>7467.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>7309.38</v>
+        <v>7306.04</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1750</t>
+          <t>-2249</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>138.9183568647506</t>
+          <t>-8.815079963841526</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-634.1120569682398</t>
+          <t>-821.3489825210982</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>5821.0</t>
+          <t>4157.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.84</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>-22.22</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>260</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>52.69</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-1.99</v>
+        <v>-0.68</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.44</v>
+        <v>2.32</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>22.88</v>
+        <v>22.98</v>
       </c>
       <c r="AN8" t="n">
-        <v>23.22</v>
+        <v>23.19</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>78.99</t>
+          <t>48.56</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-94.95</t>
+          <t>-94.25</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>81544.9167842031</t>
+          <t>81442.64154929577</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>5739.0</t>
+          <t>5821.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>9625.6</v>
+        <v>6127.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7974.8</t>
+          <t>7878.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>7390.28</v>
+        <v>7309.38</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>-1750</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>279.4693411980216</t>
+          <t>138.9183568647506</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-522.2695898581487</t>
+          <t>-634.1120569682398</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>5739.0</t>
+          <t>5821.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.84</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3795,17 +3795,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,50 +3968,50 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>260</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>38.71</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>68.82</t>
+          <t>52.69</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>-1.9</v>
+        <v>-1.99</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.92</v>
+        <v>3.44</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>22.8</v>
+        <v>22.88</v>
       </c>
       <c r="AN9" t="n">
-        <v>23.25</v>
+        <v>23.22</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4020,14 +4020,14 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>154.33</t>
+          <t>78.99</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-95.95</t>
+          <t>-94.95</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>81544.9167842031</t>
+          <t>81442.64154929577</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4584.0</t>
+          <t>5739.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>9280.4</v>
+        <v>9625.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>8403.9</t>
+          <t>7974.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>7418.64</v>
+        <v>7390.28</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>425.2400559355071</t>
+          <t>279.4693411980216</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-335.0564372059416</t>
+          <t>-522.2695898581487</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>4584.0</t>
+          <t>5739.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.84</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>23.2</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>23.25</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>260</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>77.42</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>88.17</t>
+          <t>68.82</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.68</v>
+        <v>-1.9</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>22.74</v>
+        <v>22.8</v>
       </c>
       <c r="AN10" t="n">
-        <v>23.26</v>
+        <v>23.25</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>362.90</t>
+          <t>154.33</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-97.51</t>
+          <t>-95.95</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>81544.9167842031</t>
+          <t>81442.64154929577</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>9462.4</v>
+        <v>9280.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>8873.4</t>
+          <t>8403.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>7472.64</v>
+        <v>7418.64</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>876</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>563.475781961225</t>
+          <t>425.2400559355071</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>68.1072250545676</t>
+          <t>-335.0564372059416</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.84</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>361.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,79 +4696,79 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-3.93</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-1.12</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>6.64</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>23.95</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-4.59</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-18.48</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>23.0</t>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>260</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>77.42</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>82.37</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>2.35</v>
+        <v>0.68</v>
       </c>
       <c r="AI11" t="n">
-        <v>3.29</v>
+        <v>3.93</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>22.66</v>
+        <v>22.74</v>
       </c>
       <c r="AN11" t="n">
         <v>23.26</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>23.66</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>4280.47</t>
+          <t>362.90</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-99.77</t>
+          <t>-97.51</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>81544.9167842031</t>
+          <t>81442.64154929577</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>9716.799999999999</v>
+        <v>9462.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>11919.9</t>
+          <t>8873.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>7436.54</v>
+        <v>7472.64</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2203</t>
+          <t>589</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>653.54279230789</t>
+          <t>563.475781961225</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>512.0871988176314</t>
+          <t>68.1072250545676</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>8700.0</t>
+          <t>5793.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.84</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>24.05</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>24.45</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.75</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>361.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-35.31</t>
+          <t>-18.48</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>260</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>72.03</t>
+          <t>82.37</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>3.56</v>
+        <v>2.35</v>
       </c>
       <c r="AI12" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>22.57</v>
+        <v>22.66</v>
       </c>
       <c r="AN12" t="n">
         <v>23.26</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>430.70</t>
+          <t>4280.47</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-99.77</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>81544.9167842031</t>
+          <t>81442.64154929577</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>9629.200000000001</v>
+        <v>9716.799999999999</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>14884.2</t>
+          <t>11919.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>7449.74</v>
+        <v>7436.54</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-5255</t>
+          <t>-2203</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>679.2619911243006</t>
+          <t>653.54279230789</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>816.5911899499497</t>
+          <t>512.0871988176314</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>23312.0</t>
+          <t>8700.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.84</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/ITO導電玻璃.xlsx
+++ b/Result/checksun_type/ITO導電玻璃.xlsx
@@ -923,12 +923,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -938,84 +938,84 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>23.9</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>17.62</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-1.27</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-4.85</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,22 +1068,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1094,63 +1094,63 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6,801</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-1.3</v>
+        <v>-0.72</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.14</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>23.3</v>
+        <v>23.31</v>
       </c>
       <c r="AV2" t="n">
-        <v>23</v>
+        <v>22.99</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-81.34</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.08</v>
@@ -1172,43 +1172,43 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>81339.02742616033</t>
+          <t>81258.02317415731</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>5182.0</t>
+          <t>15776.0</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>4604.6</v>
+        <v>7008.2</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>4839.2</t>
+          <t>5958.4</t>
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>6785.7</v>
+        <v>6912.06</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-234</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>-559.9808673256268</t>
+          <t>-455.3936028144808</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-755.0937376083275</t>
+          <t>119.8363519968225</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>5182.0</t>
+          <t>15776.0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1273,22 +1273,22 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>108.64</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>90.81</t>
+          <t>90.23</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1385,167 +1385,167 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>224.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-4.85</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-8.73</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>10.87</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>22.15</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2025/07/08</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>22.75</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>260.0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.43</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-1.27</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-6.50</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-9.13</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>10.87</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>22.15</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>2025/07/08</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1556,50 +1556,50 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6,801</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>-0.48</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-1.37</v>
+        <v>-1.3</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>23.33</v>
+        <v>23.3</v>
       </c>
       <c r="AV3" t="n">
-        <v>23.02</v>
+        <v>23</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1608,14 +1608,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-69.66</t>
+          <t>-81.34</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-95.49</t>
+          <t>-96.25</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1634,43 +1634,43 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>81339.02742616033</t>
+          <t>81258.02317415731</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>5953.0</t>
+          <t>5182.0</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>4581.8</v>
+        <v>4604.6</v>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>4900.3</t>
+          <t>4839.2</t>
         </is>
       </c>
       <c r="BH3" t="n">
-        <v>6754.58</v>
+        <v>6785.7</v>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-318</t>
+          <t>-234</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-524.5058000014994</t>
+          <t>-559.9808673256268</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-842.9548035582447</t>
+          <t>-755.0937376083275</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>5953.0</t>
+          <t>5182.0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>108.64</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>90.81</t>
+          <t>90.23</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1800,22 +1800,22 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>260.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1872,17 +1872,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-18.40</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1992,22 +1992,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -2018,12 +2018,12 @@
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6,801</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2033,51 +2033,51 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>-0.99</v>
+        <v>-0.48</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-1.06</v>
+        <v>-1.37</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.01</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>23.38</v>
+        <v>23.33</v>
       </c>
       <c r="AV4" t="n">
-        <v>23.04</v>
+        <v>23.02</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>23.71</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-69.66</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-94.70</t>
+          <t>-95.49</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2096,43 +2096,43 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>81339.02742616033</t>
+          <t>81258.02317415731</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2830.0</t>
+          <t>5953.0</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>4222.6</v>
+        <v>4581.8</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>5175.0</t>
+          <t>4900.3</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>6856.42</v>
+        <v>6754.58</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-952</t>
+          <t>-318</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-466.6059811730004</t>
+          <t>-524.5058000014994</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-1020.972226216761</t>
+          <t>-842.9548035582447</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>2830.0</t>
+          <t>5953.0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>108.64</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>90.81</t>
+          <t>90.23</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2262,17 +2262,17 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>229.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2324,84 +2324,84 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4.18</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-18.40</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-1.27</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-33.26</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2480,12 +2480,12 @@
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6,801</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2499,31 +2499,31 @@
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>-0.95</v>
+        <v>-0.99</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.44</v>
+        <v>-1.06</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>23.22</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>23.32</v>
+        <v>23.38</v>
       </c>
       <c r="AV5" t="n">
-        <v>23.08</v>
+        <v>23.04</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -2532,14 +2532,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-26.25</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-94.06</t>
+          <t>-94.70</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2558,43 +2558,43 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>81339.02742616033</t>
+          <t>81258.02317415731</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>5300.0</t>
+          <t>2830.0</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>4820.8</v>
+        <v>4222.6</v>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>7223.2</t>
+          <t>5175.0</t>
         </is>
       </c>
       <c r="BH5" t="n">
-        <v>7076.86</v>
+        <v>6856.42</v>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-2402</t>
+          <t>-952</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-365.8121184377713</t>
+          <t>-466.6059811730004</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-904.2123933640405</t>
+          <t>-1020.972226216761</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>5300.0</t>
+          <t>2830.0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>108.64</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>90.81</t>
+          <t>90.23</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2724,14 +2724,14 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
-        <is>
-          <t>23.3</t>
-        </is>
-      </c>
       <c r="CN5" t="inlineStr">
         <is>
           <t>22.9</t>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>229.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2796,142 +2796,142 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-0.73</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-33.26</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>-8.73</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>10.87</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>22.15</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>2025/07/08</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>22.75</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>2.98</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
           <t>-0.87</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-1.27</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-30.81</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>-7.94</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>10.87</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>22.15</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>2025/07/08</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0.88</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2942,67 +2942,67 @@
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6,801</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>-0.26</v>
+        <v>-0.95</v>
       </c>
       <c r="AQ6" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>-2.66</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>23.22</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>23.71</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>-26.25</t>
+        </is>
+      </c>
+      <c r="AY6" t="n">
         <v>0.09</v>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>-2.52</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>23.26</t>
-        </is>
-      </c>
-      <c r="AU6" t="n">
-        <v>23.24</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>23.11</v>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>23.71</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>-6.10</t>
-        </is>
-      </c>
-      <c r="AY6" t="n">
+      <c r="AZ6" t="n">
         <v>0.12</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>0.13</v>
-      </c>
       <c r="BA6" t="inlineStr">
         <is>
           <t>2.01</t>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-93.67</t>
+          <t>-94.06</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -3020,43 +3020,43 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>81339.02742616033</t>
+          <t>81258.02317415731</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>3758.0</t>
+          <t>5300.0</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>4908.6</v>
+        <v>4820.8</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>7094.5</t>
+          <t>7223.2</t>
         </is>
       </c>
       <c r="BH6" t="n">
-        <v>7155.24</v>
+        <v>7076.86</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>-2185</t>
+          <t>-2402</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-267.9211593602678</t>
+          <t>-365.8121184377713</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-969.7621895257253</t>
+          <t>-904.2123933640405</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>3758.0</t>
+          <t>5300.0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>108.64</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>90.81</t>
+          <t>90.23</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
@@ -3223,7 +3223,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>219.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3258,17 +3258,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-30.19</t>
+          <t>-30.81</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.53</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3378,22 +3378,22 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3404,63 +3404,63 @@
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6,801</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>31.41</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>-0.95</v>
+        <v>-0.26</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>23.27</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>23.14</v>
+        <v>23.24</v>
       </c>
       <c r="AV7" t="n">
-        <v>23.13</v>
+        <v>23.11</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.71</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.13</v>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-93.57</t>
+          <t>-93.67</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3482,43 +3482,43 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>81339.02742616033</t>
+          <t>81258.02317415731</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>5068.0</t>
+          <t>3758.0</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>5073.8</v>
+        <v>4908.6</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>7268.1</t>
+          <t>7094.5</t>
         </is>
       </c>
       <c r="BH7" t="n">
-        <v>7204.54</v>
+        <v>7155.24</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-2194</t>
+          <t>-2185</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-140.3136993301846</t>
+          <t>-267.9211593602678</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-863.5561058450712</t>
+          <t>-969.7621895257253</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>5068.0</t>
+          <t>3758.0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>108.64</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>90.81</t>
+          <t>90.23</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>219.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-30.12</t>
+          <t>-30.19</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-6.75</t>
+          <t>-8.53</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3840,22 +3840,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3866,63 +3866,63 @@
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6,801</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>44.31</t>
+          <t>31.41</t>
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>0.34</v>
+        <v>-0.95</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>23.27</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>23.07</v>
+        <v>23.14</v>
       </c>
       <c r="AV8" t="n">
-        <v>23.17</v>
+        <v>23.13</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>23.69</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AZ8" t="n">
         <v>0.13</v>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-93.67</t>
+          <t>-93.57</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3944,43 +3944,43 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>81339.02742616033</t>
+          <t>81258.02317415731</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>4157.0</t>
+          <t>5068.0</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>5218.8</v>
+        <v>5073.8</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>7467.8</t>
+          <t>7268.1</t>
         </is>
       </c>
       <c r="BH8" t="n">
-        <v>7306.04</v>
+        <v>7204.54</v>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-2249</t>
+          <t>-2194</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-8.815079963841526</t>
+          <t>-140.3136993301846</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-821.3489825210982</t>
+          <t>-863.5561058450712</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>4157.0</t>
+          <t>5068.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>108.64</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>90.81</t>
+          <t>90.23</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4110,22 +4110,22 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4182,17 +4182,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-22.22</t>
+          <t>-30.12</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-6.75</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4302,22 +4302,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4328,66 +4328,66 @@
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6,801</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>44.31</t>
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>-0.68</v>
+        <v>0.34</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.32</v>
+        <v>1.53</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>22.98</v>
+        <v>23.07</v>
       </c>
       <c r="AV9" t="n">
-        <v>23.19</v>
+        <v>23.17</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>23.69</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="AY9" t="n">
         <v>0.17</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-94.25</t>
+          <t>-93.67</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4406,43 +4406,43 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>81339.02742616033</t>
+          <t>81258.02317415731</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>5821.0</t>
+          <t>4157.0</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>6127.4</v>
+        <v>5218.8</v>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>7878.3</t>
+          <t>7467.8</t>
         </is>
       </c>
       <c r="BH9" t="n">
-        <v>7309.38</v>
+        <v>7306.04</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-1750</t>
+          <t>-2249</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>138.9183568647506</t>
+          <t>-8.815079963841526</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-634.1120569682398</t>
+          <t>-821.3489825210982</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>5821.0</t>
+          <t>4157.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>108.64</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>90.81</t>
+          <t>90.23</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4572,22 +4572,22 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4644,17 +4644,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>20.70</t>
+          <t>-22.22</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4790,66 +4790,66 @@
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6,801</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>52.69</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="AP10" t="n">
-        <v>-1.99</v>
+        <v>-0.68</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.44</v>
+        <v>2.32</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>22.88</v>
+        <v>22.98</v>
       </c>
       <c r="AV10" t="n">
-        <v>23.22</v>
+        <v>23.19</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>78.99</t>
+          <t>48.56</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-94.95</t>
+          <t>-94.25</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4868,43 +4868,43 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>81339.02742616033</t>
+          <t>81258.02317415731</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>5739.0</t>
+          <t>5821.0</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>9625.6</v>
+        <v>6127.4</v>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>7974.8</t>
+          <t>7878.3</t>
         </is>
       </c>
       <c r="BH10" t="n">
-        <v>7390.28</v>
+        <v>7309.38</v>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>-1750</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>279.4693411980216</t>
+          <t>138.9183568647506</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-522.2695898581487</t>
+          <t>-634.1120569682398</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>5739.0</t>
+          <t>5821.0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>108.64</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>90.81</t>
+          <t>90.23</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5039,17 +5039,17 @@
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5106,17 +5106,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -5252,50 +5252,50 @@
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6,801</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>38.71</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>68.82</t>
+          <t>52.69</t>
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>-1.9</v>
+        <v>-1.99</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3.92</v>
+        <v>3.44</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>22.8</v>
+        <v>22.88</v>
       </c>
       <c r="AV11" t="n">
-        <v>23.25</v>
+        <v>23.22</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
@@ -5304,14 +5304,14 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>154.33</t>
+          <t>78.99</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-95.95</t>
+          <t>-94.95</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5330,43 +5330,43 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>81339.02742616033</t>
+          <t>81258.02317415731</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>4584.0</t>
+          <t>5739.0</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>9280.4</v>
+        <v>9625.6</v>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>8403.9</t>
+          <t>7974.8</t>
         </is>
       </c>
       <c r="BH11" t="n">
-        <v>7418.64</v>
+        <v>7390.28</v>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>425.2400559355071</t>
+          <t>279.4693411980216</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-335.0564372059416</t>
+          <t>-522.2695898581487</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>4584.0</t>
+          <t>5739.0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>108.64</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>90.81</t>
+          <t>90.23</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5496,22 +5496,22 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CO11" t="inlineStr">
+        <is>
           <t>23.2</t>
-        </is>
-      </c>
-      <c r="CO11" t="inlineStr">
-        <is>
-          <t>23.25</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>196.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-7.74</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5688,22 +5688,22 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5714,66 +5714,66 @@
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6,801</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>77.42</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>88.17</t>
+          <t>68.82</t>
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>0.68</v>
+        <v>-1.9</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>22.74</v>
+        <v>22.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>23.26</v>
+        <v>23.25</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>362.90</t>
+          <t>154.33</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-97.51</t>
+          <t>-95.95</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5792,43 +5792,43 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>81339.02742616033</t>
+          <t>81258.02317415731</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>9462.4</v>
+        <v>9280.4</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>8873.4</t>
+          <t>8403.9</t>
         </is>
       </c>
       <c r="BH12" t="n">
-        <v>7472.64</v>
+        <v>7418.64</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>876</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>563.475781961225</t>
+          <t>425.2400559355071</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>68.1072250545676</t>
+          <t>-335.0564372059416</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>5793.0</t>
+          <t>4584.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>104.55</t>
+          <t>108.64</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>90.81</t>
+          <t>90.23</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>1636</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>23.85</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">

--- a/Result/checksun_type/ITO導電玻璃.xlsx
+++ b/Result/checksun_type/ITO導電玻璃.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,325 +1068,345 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>22.15</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2025/07/08</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>22.75</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>8.62</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>3.49</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>6,801</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>7463</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>38.89</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>3.28</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AU2" t="n">
         <v>-0.72</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>1.38</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>-3.01</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>23.14</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>23.31</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>22.99</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>-0.06</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>0.08</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>0.08</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>2.01</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-96.25</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>81258.02317415731</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>15776.0</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>7008.2</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>5958.4</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>6912.06</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>1049</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>-455.3936028144808</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>119.8363519968225</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>15776.0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
         <is>
           <t>23.05</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>2025/12/05</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>3.69</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>-13.42998910113004</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>-25.43417574544826</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>-6.333574654154932</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價漲量增</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>108.64</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>19.70%</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>-0.85%</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>90.23</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>1636</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>安可-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>24.0</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>23.9</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>32.99</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>** 平面顯示器 - ITO導電基板** 觸控面板 - ITO導電玻璃** LED照明產業 - 藍寶石晶圓/晶片</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1510,325 +1550,345 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>22.15</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2025/07/08</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>22.75</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>2.91</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>-1.74</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>6,801</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>7463</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>16.67</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>5.56</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
         <v>-1.3</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>-3.03</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
         <v>23.3</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>23</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>23.72</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>-81.34</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>0.01</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>0.08</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>2.01</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-96.25</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>81258.02317415731</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>5182.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>4604.6</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>4839.2</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>6785.7</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>-234</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>-559.9808673256268</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-755.0937376083275</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>5182.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
         <is>
           <t>23.05</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2025/12/05</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>-0.22</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>-13.42998910113004</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>-25.43417574544826</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>-6.333574654154932</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>0.70</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>108.64</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>19.70%</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>-0.85%</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>90.23</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>1636</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>安可-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>23.4</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>32.99</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>** 平面顯示器 - ITO導電基板** 觸控面板 - ITO導電玻璃** LED照明產業 - 藍寶石晶圓/晶片</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1972,325 +2032,345 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>22.15</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2025/07/08</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>22.75</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>3.38</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>0.23</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>6,801</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>7463</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>-0.48</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AU4" t="n">
         <v>-1.37</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>1.34</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>-2.93</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>23.01</t>
         </is>
       </c>
-      <c r="AU4" t="n">
+      <c r="AY4" t="n">
         <v>23.33</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>23.02</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>23.72</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>-69.66</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>0.03</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>0.09</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>2.01</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-95.49</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>81258.02317415731</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>5953.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>4581.8</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>4900.3</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>6754.58</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>-318</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-524.5058000014994</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-842.9548035582447</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>5953.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
         <is>
           <t>23.05</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>2025/12/05</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>-0.65</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>-13.42998910113004</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>-25.43417574544826</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>-6.333574654154932</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>108.64</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>19.70%</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>-0.85%</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>90.23</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>1636</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>安可-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>22.9</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>23.05</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>22.7</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>22.9</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>32.99</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>** 平面顯示器 - ITO導電基板** 觸控面板 - ITO導電玻璃** LED照明產業 - 藍寶石晶圓/晶片</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2434,325 +2514,345 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>22.15</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2025/07/08</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>22.75</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>1.60</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>-1.31</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>6,801</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>7463</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>4.55</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>-0.99</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
         <v>-1.06</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>-2.83</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>23.13</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>23.38</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>23.04</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>23.71</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>-48.83</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>0.05</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>0.11</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>2.01</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-94.70</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>81258.02317415731</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>2830.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>4222.6</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>5175.0</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>6856.42</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>-952</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-466.6059811730004</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-1020.972226216761</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>2830.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
         <is>
           <t>23.05</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>2025/12/05</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>-0.65</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>-13.42998910113004</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>-25.43417574544826</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>-6.333574654154932</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>108.64</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>19.70%</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>-0.85%</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>90.23</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>1636</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>安可-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>22.9</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>22.9</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>32.99</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>** 平面顯示器 - ITO導電基板** 觸控面板 - ITO導電玻璃** LED照明產業 - 藍寶石晶圓/晶片</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2896,325 +2996,345 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>22.15</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2025/07/08</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>22.75</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>2.98</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>-0.87</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>6,801</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>7463</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>4.55</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>-0.95</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AU6" t="n">
         <v>-0.44</v>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>1.05</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>-2.66</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>23.22</t>
         </is>
       </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
         <v>23.32</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>23.08</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>23.71</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>-26.25</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>0.09</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>0.12</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>2.01</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-94.06</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>81258.02317415731</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>5300.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>4820.8</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>7223.2</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>7076.86</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>-2402</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-365.8121184377713</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-904.2123933640405</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>5300.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
         <is>
           <t>23.05</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>2025/12/05</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>-0.22</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>-13.42998910113004</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>-25.43417574544826</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>-6.333574654154932</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>0.70</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>108.64</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>19.70%</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>-0.85%</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>90.23</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>1636</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>安可-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>23.3</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>22.9</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>32.99</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>** 平面顯示器 - ITO導電基板** 觸控面板 - ITO導電玻璃** LED照明產業 - 藍寶石晶圓/晶片</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3358,325 +3478,345 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>22.15</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2025/07/08</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>22.75</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>2.12</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>0.88</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>6,801</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>7463</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>13.64</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>19.82</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>-0.26</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AU7" t="n">
         <v>0.09</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>0.56</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>-2.52</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>23.26</t>
         </is>
       </c>
-      <c r="AU7" t="n">
+      <c r="AY7" t="n">
         <v>23.24</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>23.11</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>23.71</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>-6.10</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>0.12</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>0.13</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>2.01</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-93.67</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>81258.02317415731</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>3758.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>4908.6</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>7094.5</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>7155.24</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>-2185</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-267.9211593602678</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-969.7621895257253</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>3758.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
         <is>
           <t>23.05</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2025/12/05</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>0.65</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>-13.42998910113004</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>-25.43417574544826</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>-6.333574654154932</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>0.70</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>108.64</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>19.70%</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>-0.85%</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>90.23</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>1636</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>安可-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>23.15</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>23.3</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>22.9</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>32.99</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>** 平面顯示器 - ITO導電基板** 觸控面板 - ITO導電玻璃** LED照明產業 - 藍寶石晶圓/晶片</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3820,325 +3960,345 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>22.15</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2025/07/08</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>22.75</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>2.85</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>-1.73</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>6,801</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>7463</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>31.41</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>-0.95</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>0.03</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>-2.39</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>23.27</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>23.14</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>23.13</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>6.41</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>0.14</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>0.13</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>2.01</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>-93.57</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>81258.02317415731</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>5068.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>5073.8</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>7268.1</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BL8" t="n">
         <v>7204.54</v>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>-2194</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-140.3136993301846</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-863.5561058450712</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>5068.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
         <is>
           <t>23.05</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2025/12/05</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>-13.42998910113004</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>-25.43417574544826</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>-6.333574654154932</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>0.70</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>108.64</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>19.70%</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>-0.85%</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>90.23</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>1636</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>安可-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>23.5</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>23.55</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>22.95</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>23.05</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>32.99</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>** 平面顯示器 - ITO導電基板** 觸控面板 - ITO導電玻璃** LED照明產業 - 藍寶石晶圓/晶片</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4282,325 +4442,345 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>22.15</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2025/07/08</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>22.75</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>2.30</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>0.44</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>6,801</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>7463</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>45.83</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>44.31</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>0.34</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AU9" t="n">
         <v>1.53</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>-0.43</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>-2.21</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>23.42</t>
         </is>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
         <v>23.07</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>23.17</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>23.69</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>36.65</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>0.17</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>0.13</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>2.01</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-93.67</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>81258.02317415731</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>4157.0</t>
         </is>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>5218.8</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>7467.8</t>
         </is>
       </c>
-      <c r="BH9" t="n">
+      <c r="BL9" t="n">
         <v>7306.04</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>-2249</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-8.815079963841526</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-821.3489825210982</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>4157.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
         <is>
           <t>23.05</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>2025/12/05</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>1.95</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>-13.42998910113004</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>-25.43417574544826</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>-6.333574654154932</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>0.71</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
         <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>108.64</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>19.70%</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>-0.85%</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>90.23</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>1636</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>安可-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>23.45</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>23.65</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>23.25</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>23.5</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>32.99</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>** 平面顯示器 - ITO導電基板** 觸控面板 - ITO導電玻璃** LED照明產業 - 藍寶石晶圓/晶片</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4744,325 +4924,345 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>22.15</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2025/07/08</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>22.75</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>3.23</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>-1.49</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>6,801</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>7463</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>48.39</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>43.01</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>-0.68</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AU10" t="n">
         <v>2.32</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>-0.92</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>-2.07</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>23.51</t>
         </is>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY10" t="n">
         <v>22.98</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>23.19</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>23.68</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>48.56</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>0.17</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>0.12</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>2.01</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-94.25</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>81258.02317415731</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>5821.0</t>
         </is>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>6127.4</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>7878.3</t>
         </is>
       </c>
-      <c r="BH10" t="n">
+      <c r="BL10" t="n">
         <v>7309.38</v>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>-1750</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>138.9183568647506</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-634.1120569682398</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>5821.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
         <is>
           <t>23.05</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2025/12/05</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>1.30</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>-13.42998910113004</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>-25.43417574544826</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>-6.333574654154932</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>0.71</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
         <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>108.64</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>19.70%</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>-0.85%</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>90.23</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>1636</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>安可-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>23.15</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>23.95</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>23.1</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>23.35</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>32.99</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>** 平面顯示器 - ITO導電基板** 觸控面板 - ITO導電玻璃** LED照明產業 - 藍寶石晶圓/晶片</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5206,325 +5406,345 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>22.15</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2025/07/08</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>22.75</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>3.23</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>0.87</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>6,801</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>7463</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>38.71</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>52.69</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>-1.99</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AU11" t="n">
         <v>3.44</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>-1.46</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>-1.90</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>23.67</t>
         </is>
       </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>22.88</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>23.22</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>23.67</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>78.99</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>0.18</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>0.1</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>2.01</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-94.95</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>81258.02317415731</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>5739.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>9625.6</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>7974.8</t>
         </is>
       </c>
-      <c r="BH11" t="n">
+      <c r="BL11" t="n">
         <v>7390.28</v>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>1650</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>279.4693411980216</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-522.2695898581487</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>5739.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
         <is>
           <t>23.05</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>2025/12/05</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>0.65</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>-13.42998910113004</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>-25.43417574544826</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>-6.333574654154932</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>0.70</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>108.64</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>19.70%</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>-0.85%</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>90.23</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>1636</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>安可-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>23.15</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>23.25</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>22.95</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>32.99</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>** 平面顯示器 - ITO導電基板** 觸控面板 - ITO導電玻璃** LED照明產業 - 藍寶石晶圓/晶片</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5668,325 +5888,345 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>2025/10/14</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>22.15</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2025/07/08</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>22.75</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>2.55</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>-2.37</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>6,801</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>7463</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>41.94</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>68.82</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>-1.9</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
         <v>3.92</v>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>-1.9</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>-1.79</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>23.7</t>
         </is>
       </c>
-      <c r="AU12" t="n">
+      <c r="AY12" t="n">
         <v>22.8</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
         <v>23.25</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>23.67</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>154.33</t>
         </is>
       </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="n">
         <v>0.21</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>0.08</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>2.01</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>-95.95</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/11/13</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>81258.02317415731</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>4584.0</t>
         </is>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>9280.4</v>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>8403.9</t>
         </is>
       </c>
-      <c r="BH12" t="n">
+      <c r="BL12" t="n">
         <v>7418.64</v>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>876</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>425.2400559355071</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-335.0564372059416</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>4584.0</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
         <is>
           <t>23.05</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>2025/12/05</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>0.87</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>安可</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>光電業</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>-13.42998910113004</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>-25.43417574544826</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>-6.333574654154932</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>0.70</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>3.47</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>108.64</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>19.70%</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>-0.85%</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>90.23</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>1636</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>光電產品73.41%、化學製品25.52%、其他1.07% (2024年)</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>安可-光電業-上櫃</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>光電業平上櫃</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>23.85</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>23.85</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>23.25</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>32.99</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>** 平面顯示器 - ITO導電基板** 觸控面板 - ITO導電玻璃** LED照明產業 - 藍寶石晶圓/晶片</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/ITO導電玻璃.xlsx
+++ b/Result/checksun_type/ITO導電玻璃.xlsx
@@ -933,7 +933,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b2】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>663.0</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>17.62</t>
+          <t>32.59</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,63 +1134,63 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>6,801</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>735</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>68.89</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>3.28</v>
+        <v>2.15</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.72</v>
+        <v>-0.09</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>23.14</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>23.31</v>
+        <v>23.32</v>
       </c>
       <c r="AZ2" t="n">
-        <v>22.99</v>
+        <v>22.98</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.71</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>37.60</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="BD2" t="n">
         <v>0.08</v>
@@ -1202,53 +1202,53 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-96.25</t>
+          <t>-95.86</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>81258.02317415731</t>
+          <t>81181.22650771389</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>15776.0</t>
+          <t>17668.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>7008.2</v>
+        <v>9481.799999999999</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>5958.4</t>
+          <t>7151.3</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>6912.06</v>
+        <v>7185.22</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-455.3936028144808</t>
+          <t>-251.3035860860211</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>119.8363519968225</t>
+          <t>871.1915059205076</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>15776.0</t>
+          <t>17668.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>108.64</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>90.23</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,172 +1440,172 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>23.9</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.42</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>17.62</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>3.77</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-4.85</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-5.16</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>10.87</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>22.15</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2025/07/08</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>22.75</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>25.2</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-8.73</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>10.87</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>22.15</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2025/07/08</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2025/09/05</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,63 +1616,63 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>6,801</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>735</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AU3" t="n">
-        <v>-1.3</v>
+        <v>-0.72</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.14</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>23.3</v>
+        <v>23.31</v>
       </c>
       <c r="AZ3" t="n">
-        <v>23</v>
+        <v>22.99</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-81.34</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="BD3" t="n">
         <v>0.08</v>
@@ -1689,48 +1689,48 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>81258.02317415731</t>
+          <t>81181.22650771389</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>5182.0</t>
+          <t>15776.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>4604.6</v>
+        <v>7008.2</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>4839.2</t>
+          <t>5958.4</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>6785.7</v>
+        <v>6912.06</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-234</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-559.9808673256268</t>
+          <t>-455.3936028144808</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-755.0937376083275</t>
+          <t>119.8363519968225</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>5182.0</t>
+          <t>15776.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1795,17 +1795,17 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>108.64</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>90.23</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,187 +1907,187 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>224.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-4.85</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-8.73</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>10.87</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>260.0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>4.18</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-6.50</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>22.15</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/07/08</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>22.75</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>25.2</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-9.13</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>10.87</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>22.15</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/07/08</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2025/09/05</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,50 +2098,50 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>6,801</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>735</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-0.48</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>-1.37</v>
+        <v>-1.3</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>23.33</v>
+        <v>23.3</v>
       </c>
       <c r="AZ4" t="n">
-        <v>23.02</v>
+        <v>23</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2150,14 +2150,14 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-69.66</t>
+          <t>-81.34</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,53 +2166,53 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-95.49</t>
+          <t>-96.25</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>81258.02317415731</t>
+          <t>81181.22650771389</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>5953.0</t>
+          <t>5182.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>4581.8</v>
+        <v>4604.6</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>4900.3</t>
+          <t>4839.2</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>6754.58</v>
+        <v>6785.7</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-318</t>
+          <t>-234</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-524.5058000014994</t>
+          <t>-559.9808673256268</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-842.9548035582447</t>
+          <t>-755.0937376083275</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>5953.0</t>
+          <t>5182.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>108.64</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>90.23</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>260.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-18.40</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,12 +2580,12 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>6,801</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>735</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2595,51 +2595,51 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-0.99</v>
+        <v>-0.48</v>
       </c>
       <c r="AU5" t="n">
-        <v>-1.06</v>
+        <v>-1.37</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.01</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>23.38</v>
+        <v>23.33</v>
       </c>
       <c r="AZ5" t="n">
-        <v>23.04</v>
+        <v>23.02</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>23.71</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-69.66</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,53 +2648,53 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-94.70</t>
+          <t>-95.49</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>81258.02317415731</t>
+          <t>81181.22650771389</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>2830.0</t>
+          <t>5953.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>4222.6</v>
+        <v>4581.8</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>5175.0</t>
+          <t>4900.3</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>6856.42</v>
+        <v>6754.58</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-952</t>
+          <t>-318</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-466.6059811730004</t>
+          <t>-524.5058000014994</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-1020.972226216761</t>
+          <t>-842.9548035582447</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>2830.0</t>
+          <t>5953.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>108.64</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>90.23</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,17 +2824,17 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>229.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,172 +2886,172 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3.78</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-18.40</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>3.77</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-33.26</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>-9.13</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>10.87</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>22.15</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2025/07/08</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>22.75</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>25.2</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>-8.73</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>10.87</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>22.15</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>2025/07/08</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>2025/09/05</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,12 +3062,12 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>6,801</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>735</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -3081,31 +3081,31 @@
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-0.95</v>
+        <v>-0.99</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.44</v>
+        <v>-1.06</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>23.22</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>23.32</v>
+        <v>23.38</v>
       </c>
       <c r="AZ6" t="n">
-        <v>23.08</v>
+        <v>23.04</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -3114,14 +3114,14 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-26.25</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,53 +3130,53 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-94.06</t>
+          <t>-94.70</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>81258.02317415731</t>
+          <t>81181.22650771389</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>5300.0</t>
+          <t>2830.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>4820.8</v>
+        <v>4222.6</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>7223.2</t>
+          <t>5175.0</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>7076.86</v>
+        <v>6856.42</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-2402</t>
+          <t>-952</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-365.8121184377713</t>
+          <t>-466.6059811730004</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-904.2123933640405</t>
+          <t>-1020.972226216761</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>5300.0</t>
+          <t>2830.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>108.64</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>90.23</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,14 +3306,14 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
-        <is>
-          <t>23.3</t>
-        </is>
-      </c>
       <c r="CR6" t="inlineStr">
         <is>
           <t>22.9</t>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>229.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,172 +3368,172 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-33.26</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-8.73</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>10.87</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>22.15</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2025/07/08</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>22.75</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2.93</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-30.81</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>25.2</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>-7.94</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>10.87</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>22.15</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2025/07/08</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>2025/09/05</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,67 +3544,67 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>6,801</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>735</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-0.26</v>
+        <v>-0.95</v>
       </c>
       <c r="AU7" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>-2.66</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>23.22</t>
+        </is>
+      </c>
+      <c r="AY7" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>23.71</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-26.25</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
         <v>0.09</v>
       </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>-2.52</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>23.26</t>
-        </is>
-      </c>
-      <c r="AY7" t="n">
-        <v>23.24</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>23.11</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>23.71</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-6.10</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
+      <c r="BD7" t="n">
         <v>0.12</v>
       </c>
-      <c r="BD7" t="n">
-        <v>0.13</v>
-      </c>
       <c r="BE7" t="inlineStr">
         <is>
           <t>2.01</t>
@@ -3612,53 +3612,53 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-93.67</t>
+          <t>-94.06</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>81258.02317415731</t>
+          <t>81181.22650771389</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>3758.0</t>
+          <t>5300.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>4908.6</v>
+        <v>4820.8</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>7094.5</t>
+          <t>7223.2</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>7155.24</v>
+        <v>7076.86</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-2185</t>
+          <t>-2402</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-267.9211593602678</t>
+          <t>-365.8121184377713</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-969.7621895257253</t>
+          <t>-904.2123933640405</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>3758.0</t>
+          <t>5300.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>108.64</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>90.23</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>219.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-30.19</t>
+          <t>-30.81</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.53</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,63 +4026,63 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>6,801</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>735</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.64</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>31.41</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-0.95</v>
+        <v>-0.26</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.27</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>23.14</v>
+        <v>23.24</v>
       </c>
       <c r="AZ8" t="n">
-        <v>23.13</v>
+        <v>23.11</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.71</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>-6.10</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BD8" t="n">
         <v>0.13</v>
@@ -4094,53 +4094,53 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-93.57</t>
+          <t>-93.67</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>81258.02317415731</t>
+          <t>81181.22650771389</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>5068.0</t>
+          <t>3758.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>5073.8</v>
+        <v>4908.6</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>7268.1</t>
+          <t>7094.5</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>7204.54</v>
+        <v>7155.24</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-2194</t>
+          <t>-2185</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-140.3136993301846</t>
+          <t>-267.9211593602678</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-863.5561058450712</t>
+          <t>-969.7621895257253</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>5068.0</t>
+          <t>3758.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>108.64</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>90.23</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4307,7 +4307,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>177.0</t>
+          <t>219.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-30.12</t>
+          <t>-30.19</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.75</t>
+          <t>-8.53</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,63 +4508,63 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>6,801</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>735</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>44.31</t>
+          <t>31.41</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>0.34</v>
+        <v>-0.95</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>23.27</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>23.07</v>
+        <v>23.14</v>
       </c>
       <c r="AZ9" t="n">
-        <v>23.17</v>
+        <v>23.13</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>23.69</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BD9" t="n">
         <v>0.13</v>
@@ -4576,53 +4576,53 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-93.67</t>
+          <t>-93.57</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>81258.02317415731</t>
+          <t>81181.22650771389</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>4157.0</t>
+          <t>5068.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>5218.8</v>
+        <v>5073.8</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>7467.8</t>
+          <t>7268.1</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>7306.04</v>
+        <v>7204.54</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-2249</t>
+          <t>-2194</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-8.815079963841526</t>
+          <t>-140.3136993301846</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-821.3489825210982</t>
+          <t>-863.5561058450712</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>4157.0</t>
+          <t>5068.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>108.64</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>90.23</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>23.45</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-22.22</t>
+          <t>-30.12</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-6.75</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,66 +4990,66 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>6,801</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>735</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>48.39</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>43.01</t>
+          <t>44.31</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>-0.68</v>
+        <v>0.34</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.32</v>
+        <v>1.53</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>22.98</v>
+        <v>23.07</v>
       </c>
       <c r="AZ10" t="n">
-        <v>23.19</v>
+        <v>23.17</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>23.68</t>
+          <t>23.69</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>48.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC10" t="n">
         <v>0.17</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,53 +5058,53 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-94.25</t>
+          <t>-93.67</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>81258.02317415731</t>
+          <t>81181.22650771389</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>5821.0</t>
+          <t>4157.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>6127.4</v>
+        <v>5218.8</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>7878.3</t>
+          <t>7467.8</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>7309.38</v>
+        <v>7306.04</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-1750</t>
+          <t>-2249</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>138.9183568647506</t>
+          <t>-8.815079963841526</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-634.1120569682398</t>
+          <t>-821.3489825210982</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>5821.0</t>
+          <t>4157.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>108.64</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>90.23</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>23.65</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5296,162 +5296,162 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>23.35</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-22.22</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-7.34</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>10.87</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>22.15</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2025/07/08</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>22.75</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2.93</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>20.70</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>25.2</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>-7.94</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>10.87</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>22.15</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>2025/07/08</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>2025/09/05</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,66 +5472,66 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>6,801</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>735</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>48.39</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>52.69</t>
+          <t>43.01</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>-1.99</v>
+        <v>-0.68</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.44</v>
+        <v>2.32</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>22.88</v>
+        <v>22.98</v>
       </c>
       <c r="AZ11" t="n">
-        <v>23.22</v>
+        <v>23.19</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>78.99</t>
+          <t>48.56</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,53 +5540,53 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-94.95</t>
+          <t>-94.25</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>81258.02317415731</t>
+          <t>81181.22650771389</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>5739.0</t>
+          <t>5821.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>9625.6</v>
+        <v>6127.4</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>7974.8</t>
+          <t>7878.3</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>7390.28</v>
+        <v>7309.38</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>-1750</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>279.4693411980216</t>
+          <t>138.9183568647506</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-522.2695898581487</t>
+          <t>-634.1120569682398</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>5739.0</t>
+          <t>5821.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>108.64</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>90.23</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5721,17 +5721,17 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>196.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>20.70</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-7.74</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,50 +5954,50 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>6,801</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>735</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>38.71</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>68.82</t>
+          <t>52.69</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-1.9</v>
+        <v>-1.99</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.92</v>
+        <v>3.44</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.67</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>22.8</v>
+        <v>22.88</v>
       </c>
       <c r="AZ12" t="n">
-        <v>23.25</v>
+        <v>23.22</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -6006,14 +6006,14 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>154.33</t>
+          <t>78.99</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,53 +6022,53 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-95.95</t>
+          <t>-94.95</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>81258.02317415731</t>
+          <t>81181.22650771389</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>4584.0</t>
+          <t>5739.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>9280.4</v>
+        <v>9625.6</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>8403.9</t>
+          <t>7974.8</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>7418.64</v>
+        <v>7390.28</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>425.2400559355071</t>
+          <t>279.4693411980216</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-335.0564372059416</t>
+          <t>-522.2695898581487</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>4584.0</t>
+          <t>5739.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>108.64</t>
+          <t>108.18</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>90.23</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>1636</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CS12" t="inlineStr">
+        <is>
           <t>23.2</t>
-        </is>
-      </c>
-      <c r="CS12" t="inlineStr">
-        <is>
-          <t>23.25</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/ITO導電玻璃.xlsx
+++ b/Result/checksun_type/ITO導電玻璃.xlsx
@@ -933,7 +933,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b2】</t>
+          <t>價_量;【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>735.0</t>
+          <t>272.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>32.59</t>
+          <t>41.44</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-6.94</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,87 +1113,87 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>68.89</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>2.15</v>
+        <v>0.17</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.09</v>
+        <v>0.29</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>23.41</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>23.32</v>
+        <v>23.34</v>
       </c>
       <c r="AZ2" t="n">
-        <v>22.98</v>
+        <v>22.96</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>23.71</t>
+          <t>23.68</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>37.60</t>
+          <t>29.12</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-95.86</t>
+          <t>-95.54</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>81181.22650771389</t>
+          <t>81081.01470588235</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>17668.0</t>
+          <t>6420.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>9481.799999999999</v>
+        <v>10199.8</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>7151.3</t>
+          <t>7211.2</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>7185.22</v>
+        <v>7252.54</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-251.3035860860211</t>
+          <t>-130.8322149929296</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>871.1915059205076</t>
+          <t>531.7603260190735</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>17668.0</t>
+          <t>6420.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1313,22 +1313,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>106.59</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>89.07</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
           <t>24.05</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>24.4</t>
-        </is>
-      </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.45</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b2】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>663.0</t>
+          <t>735.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>17.62</t>
+          <t>32.59</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,63 +1616,63 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>68.89</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>3.28</v>
+        <v>2.15</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.72</v>
+        <v>-0.09</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-3.01</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>23.14</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>23.31</v>
+        <v>23.32</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22.99</v>
+        <v>22.98</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>23.71</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>37.60</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="BD3" t="n">
         <v>0.08</v>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-96.25</t>
+          <t>-95.86</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>81181.22650771389</t>
+          <t>81081.01470588235</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>15776.0</t>
+          <t>17668.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>7008.2</v>
+        <v>9481.799999999999</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>5958.4</t>
+          <t>7151.3</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>6912.06</v>
+        <v>7185.22</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-455.3936028144808</t>
+          <t>-251.3035860860211</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>119.8363519968225</t>
+          <t>871.1915059205076</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>15776.0</t>
+          <t>17668.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>106.59</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>89.07</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>663.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,172 +1922,172 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>23.9</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-1.92</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>17.62</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>3.36</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-4.85</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-5.16</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>10.87</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>22.15</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/07/08</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>22.75</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>25.2</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-8.73</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>10.87</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>22.15</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/07/08</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2025/09/05</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,63 +2098,63 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AU4" t="n">
-        <v>-1.3</v>
+        <v>-0.72</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.01</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.14</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>23.3</v>
+        <v>23.31</v>
       </c>
       <c r="AZ4" t="n">
-        <v>23</v>
+        <v>22.99</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-81.34</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="BD4" t="n">
         <v>0.08</v>
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>81181.22650771389</t>
+          <t>81081.01470588235</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>5182.0</t>
+          <t>15776.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>4604.6</v>
+        <v>7008.2</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>4839.2</t>
+          <t>5958.4</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>6785.7</v>
+        <v>6912.06</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-234</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-559.9808673256268</t>
+          <t>-455.3936028144808</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-755.0937376083275</t>
+          <t>119.8363519968225</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>5182.0</t>
+          <t>15776.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2277,22 +2277,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>106.59</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>89.07</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,187 +2389,187 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>224.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-4.85</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-8.73</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>10.87</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>260.0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>22.9</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>3.78</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-6.50</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>22.15</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2025/07/08</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>22.75</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>25.2</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-9.13</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>10.87</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>22.15</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2025/07/08</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>2025/09/05</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,50 +2580,50 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-0.48</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>-1.37</v>
+        <v>-1.3</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>23.33</v>
+        <v>23.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>23.02</v>
+        <v>23</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2632,14 +2632,14 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-69.66</t>
+          <t>-81.34</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-95.49</t>
+          <t>-96.25</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>81181.22650771389</t>
+          <t>81081.01470588235</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>5953.0</t>
+          <t>5182.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>4581.8</v>
+        <v>4604.6</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>4900.3</t>
+          <t>4839.2</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>6754.58</v>
+        <v>6785.7</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-318</t>
+          <t>-234</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-524.5058000014994</t>
+          <t>-559.9808673256268</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-842.9548035582447</t>
+          <t>-755.0937376083275</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>5953.0</t>
+          <t>5182.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>106.59</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>89.07</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>260.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-18.40</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,12 +3062,12 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -3077,51 +3077,51 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-0.99</v>
+        <v>-0.48</v>
       </c>
       <c r="AU6" t="n">
-        <v>-1.06</v>
+        <v>-1.37</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>23.13</t>
+          <t>23.01</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>23.38</v>
+        <v>23.33</v>
       </c>
       <c r="AZ6" t="n">
-        <v>23.04</v>
+        <v>23.02</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>23.71</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-69.66</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-94.70</t>
+          <t>-95.49</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>81181.22650771389</t>
+          <t>81081.01470588235</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>2830.0</t>
+          <t>5953.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>4222.6</v>
+        <v>4581.8</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>5175.0</t>
+          <t>4900.3</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>6856.42</v>
+        <v>6754.58</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-952</t>
+          <t>-318</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-466.6059811730004</t>
+          <t>-524.5058000014994</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-1020.972226216761</t>
+          <t>-842.9548035582447</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>2830.0</t>
+          <t>5953.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>106.59</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>89.07</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,17 +3306,17 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>229.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,172 +3368,172 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>22.9</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-18.40</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>23.0</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>3.36</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-33.26</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-9.13</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>10.87</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>22.15</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2025/07/08</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>22.75</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>25.2</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>-8.73</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>10.87</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>22.15</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2025/07/08</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>2025/09/05</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,12 +3544,12 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3563,31 +3563,31 @@
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-0.95</v>
+        <v>-0.99</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.44</v>
+        <v>-1.06</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>23.22</t>
+          <t>23.13</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>23.32</v>
+        <v>23.38</v>
       </c>
       <c r="AZ7" t="n">
-        <v>23.08</v>
+        <v>23.04</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3596,14 +3596,14 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-26.25</t>
+          <t>-48.83</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-94.06</t>
+          <t>-94.70</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>81181.22650771389</t>
+          <t>81081.01470588235</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>5300.0</t>
+          <t>2830.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>4820.8</v>
+        <v>4222.6</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>7223.2</t>
+          <t>5175.0</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>7076.86</v>
+        <v>6856.42</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-2402</t>
+          <t>-952</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-365.8121184377713</t>
+          <t>-466.6059811730004</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-904.2123933640405</t>
+          <t>-1020.972226216761</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>5300.0</t>
+          <t>2830.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>108.18</t>
+          <t>106.59</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>89.07</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,14 +3788,14 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="CQ7" t="inlineStr">
+        <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
-        <is>
-          <t>23.3</t>
-        </is>
-      </c>
       <c r="CR7" t="inlineStr">
         <is>
           <t>22.9</t>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>229.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,172 +3850,172 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-33.26</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-09-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-07-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-07-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>23.95</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>-8.73</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>10.87</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025/08/22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>25.7</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>22.15</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2025/07/08</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>22.75</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2.52</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-30.81</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-09-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-07-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-07-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/09/05</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>25.2</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>23.95</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>-7.94</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>10.87</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025/08/22</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2025/10/14</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>22.15</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>2025/07/08</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>2025/09/05</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,67 +4026,67 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>4.55</t>
         </is>
       